--- a/Översikt KROKOM.xlsx
+++ b/Översikt KROKOM.xlsx
@@ -567,7 +567,7 @@
         <v>45716</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44522</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45348</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44165</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45384</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>45254</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>45709</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>45637</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45603</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44378</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45478</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45121</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>44323.61518518518</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>44565</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45155</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45646</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>45630</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45453</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44363</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>45219</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>45041</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>45625</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45553</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>45790</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45663</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>45428</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>45644</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>45845</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>45596.5093287037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>44306.52587962963</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44575</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>44326</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44581</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>45792</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45475</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>44780</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>45784.56270833333</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45691</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>44323</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>44475</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>45646</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>45646</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>44231</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>45849.31563657407</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>45551</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45512</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>45534</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>45488.56961805555</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>45639</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>45719.52238425926</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44795</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>45041</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44498</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>45580</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>45527</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>45454</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45219</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>45643</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44118</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>44552</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>45457</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>45181</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>45169</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44308</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>44133</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>44698</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44585</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>45475</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>44500</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45616</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>45316</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45839.68914351852</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>45149</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>45267</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44271</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>44265</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44534</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>44494</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>44326</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45370</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44477</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>45180</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>44834</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44797</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>45474</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>45252</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>45581</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>45832.38581018519</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45755.47527777778</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>44183</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>44515</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>44162</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44452</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>45079</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>45726.46192129629</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>44540</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44557</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45551</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45838.67858796296</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>44150</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>45615.60217592592</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>45874.67765046296</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>45532</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44903</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>44546</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44510.94930555556</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>44728</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>44879</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45621</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>45735</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45632</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>45310</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>45617</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>44895</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44553</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>45624</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45169</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44904</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45527</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45849.42818287037</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>44174</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>45595</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>44966</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>45764</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>44867</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>45313</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>45692</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>44540</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45526</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45656.54600694445</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45511.55719907407</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45636</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45216</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>45271</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45453.63133101852</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>45630</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>45821.44299768518</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>45216.67748842593</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>44757</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>44873</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45372</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>44757</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>44841</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>45233</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>44355</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44161</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>44378</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>44524</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>44316</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>44230</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>44757</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45268</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>44879</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45223</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>45376</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44540</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>45793.4189699074</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45595</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>45554</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45348</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>44209</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45804.60005787037</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>45805</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>45647.6565625</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>45643.53393518519</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>45656.59703703703</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>44279</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>44099</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>44154</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>44090</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>44512</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44445</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44512</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>44445</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>44728</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>44207</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>44797</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>44742</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>44377</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45407</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45180</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>45635</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>45243</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>44308</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45123</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>45622</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>44630</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45153</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44603</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45595</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45595</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45838</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>45079</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45838.67815972222</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>45271</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45595</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45839.60460648148</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44568</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>45841.52454861111</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45847.51078703703</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45020</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>45700</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45645.67945601852</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>44683</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45685.78776620371</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45098</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>45819.65796296296</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45862.43403935185</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45862.4257175926</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45695.42197916667</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>45826.45174768518</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>45686.27208333334</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45609</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45750.42127314815</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45595</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>45609</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44540</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45702.47149305556</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>44568</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>44075</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>44568</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45736.42743055556</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44313</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44113</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44102</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44103</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44214</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44371</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>44748.94689814815</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44407</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44473.44813657407</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44473.508125</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44256</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44183</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>44175</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>44679</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44449</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44665</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44173</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>44445</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>44494</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>44610</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44788</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44376.87497685185</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>44377.44767361111</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>44285</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44133</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>44263</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>44183</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>44183</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>44524</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44370</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>44591</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>44123</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>44714.438125</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>44162</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>44057</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>44090</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44141</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44255</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44577.47756944445</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44287</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44533</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44749</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44126.94510416667</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>44831.37650462963</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44200</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44172</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>44512.94539351852</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44369.41452546296</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44271.43831018519</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44312</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>44502.94153935185</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>44306</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44788</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44502</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>44207</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>44851.57131944445</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>44209</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>44209</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>44243</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>44473</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44106</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>44466.53040509259</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>44300</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>44539</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>44495</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>44495</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>44277.59521990741</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44062</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>44512</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>44172</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>44337</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>44214</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>44693.41668981482</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>44502.94140046297</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>44139</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>44473.53681712963</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26040,7 +26040,7 @@
         <v>44077</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>44470</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>44858</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>44153</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26268,7 +26268,7 @@
         <v>44714</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>44151</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44377</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>44728.94420138889</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>44459</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>44382.92065972222</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44526</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>44095</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44358.63585648148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>44214</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>44524</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44820</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>44076</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44113</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>44123</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>44610</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>44123</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>44473.53013888889</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>44459</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>44337</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>44848</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>44875.41104166667</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>44697.94231481481</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>44123</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>44519.63436342592</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>44727</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>44470</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         <v>44169</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>44214</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>44279</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44705</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44307.42378472222</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>44284</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>44209</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>44468</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>44447</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44118.98730324074</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44470.39989583333</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>45452.56446759259</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>44285</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>45679.70027777777</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>45600.58076388889</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>45749</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>45720</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>45035</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>45758.58943287037</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44848</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>45412.51260416667</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45670</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>44400.37204861111</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45714.34859953704</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45719.32584490741</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45560.69164351852</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>45370.94969907407</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>44908</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>45203.46523148148</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>45245</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>45586.53618055556</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>45459.55150462963</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>45698.39486111111</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45607</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>45698.45653935185</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>45362</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>45485</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>44825</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45370</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45695</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45665.57373842593</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45251.65152777778</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>45572.45601851852</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>44803</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>45770.64677083334</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45615.61121527778</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45608.61606481481</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45674</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>45713.60719907407</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45721.54896990741</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45721</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45203</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>45342</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45700.37127314815</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45700.37481481482</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>45593.38568287037</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>45672.53806712963</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>45386</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>45189.60987268519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45362</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45414.486875</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45552.57210648148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>45195</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>45649.4634375</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45531.62141203704</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>45643.65354166667</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45411</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>45747.47025462963</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44830</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>45630.47099537037</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>45055</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44316</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45310</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>45253</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>44875</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45160.66704861111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>45547.42732638889</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>45763.46918981482</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>44834.95019675926</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>45082</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>45740</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44874</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45705.33446759259</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -32698,7 +32698,7 @@
         <v>44887</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45602</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>45751.37320601852</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>44901.59349537037</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45554</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>44140</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>45471.63390046296</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>45239.9681712963</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>45474.69155092593</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44389</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45532.58101851852</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>45243.37567129629</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -33402,7 +33402,7 @@
         <v>45758.66180555556</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45758.67065972222</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>45055</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -33573,7 +33573,7 @@
         <v>45398</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>45369</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -33687,7 +33687,7 @@
         <v>45457.55922453704</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45265.52887731481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>45748.3822337963</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45692.64298611111</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>45454.57899305555</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45250</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>45649.45143518518</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45457.35388888889</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45467</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45452.55271990741</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45226</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>45726.37850694444</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>45411.4666087963</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44456</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>45209</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>45746</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45744</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45740.60405092593</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>45371</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>45392</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>45414.96341435185</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>45751.6877662037</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>45751.28243055556</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>45090</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>45554.59538194445</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>45740.60347222222</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>45726.56341435185</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>45726.5827199074</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45726.61520833334</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -35410,7 +35410,7 @@
         <v>45096</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>45580.36991898148</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45474.69074074074</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45377</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>45560.45841435185</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -35705,7 +35705,7 @@
         <v>45118</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45597.49638888889</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>45260</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>45279</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>44540</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45278.65582175926</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44866</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45467</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>45117</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>45407</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>45432.36971064815</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>45446.68733796296</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -36394,7 +36394,7 @@
         <v>45686.35247685185</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>44911</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>45748.36445601852</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45748.37173611111</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -36627,7 +36627,7 @@
         <v>45371</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>44965</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>45099.37211805556</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -36803,7 +36803,7 @@
         <v>45266</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>45245</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>45691.61996527778</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>45042</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>45721.4546412037</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>45254</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>45446.47634259259</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>45525</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45112</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>45133</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>44061</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>44539</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45309.94650462963</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>45560</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>45484</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>45527.39858796296</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>45245.5478125</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45586</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45478.60708333334</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45373</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45090</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>44873</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45182</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>44970</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45484</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>45477.35225694445</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38320,7 +38320,7 @@
         <v>45393</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -38377,7 +38377,7 @@
         <v>45532.48732638889</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -38434,7 +38434,7 @@
         <v>44550</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45415.45006944444</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>44522.46662037037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>44974</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -38667,7 +38667,7 @@
         <v>45760.81083333334</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -38724,7 +38724,7 @@
         <v>45601.33743055556</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>44922</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -38843,7 +38843,7 @@
         <v>44483.42253472222</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>45244</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -38957,7 +38957,7 @@
         <v>45324</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39014,7 +39014,7 @@
         <v>45764.55260416667</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>45217</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>45474</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>45282</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>45478.42063657408</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>45165.69965277778</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>44516</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>45203</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>45300</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -39527,7 +39527,7 @@
         <v>45152</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -39589,7 +39589,7 @@
         <v>45686.32671296296</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45511.95109953704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45701</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>44466.56642361111</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>44498</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>44504</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>45635.67949074074</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>45608.43930555556</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40050,7 +40050,7 @@
         <v>45715</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>45776</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40169,7 +40169,7 @@
         <v>45693</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>44939</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>45777</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -40345,7 +40345,7 @@
         <v>45712</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>45551.34414351852</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>45777</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>45777</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>45779.56659722222</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>45779.63834490741</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45779.57626157408</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45779.65980324074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>45477.32728009259</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45721.45563657407</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45779.42630787037</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45779.5674074074</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45696</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41111,7 +41111,7 @@
         <v>45488.94857638889</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>45608.86341435185</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>45783.44828703703</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>45783</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -41344,7 +41344,7 @@
         <v>45475</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45112</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45418.94616898148</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -41515,7 +41515,7 @@
         <v>45783</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -41572,7 +41572,7 @@
         <v>45783.45121527778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>45783.43409722222</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>45713.37111111111</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45688.38393518519</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>44600.37212962963</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>45740</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>44362</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>45538.68200231482</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         <v>45117</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>45579.66459490741</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42147,7 +42147,7 @@
         <v>45392</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>44480</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>44592</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -42323,7 +42323,7 @@
         <v>44893</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -42380,7 +42380,7 @@
         <v>45406.05033564815</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -42442,7 +42442,7 @@
         <v>45594.463125</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -42499,7 +42499,7 @@
         <v>45786.35219907408</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -42556,7 +42556,7 @@
         <v>45119</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>44904</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -42670,7 +42670,7 @@
         <v>45786</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>45180</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>44188</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>45121</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>45706</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45785.52112268518</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>45785.5403125</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>45666.65987268519</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
         <v>45496.41289351852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43198,7 +43198,7 @@
         <v>45618.53126157408</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45618.53633101852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>45601.38071759259</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45785.54635416667</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45554.59447916667</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45786</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>45551.47325231481</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45700.30092592593</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45786.64972222222</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45786.65702546296</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45491.44971064815</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>45785</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45786.66140046297</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45715</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>45550.66542824074</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45109.44534722222</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
         <v>44214</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45785.51092592593</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>45467</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -44311,7 +44311,7 @@
         <v>44498</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>45561.61515046296</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>44938.93989583333</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>45700.56194444445</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>45750.60577546297</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -44601,7 +44601,7 @@
         <v>45602.38614583333</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -44658,7 +44658,7 @@
         <v>45602.39862268518</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>45602.42878472222</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>44971</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>45789.58238425926</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45789.61349537037</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45243.33297453704</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45005,7 +45005,7 @@
         <v>45145.95255787037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45067,7 +45067,7 @@
         <v>45572</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>45583.52885416667</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45687.48931712963</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>45566.51501157408</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>44510.9491087963</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>44207</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45706.59251157408</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>45632</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45635.39820601852</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -45590,7 +45590,7 @@
         <v>44582</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>45721.66456018519</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -45704,7 +45704,7 @@
         <v>45484</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>45232.46239583333</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45552.67611111111</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -45880,7 +45880,7 @@
         <v>45614.63575231482</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>45660.49618055556</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -45994,7 +45994,7 @@
         <v>45834.34737268519</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45833.63579861111</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>45833.49052083334</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46170,7 +46170,7 @@
         <v>45833.49057870371</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>44887</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>44818</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45195</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45631.61869212963</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>44631</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45695.60015046296</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>44970</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45056</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>45056</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45713</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45166</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>44391</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45476</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>44596</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>45534.57745370371</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>45791</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>45603.44815972223</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45791.3162037037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>45643.64706018518</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>44557</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>45714.69212962963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>44658</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>45588</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45796.52836805556</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>45588</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>44186</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45378</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>45835.42712962963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45707.55246527777</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>45720.60774305555</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45615.61302083333</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48044,7 +48044,7 @@
         <v>45686.33310185185</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48106,7 +48106,7 @@
         <v>45560.6599537037</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45793.45204861111</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45748</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>45698.40146990741</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -48339,7 +48339,7 @@
         <v>45343.95162037037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45699</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>44988.94056712963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>44141</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45198.42734953704</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -48644,7 +48644,7 @@
         <v>45796.59857638889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>45706.55993055556</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -48758,7 +48758,7 @@
         <v>45836.34413194445</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>44686</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45573.54893518519</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45432.54027777778</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45182</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45182</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45608</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45695.57171296296</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45723.50841435185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45225.60212962963</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45840.40717592592</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -49400,7 +49400,7 @@
         <v>45839.61594907408</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>45615.59521990741</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         <v>45839.61582175926</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45840.58494212963</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45204</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45401.59810185185</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>44741</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45695.4046875</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -49871,7 +49871,7 @@
         <v>45695.42418981482</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>45839.61541666667</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45460.44076388889</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>45839.72320601852</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45695.45013888889</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50171,7 +50171,7 @@
         <v>45707.33935185185</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>45565.32449074074</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         <v>45772.62052083333</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -50347,7 +50347,7 @@
         <v>44151</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -50404,7 +50404,7 @@
         <v>45246</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -50461,7 +50461,7 @@
         <v>44788</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -50518,7 +50518,7 @@
         <v>45554.59550925926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -50575,7 +50575,7 @@
         <v>45798.63611111111</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45656</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>45798.63596064815</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -50761,7 +50761,7 @@
         <v>45746.79134259259</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -50818,7 +50818,7 @@
         <v>45839.61563657408</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -50880,7 +50880,7 @@
         <v>45716.55237268518</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>44601.35342592592</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -50999,7 +50999,7 @@
         <v>45800.57129629629</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45800.57461805556</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>45800</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45667.57217592592</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45800.37061342593</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45699.66576388889</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -51346,7 +51346,7 @@
         <v>45190</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -51403,7 +51403,7 @@
         <v>45686</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -51460,7 +51460,7 @@
         <v>45216</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45316</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -51574,7 +51574,7 @@
         <v>45772.58283564815</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45772.59200231481</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -51688,7 +51688,7 @@
         <v>44732</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>45841.46925925926</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -51807,7 +51807,7 @@
         <v>45800.56810185185</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -51864,7 +51864,7 @@
         <v>45547.42736111111</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -51921,7 +51921,7 @@
         <v>45791</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>45841.67834490741</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45176</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52102,7 +52102,7 @@
         <v>45694.64416666667</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52164,7 +52164,7 @@
         <v>45842.39587962963</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45842.40013888889</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45117</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -52350,7 +52350,7 @@
         <v>45123.61459490741</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -52412,7 +52412,7 @@
         <v>45800.65177083333</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -52469,7 +52469,7 @@
         <v>45800.64319444444</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -52526,7 +52526,7 @@
         <v>45620.67667824074</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -52583,7 +52583,7 @@
         <v>45231</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -52645,7 +52645,7 @@
         <v>45600.49616898148</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -52702,7 +52702,7 @@
         <v>45662</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -52759,7 +52759,7 @@
         <v>45842.6099537037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -52816,7 +52816,7 @@
         <v>45684.62510416667</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -52878,7 +52878,7 @@
         <v>45762.60907407408</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -52940,7 +52940,7 @@
         <v>45746</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53002,7 +53002,7 @@
         <v>45117</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>45800</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53121,7 +53121,7 @@
         <v>45803</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53178,7 +53178,7 @@
         <v>45401.59133101852</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53235,7 +53235,7 @@
         <v>45693.67361111111</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>45803.6837962963</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -53354,7 +53354,7 @@
         <v>45638.81385416666</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -53411,7 +53411,7 @@
         <v>45574.43403935185</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>45704.71069444445</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         <v>45618.54398148148</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         <v>45692.58106481482</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>45097</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>45803.69828703703</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45700.27895833334</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>45623.48571759259</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -53882,7 +53882,7 @@
         <v>45701.60901620371</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -53939,7 +53939,7 @@
         <v>45694.43806712963</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>45630</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>45848.48070601852</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45687</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>45676</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54229,7 +54229,7 @@
         <v>45847.46962962963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -54286,7 +54286,7 @@
         <v>45761.50909722222</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -54343,7 +54343,7 @@
         <v>45261</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -54400,7 +54400,7 @@
         <v>45848.60371527778</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -54457,7 +54457,7 @@
         <v>45805.47425925926</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -54514,7 +54514,7 @@
         <v>45721</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -54571,7 +54571,7 @@
         <v>44203</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         <v>45841.43987268519</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45216</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -54742,7 +54742,7 @@
         <v>44140</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -54799,7 +54799,7 @@
         <v>45847.51106481482</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -54856,7 +54856,7 @@
         <v>45805.54185185185</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -54913,7 +54913,7 @@
         <v>45721.5113425926</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -54970,7 +54970,7 @@
         <v>45705</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55027,7 +55027,7 @@
         <v>45614.63697916667</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55084,7 +55084,7 @@
         <v>44715.48863425926</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55146,7 +55146,7 @@
         <v>45510.58033564815</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45751.3734837963</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45751.57877314815</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -55322,7 +55322,7 @@
         <v>45457.38799768518</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -55379,7 +55379,7 @@
         <v>45733</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>45408</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -55493,7 +55493,7 @@
         <v>45805</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -55550,7 +55550,7 @@
         <v>45693.48239583334</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -55607,7 +55607,7 @@
         <v>44349</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -55669,7 +55669,7 @@
         <v>45698.4930787037</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>44273</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -55783,7 +55783,7 @@
         <v>45692</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -55845,7 +55845,7 @@
         <v>45695.61160879629</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -55907,7 +55907,7 @@
         <v>44154</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -55964,7 +55964,7 @@
         <v>45602</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56021,7 +56021,7 @@
         <v>45847.65717592592</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56083,7 +56083,7 @@
         <v>45847.46462962963</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56140,7 +56140,7 @@
         <v>45698.57129629629</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56197,7 +56197,7 @@
         <v>45686.39777777778</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56259,7 +56259,7 @@
         <v>45849.4525462963</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -56316,7 +56316,7 @@
         <v>45238</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -56373,7 +56373,7 @@
         <v>45849.3859837963</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -56435,7 +56435,7 @@
         <v>44524</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -56492,7 +56492,7 @@
         <v>45748.59744212963</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -56549,7 +56549,7 @@
         <v>45607</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -56606,7 +56606,7 @@
         <v>45614.63606481482</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -56663,7 +56663,7 @@
         <v>45614.63701388889</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -56720,7 +56720,7 @@
         <v>44285</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -56777,7 +56777,7 @@
         <v>45848</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -56834,7 +56834,7 @@
         <v>45807.58930555556</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -56891,7 +56891,7 @@
         <v>44179</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -56948,7 +56948,7 @@
         <v>45720.40268518519</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57005,7 +57005,7 @@
         <v>45810.32105324074</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57062,7 +57062,7 @@
         <v>45140</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57119,7 +57119,7 @@
         <v>45090</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57176,7 +57176,7 @@
         <v>45466.62116898148</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57233,7 +57233,7 @@
         <v>45639</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -57290,7 +57290,7 @@
         <v>45764</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -57347,7 +57347,7 @@
         <v>45642.6366087963</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -57404,7 +57404,7 @@
         <v>44334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -57461,7 +57461,7 @@
         <v>45696.3440162037</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -57518,7 +57518,7 @@
         <v>45807.56728009259</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -57575,7 +57575,7 @@
         <v>45118.94061342593</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -57632,7 +57632,7 @@
         <v>45638.81375</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -57689,7 +57689,7 @@
         <v>45708</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -57751,7 +57751,7 @@
         <v>45693</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -57808,7 +57808,7 @@
         <v>45713.36836805556</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -57870,7 +57870,7 @@
         <v>45168</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -57927,7 +57927,7 @@
         <v>44792.27644675926</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -57984,7 +57984,7 @@
         <v>44750</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58041,7 +58041,7 @@
         <v>44721.39003472222</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58103,7 +58103,7 @@
         <v>45474.3981712963</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58160,7 +58160,7 @@
         <v>45737.36873842592</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58217,7 +58217,7 @@
         <v>44331</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -58274,7 +58274,7 @@
         <v>44726</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -58331,7 +58331,7 @@
         <v>45692</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -58393,7 +58393,7 @@
         <v>45811.54760416667</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -58450,7 +58450,7 @@
         <v>45853.6156712963</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -58512,7 +58512,7 @@
         <v>45695.47791666666</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -58569,7 +58569,7 @@
         <v>45854.66518518519</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -58626,7 +58626,7 @@
         <v>45810.31376157407</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -58683,7 +58683,7 @@
         <v>45812.32266203704</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -58740,7 +58740,7 @@
         <v>44855</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -58797,7 +58797,7 @@
         <v>44855</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -58854,7 +58854,7 @@
         <v>45694.34268518518</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -58916,7 +58916,7 @@
         <v>44880</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -58973,7 +58973,7 @@
         <v>45811.67769675926</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59030,7 +59030,7 @@
         <v>45204.40770833333</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59087,7 +59087,7 @@
         <v>45467</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59144,7 +59144,7 @@
         <v>44741</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59201,7 +59201,7 @@
         <v>45811.69912037037</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -59258,7 +59258,7 @@
         <v>45670</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -59315,7 +59315,7 @@
         <v>45854.65378472222</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -59372,7 +59372,7 @@
         <v>45614.65925925926</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -59429,7 +59429,7 @@
         <v>45519.60965277778</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -59486,7 +59486,7 @@
         <v>45750.42650462963</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -59543,7 +59543,7 @@
         <v>45813.44443287037</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -59600,7 +59600,7 @@
         <v>44726</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -59657,7 +59657,7 @@
         <v>45813.46969907408</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -59714,7 +59714,7 @@
         <v>45814</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -59771,7 +59771,7 @@
         <v>45814</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -59828,7 +59828,7 @@
         <v>45300</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -59885,7 +59885,7 @@
         <v>45713.36561342593</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -59947,7 +59947,7 @@
         <v>45713.38028935185</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60009,7 +60009,7 @@
         <v>45700.6833912037</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60066,7 +60066,7 @@
         <v>45744.59894675926</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60128,7 +60128,7 @@
         <v>45279</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60185,7 +60185,7 @@
         <v>45635</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -60242,7 +60242,7 @@
         <v>45238</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -60304,7 +60304,7 @@
         <v>45813.68361111111</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -60361,7 +60361,7 @@
         <v>45257</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -60418,7 +60418,7 @@
         <v>45247</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -60475,7 +60475,7 @@
         <v>45785.67431712963</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -60537,7 +60537,7 @@
         <v>45713.59623842593</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -60599,7 +60599,7 @@
         <v>45709</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>45855.61193287037</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -60718,7 +60718,7 @@
         <v>45818.36246527778</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -60780,7 +60780,7 @@
         <v>44757</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -60842,7 +60842,7 @@
         <v>45818.3293287037</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -60904,7 +60904,7 @@
         <v>45671.59114583334</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>45817.56761574074</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61018,7 +61018,7 @@
         <v>44711</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61080,7 +61080,7 @@
         <v>44377</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61137,7 +61137,7 @@
         <v>45815.50844907408</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61194,7 +61194,7 @@
         <v>45818.34474537037</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -61256,7 +61256,7 @@
         <v>45713.59163194444</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -61318,7 +61318,7 @@
         <v>45369</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>45274</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -61432,7 +61432,7 @@
         <v>45818.34473379629</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -61494,7 +61494,7 @@
         <v>44370</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -61551,7 +61551,7 @@
         <v>44427</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -61608,7 +61608,7 @@
         <v>45818.33532407408</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -61670,7 +61670,7 @@
         <v>45818.34833333334</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -61732,7 +61732,7 @@
         <v>45818.37056712963</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -61794,7 +61794,7 @@
         <v>45862.34668981482</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -61856,7 +61856,7 @@
         <v>45820</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -61913,7 +61913,7 @@
         <v>45173</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -61975,7 +61975,7 @@
         <v>45860</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62032,7 +62032,7 @@
         <v>45820</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62089,7 +62089,7 @@
         <v>45694.65905092593</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62146,7 +62146,7 @@
         <v>45203.44248842593</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62203,7 +62203,7 @@
         <v>45165.70483796296</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -62260,7 +62260,7 @@
         <v>45713.59952546296</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -62322,7 +62322,7 @@
         <v>45820.36233796296</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>45820.36512731481</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -62436,7 +62436,7 @@
         <v>45820.47200231482</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -62498,7 +62498,7 @@
         <v>45820</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -62555,7 +62555,7 @@
         <v>45653.57240740741</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -62617,7 +62617,7 @@
         <v>45862.42901620371</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -62674,7 +62674,7 @@
         <v>45820.36498842593</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -62731,7 +62731,7 @@
         <v>45820.36506944444</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -62788,7 +62788,7 @@
         <v>45861.6841087963</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -62850,7 +62850,7 @@
         <v>45448.67574074074</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -62912,7 +62912,7 @@
         <v>45821.39026620371</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -62969,7 +62969,7 @@
         <v>45692.60364583333</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63026,7 +63026,7 @@
         <v>45863.45778935185</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63083,7 +63083,7 @@
         <v>45708</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63145,7 +63145,7 @@
         <v>45863</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63202,7 +63202,7 @@
         <v>44847</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -63259,7 +63259,7 @@
         <v>45701</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -63321,7 +63321,7 @@
         <v>44847</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -63378,7 +63378,7 @@
         <v>44858</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -63435,7 +63435,7 @@
         <v>45713.59741898148</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -63497,7 +63497,7 @@
         <v>45863.58127314815</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -63559,7 +63559,7 @@
         <v>45180</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -63621,7 +63621,7 @@
         <v>45863.59111111111</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -63683,7 +63683,7 @@
         <v>45763.44112268519</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45764.47059027778</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -63797,7 +63797,7 @@
         <v>45750.6447800926</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -63859,7 +63859,7 @@
         <v>45757.56491898148</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -63916,7 +63916,7 @@
         <v>45867.41707175926</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -63973,7 +63973,7 @@
         <v>45867.46560185185</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64030,7 +64030,7 @@
         <v>45826.4705787037</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45022</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>44757</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64211,7 +64211,7 @@
         <v>45453</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64273,7 +64273,7 @@
         <v>45453.95237268518</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -64335,7 +64335,7 @@
         <v>45499.48672453704</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -64392,7 +64392,7 @@
         <v>45719</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -64449,7 +64449,7 @@
         <v>45687</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -64506,7 +64506,7 @@
         <v>45748.57269675926</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -64563,7 +64563,7 @@
         <v>45869.34439814815</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -64625,7 +64625,7 @@
         <v>45649.38149305555</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -64682,7 +64682,7 @@
         <v>45764.40834490741</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
         <v>45719.37307870371</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>45870</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -64858,7 +64858,7 @@
         <v>45827.34488425926</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -64920,7 +64920,7 @@
         <v>45483</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -64977,7 +64977,7 @@
         <v>44379.59675925926</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65034,7 +65034,7 @@
         <v>45257</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65091,7 +65091,7 @@
         <v>45348</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65148,7 +65148,7 @@
         <v>45832</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65205,7 +65205,7 @@
         <v>45832.34630787037</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65267,7 +65267,7 @@
         <v>45565.33152777778</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -65324,7 +65324,7 @@
         <v>45832.53935185185</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -65386,7 +65386,7 @@
         <v>45139</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>45832.53225694445</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>45572</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -65572,7 +65572,7 @@
         <v>44544.49326388889</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -65629,7 +65629,7 @@
         <v>45601</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -65686,7 +65686,7 @@
         <v>45758</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -65743,7 +65743,7 @@
         <v>45875.51046296296</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -65800,7 +65800,7 @@
         <v>44732</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -65857,7 +65857,7 @@
         <v>45833.34490740741</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -65919,7 +65919,7 @@
         <v>44865</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -65976,7 +65976,7 @@
         <v>45833.36050925926</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66033,7 +66033,7 @@
         <v>45833.36083333333</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66090,7 +66090,7 @@
         <v>45834.34726851852</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66152,7 +66152,7 @@
         <v>44228</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66209,7 +66209,7 @@
         <v>45834.61517361111</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -66271,7 +66271,7 @@
         <v>45876</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -66328,7 +66328,7 @@
         <v>45876</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -66385,7 +66385,7 @@
         <v>45876</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -66442,7 +66442,7 @@
         <v>45833.36111111111</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -66499,7 +66499,7 @@
         <v>45634.7925</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -66556,7 +66556,7 @@
         <v>45634.79854166666</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -66613,7 +66613,7 @@
         <v>45608.61923611111</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -66670,7 +66670,7 @@
         <v>45600.433125</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -66732,7 +66732,7 @@
         <v>45701.57363425926</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -66789,7 +66789,7 @@
         <v>45392.95844907407</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -66846,7 +66846,7 @@
         <v>45392</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -66903,7 +66903,7 @@
         <v>44335</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -66960,7 +66960,7 @@
         <v>44873</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67037,7 +67037,7 @@
         <v>44901.54615740741</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67099,7 +67099,7 @@
         <v>44133</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67156,7 +67156,7 @@
         <v>45749.38379629629</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67213,7 +67213,7 @@
         <v>44849.8044212963</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -67270,7 +67270,7 @@
         <v>45560.38056712963</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>44206</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>44764</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -67446,7 +67446,7 @@
         <v>44764</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -67503,7 +67503,7 @@
         <v>44875</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -67560,7 +67560,7 @@
         <v>44972.55690972223</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -67617,7 +67617,7 @@
         <v>44211</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -67674,7 +67674,7 @@
         <v>45469</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -67731,7 +67731,7 @@
         <v>45586.46927083333</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -67788,7 +67788,7 @@
         <v>45555.43584490741</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -67845,7 +67845,7 @@
         <v>45216.3965625</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -67902,7 +67902,7 @@
         <v>45246</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -67959,7 +67959,7 @@
         <v>45289</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68016,7 +68016,7 @@
         <v>45378</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68073,7 +68073,7 @@
         <v>45226</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68130,7 +68130,7 @@
         <v>44148</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68187,7 +68187,7 @@
         <v>45561.61509259259</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -68244,7 +68244,7 @@
         <v>45036</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -68301,7 +68301,7 @@
         <v>45036</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -68358,7 +68358,7 @@
         <v>45603.28460648148</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -68420,7 +68420,7 @@
         <v>45610.36561342593</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -68477,7 +68477,7 @@
         <v>45231</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -68534,7 +68534,7 @@
         <v>44795</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -68596,7 +68596,7 @@
         <v>44488.47928240741</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -68653,7 +68653,7 @@
         <v>45097</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -68710,7 +68710,7 @@
         <v>45226</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -68767,7 +68767,7 @@
         <v>44961</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -68824,7 +68824,7 @@
         <v>44391</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -68881,7 +68881,7 @@
         <v>45107</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -68938,7 +68938,7 @@
         <v>45621</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -68995,7 +68995,7 @@
         <v>45642.63666666667</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -69052,7 +69052,7 @@
         <v>45180.6391087963</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -69114,7 +69114,7 @@
         <v>45607.63211805555</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -69171,7 +69171,7 @@
         <v>44390</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -69228,7 +69228,7 @@
         <v>45602.65599537037</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -69285,7 +69285,7 @@
         <v>45190</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -69342,7 +69342,7 @@
         <v>45050</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -69404,7 +69404,7 @@
         <v>45453.45515046296</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -69461,7 +69461,7 @@
         <v>45056</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -69518,7 +69518,7 @@
         <v>45000</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -69575,7 +69575,7 @@
         <v>45602.57827546296</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -69632,7 +69632,7 @@
         <v>45721.55653935186</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -69689,7 +69689,7 @@
         <v>45189</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>

--- a/Översikt KROKOM.xlsx
+++ b/Översikt KROKOM.xlsx
@@ -567,7 +567,7 @@
         <v>45716</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44522</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45348</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44165</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45384</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>45254</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>45709</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>45637</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45603</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44378</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45478</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45121</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>44323.61518518518</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>44565</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45155</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45646</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>45630</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45453</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44363</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>45219</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>45041</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>45625</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45553</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>45790</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45663</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>45428</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>45644</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>45845</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>45596.5093287037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>44306.52587962963</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44575</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>44326</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44581</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>45792</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45475</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>44780</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>45784.56270833333</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45691</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>44323</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>44475</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>45646</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>45646</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>44231</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>45849.31563657407</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>45551</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45512</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>45534</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>45488.56961805555</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>45639</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>45719.52238425926</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44795</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>45041</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44498</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>45580</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>45527</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>45454</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45219</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>45643</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44118</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>44552</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>45457</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>45181</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>45169</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44308</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>44133</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>44698</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44585</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>45475</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>44500</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45616</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>45316</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45839.68914351852</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>45149</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>45267</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44271</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>44265</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44534</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>44494</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>44326</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45370</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44477</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>45180</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>44834</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44797</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>45474</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>45252</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>45581</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>45832.38581018519</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45755.47527777778</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>44183</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>44515</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>44162</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44452</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>45079</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>45726.46192129629</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>44540</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44557</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45551</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45838.67858796296</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>44150</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>45615.60217592592</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>45874.67765046296</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>45532</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44903</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>44546</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44510.94930555556</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>44728</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>44879</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45621</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>45735</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45632</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>45310</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>45617</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>44895</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44553</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>45624</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45169</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44904</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45527</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45849.42818287037</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>44174</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>45595</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>44966</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>45764</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>44867</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>45313</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>45692</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>44540</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45526</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45656.54600694445</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45511.55719907407</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45636</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45216</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>45271</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45453.63133101852</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>45630</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>45821.44299768518</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>45216.67748842593</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>44757</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>44873</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45372</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>44757</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>44841</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>45233</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>44355</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44161</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>44378</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>44524</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>44316</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>44230</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>44757</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45268</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>44879</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45223</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>45376</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44540</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>45793.4189699074</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45595</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>45554</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45348</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>44209</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45804.60005787037</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>45805</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>45647.6565625</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>45643.53393518519</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>45656.59703703703</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>44279</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>44099</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>44154</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>44090</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>44512</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44445</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44512</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>44445</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>44728</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>44207</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>44797</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>44742</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>44377</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45407</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45180</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>45635</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>45243</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>44308</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45123</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>45622</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>44630</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45153</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44603</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45595</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45595</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45838</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>45079</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45838.67815972222</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>45271</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45595</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45839.60460648148</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44568</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>45841.52454861111</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45847.51078703703</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45020</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>45700</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45645.67945601852</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>44683</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45685.78776620371</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45098</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>45819.65796296296</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45862.43403935185</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45862.4257175926</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45695.42197916667</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>45826.45174768518</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>45686.27208333334</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45609</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45750.42127314815</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45595</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>45609</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44540</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45702.47149305556</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>44568</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>44075</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>44568</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45736.42743055556</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44313</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44113</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44102</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44103</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44214</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44371</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>44748.94689814815</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44407</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44473.44813657407</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44473.508125</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44256</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44183</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>44175</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>44679</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44449</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44665</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44173</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>44445</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>44494</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>44610</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44788</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44376.87497685185</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>44377.44767361111</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>44285</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44133</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>44263</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>44183</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>44183</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>44524</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44370</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>44591</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>44123</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>44714.438125</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>44162</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>44057</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>44090</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44141</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44255</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44577.47756944445</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44287</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44533</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44749</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44126.94510416667</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>44831.37650462963</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44200</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44172</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>44512.94539351852</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44369.41452546296</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44271.43831018519</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44312</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>44502.94153935185</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>44306</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44788</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44502</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>44207</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>44851.57131944445</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>44209</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>44209</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>44243</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>44473</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44106</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>44466.53040509259</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>44300</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>44539</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>44495</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>44495</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>44277.59521990741</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44062</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>44512</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>44172</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>44337</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>44214</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>44693.41668981482</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>44502.94140046297</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>44139</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>44473.53681712963</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26040,7 +26040,7 @@
         <v>44077</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>44470</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>44858</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>44153</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26268,7 +26268,7 @@
         <v>44714</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>44151</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44377</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>44728.94420138889</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>44459</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>44382.92065972222</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44526</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>44095</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44358.63585648148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>44214</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>44524</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44820</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>44076</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44113</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>44123</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>44610</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>44123</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>44473.53013888889</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>44459</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>44337</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>44848</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>44875.41104166667</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>44697.94231481481</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>44123</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>44519.63436342592</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>44727</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>44470</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         <v>44169</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>44214</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>44279</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44705</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44307.42378472222</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>44284</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>44209</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>44468</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>44447</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44118.98730324074</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44470.39989583333</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>45452.56446759259</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>44285</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>45679.70027777777</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>45600.58076388889</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>45749</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>45720</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>45035</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>45758.58943287037</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44848</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>45412.51260416667</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45670</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>44400.37204861111</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45714.34859953704</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45719.32584490741</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45560.69164351852</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>45370.94969907407</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>44908</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>45203.46523148148</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>45245</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>45586.53618055556</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>45459.55150462963</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>45698.39486111111</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45607</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>45698.45653935185</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>45362</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>45485</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>44825</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45370</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45695</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45665.57373842593</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45251.65152777778</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>45572.45601851852</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>44803</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>45770.64677083334</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45615.61121527778</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45608.61606481481</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45674</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>45713.60719907407</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45721.54896990741</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45721</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45203</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>45342</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45700.37127314815</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45700.37481481482</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>45593.38568287037</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>45672.53806712963</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>45386</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>45189.60987268519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45362</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45414.486875</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45552.57210648148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>45195</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>45649.4634375</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45531.62141203704</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>45643.65354166667</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45411</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>45747.47025462963</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44830</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>45630.47099537037</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>45055</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44316</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45310</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>45253</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>44875</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45160.66704861111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>45547.42732638889</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>45763.46918981482</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>44834.95019675926</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>45082</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>45740</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44874</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45705.33446759259</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -32698,7 +32698,7 @@
         <v>44887</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45602</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>45751.37320601852</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>44901.59349537037</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45554</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>44140</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>45471.63390046296</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>45239.9681712963</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>45474.69155092593</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44389</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45532.58101851852</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>45243.37567129629</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -33402,7 +33402,7 @@
         <v>45758.66180555556</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45758.67065972222</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>45055</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -33573,7 +33573,7 @@
         <v>45398</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>45369</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -33687,7 +33687,7 @@
         <v>45457.55922453704</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45265.52887731481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>45748.3822337963</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45692.64298611111</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>45454.57899305555</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45250</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>45649.45143518518</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45457.35388888889</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45467</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45452.55271990741</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45226</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>45726.37850694444</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>45411.4666087963</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44456</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>45209</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>45746</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45744</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45740.60405092593</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>45371</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>45392</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>45414.96341435185</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>45751.6877662037</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>45751.28243055556</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>45090</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>45554.59538194445</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>45740.60347222222</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>45726.56341435185</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>45726.5827199074</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45726.61520833334</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -35410,7 +35410,7 @@
         <v>45096</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>45580.36991898148</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45474.69074074074</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45377</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>45560.45841435185</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -35705,7 +35705,7 @@
         <v>45118</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45597.49638888889</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>45260</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>45279</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>44540</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45278.65582175926</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44866</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45467</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>45117</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>45407</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>45432.36971064815</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>45446.68733796296</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -36394,7 +36394,7 @@
         <v>45686.35247685185</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>44911</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>45748.36445601852</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45748.37173611111</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -36627,7 +36627,7 @@
         <v>45371</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>44965</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>45099.37211805556</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -36803,7 +36803,7 @@
         <v>45266</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>45245</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>45691.61996527778</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>45042</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>45721.4546412037</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>45254</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>45446.47634259259</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>45525</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45112</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>45133</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>44061</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>44539</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45309.94650462963</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>45560</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>45484</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>45527.39858796296</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>45245.5478125</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45586</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45478.60708333334</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45373</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45090</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>44873</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45182</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>44970</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45484</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>45477.35225694445</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38320,7 +38320,7 @@
         <v>45393</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -38377,7 +38377,7 @@
         <v>45532.48732638889</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -38434,7 +38434,7 @@
         <v>44550</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45415.45006944444</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>44522.46662037037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>44974</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -38667,7 +38667,7 @@
         <v>45760.81083333334</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -38724,7 +38724,7 @@
         <v>45601.33743055556</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>44922</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -38843,7 +38843,7 @@
         <v>44483.42253472222</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>45244</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -38957,7 +38957,7 @@
         <v>45324</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39014,7 +39014,7 @@
         <v>45764.55260416667</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>45217</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>45474</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>45282</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>45478.42063657408</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>45165.69965277778</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>44516</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>45203</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>45300</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -39527,7 +39527,7 @@
         <v>45152</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -39589,7 +39589,7 @@
         <v>45686.32671296296</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45511.95109953704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45701</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>44466.56642361111</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>44498</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>44504</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>45635.67949074074</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>45608.43930555556</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40050,7 +40050,7 @@
         <v>45715</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>45776</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40169,7 +40169,7 @@
         <v>45693</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>44939</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>45777</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -40345,7 +40345,7 @@
         <v>45712</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>45551.34414351852</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>45777</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>45777</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>45779.56659722222</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>45779.63834490741</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45779.57626157408</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45779.65980324074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>45477.32728009259</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45721.45563657407</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45779.42630787037</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45779.5674074074</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45696</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41111,7 +41111,7 @@
         <v>45488.94857638889</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>45608.86341435185</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>45783.44828703703</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>45783</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -41344,7 +41344,7 @@
         <v>45475</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45112</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45418.94616898148</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -41515,7 +41515,7 @@
         <v>45783</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -41572,7 +41572,7 @@
         <v>45783.45121527778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>45783.43409722222</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>45713.37111111111</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45688.38393518519</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>44600.37212962963</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>45740</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>44362</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>45538.68200231482</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         <v>45117</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>45579.66459490741</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42147,7 +42147,7 @@
         <v>45392</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>44480</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>44592</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -42323,7 +42323,7 @@
         <v>44893</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -42380,7 +42380,7 @@
         <v>45406.05033564815</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -42442,7 +42442,7 @@
         <v>45594.463125</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -42499,7 +42499,7 @@
         <v>45786.35219907408</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -42556,7 +42556,7 @@
         <v>45119</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>44904</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -42670,7 +42670,7 @@
         <v>45786</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>45180</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>44188</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>45121</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>45706</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45785.52112268518</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>45785.5403125</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>45666.65987268519</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
         <v>45496.41289351852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43198,7 +43198,7 @@
         <v>45618.53126157408</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45618.53633101852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>45601.38071759259</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45785.54635416667</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45554.59447916667</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45786</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>45551.47325231481</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45700.30092592593</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45786.64972222222</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45786.65702546296</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45491.44971064815</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>45785</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45786.66140046297</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45715</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>45550.66542824074</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45109.44534722222</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
         <v>44214</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45785.51092592593</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>45467</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -44311,7 +44311,7 @@
         <v>44498</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>45561.61515046296</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>44938.93989583333</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>45700.56194444445</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>45750.60577546297</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -44601,7 +44601,7 @@
         <v>45602.38614583333</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -44658,7 +44658,7 @@
         <v>45602.39862268518</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>45602.42878472222</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>44971</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>45789.58238425926</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45789.61349537037</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45243.33297453704</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45005,7 +45005,7 @@
         <v>45145.95255787037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45067,7 +45067,7 @@
         <v>45572</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>45583.52885416667</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45687.48931712963</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>45566.51501157408</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>44510.9491087963</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>44207</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45706.59251157408</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>45632</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45635.39820601852</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -45590,7 +45590,7 @@
         <v>44582</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>45721.66456018519</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -45704,7 +45704,7 @@
         <v>45484</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>45232.46239583333</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45552.67611111111</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -45880,7 +45880,7 @@
         <v>45614.63575231482</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>45660.49618055556</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -45994,7 +45994,7 @@
         <v>45834.34737268519</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45833.63579861111</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>45833.49052083334</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46170,7 +46170,7 @@
         <v>45833.49057870371</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>44887</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>44818</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45195</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45631.61869212963</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>44631</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45695.60015046296</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>44970</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45056</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>45056</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45713</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45166</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>44391</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45476</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>44596</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>45534.57745370371</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>45791</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>45603.44815972223</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45791.3162037037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>45643.64706018518</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>44557</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>45714.69212962963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>44658</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>45588</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45796.52836805556</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>45588</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>44186</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45378</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>45835.42712962963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45707.55246527777</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>45720.60774305555</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45615.61302083333</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48044,7 +48044,7 @@
         <v>45686.33310185185</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48106,7 +48106,7 @@
         <v>45560.6599537037</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45793.45204861111</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45748</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>45698.40146990741</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -48339,7 +48339,7 @@
         <v>45343.95162037037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45699</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>44988.94056712963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>44141</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45198.42734953704</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -48644,7 +48644,7 @@
         <v>45796.59857638889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>45706.55993055556</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -48758,7 +48758,7 @@
         <v>45836.34413194445</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>44686</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45573.54893518519</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45432.54027777778</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45182</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45182</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45608</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45695.57171296296</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45723.50841435185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45225.60212962963</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45840.40717592592</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -49400,7 +49400,7 @@
         <v>45839.61594907408</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>45615.59521990741</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         <v>45839.61582175926</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45840.58494212963</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45204</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45401.59810185185</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>44741</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45695.4046875</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -49871,7 +49871,7 @@
         <v>45695.42418981482</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>45839.61541666667</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45460.44076388889</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>45839.72320601852</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45695.45013888889</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50171,7 +50171,7 @@
         <v>45707.33935185185</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>45565.32449074074</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         <v>45772.62052083333</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -50347,7 +50347,7 @@
         <v>44151</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -50404,7 +50404,7 @@
         <v>45246</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -50461,7 +50461,7 @@
         <v>44788</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -50518,7 +50518,7 @@
         <v>45554.59550925926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -50575,7 +50575,7 @@
         <v>45798.63611111111</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45656</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>45798.63596064815</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -50761,7 +50761,7 @@
         <v>45746.79134259259</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -50818,7 +50818,7 @@
         <v>45839.61563657408</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -50880,7 +50880,7 @@
         <v>45716.55237268518</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>44601.35342592592</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -50999,7 +50999,7 @@
         <v>45800.57129629629</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45800.57461805556</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>45800</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45667.57217592592</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45800.37061342593</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45699.66576388889</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -51346,7 +51346,7 @@
         <v>45190</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -51403,7 +51403,7 @@
         <v>45686</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -51460,7 +51460,7 @@
         <v>45216</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45316</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -51574,7 +51574,7 @@
         <v>45772.58283564815</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45772.59200231481</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -51688,7 +51688,7 @@
         <v>44732</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>45841.46925925926</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -51807,7 +51807,7 @@
         <v>45800.56810185185</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -51864,7 +51864,7 @@
         <v>45547.42736111111</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -51921,7 +51921,7 @@
         <v>45791</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>45841.67834490741</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45176</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52102,7 +52102,7 @@
         <v>45694.64416666667</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52164,7 +52164,7 @@
         <v>45842.39587962963</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45842.40013888889</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45117</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -52350,7 +52350,7 @@
         <v>45123.61459490741</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -52412,7 +52412,7 @@
         <v>45800.65177083333</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -52469,7 +52469,7 @@
         <v>45800.64319444444</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -52526,7 +52526,7 @@
         <v>45620.67667824074</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -52583,7 +52583,7 @@
         <v>45231</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -52645,7 +52645,7 @@
         <v>45600.49616898148</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -52702,7 +52702,7 @@
         <v>45662</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -52759,7 +52759,7 @@
         <v>45842.6099537037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -52816,7 +52816,7 @@
         <v>45684.62510416667</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -52878,7 +52878,7 @@
         <v>45762.60907407408</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -52940,7 +52940,7 @@
         <v>45746</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53002,7 +53002,7 @@
         <v>45117</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>45800</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53121,7 +53121,7 @@
         <v>45803</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53178,7 +53178,7 @@
         <v>45401.59133101852</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53235,7 +53235,7 @@
         <v>45693.67361111111</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>45803.6837962963</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -53354,7 +53354,7 @@
         <v>45638.81385416666</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -53411,7 +53411,7 @@
         <v>45574.43403935185</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>45704.71069444445</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         <v>45618.54398148148</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         <v>45692.58106481482</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>45097</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>45803.69828703703</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45700.27895833334</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>45623.48571759259</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -53882,7 +53882,7 @@
         <v>45701.60901620371</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -53939,7 +53939,7 @@
         <v>45694.43806712963</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>45630</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>45848.48070601852</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45687</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>45676</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54229,7 +54229,7 @@
         <v>45847.46962962963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -54286,7 +54286,7 @@
         <v>45761.50909722222</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -54343,7 +54343,7 @@
         <v>45261</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -54400,7 +54400,7 @@
         <v>45848.60371527778</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -54457,7 +54457,7 @@
         <v>45805.47425925926</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -54514,7 +54514,7 @@
         <v>45721</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -54571,7 +54571,7 @@
         <v>44203</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         <v>45841.43987268519</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45216</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -54742,7 +54742,7 @@
         <v>44140</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -54799,7 +54799,7 @@
         <v>45847.51106481482</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -54856,7 +54856,7 @@
         <v>45805.54185185185</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -54913,7 +54913,7 @@
         <v>45721.5113425926</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -54970,7 +54970,7 @@
         <v>45705</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55027,7 +55027,7 @@
         <v>45614.63697916667</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55084,7 +55084,7 @@
         <v>44715.48863425926</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55146,7 +55146,7 @@
         <v>45510.58033564815</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45751.3734837963</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45751.57877314815</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -55322,7 +55322,7 @@
         <v>45457.38799768518</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -55379,7 +55379,7 @@
         <v>45733</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>45408</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -55493,7 +55493,7 @@
         <v>45805</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -55550,7 +55550,7 @@
         <v>45693.48239583334</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -55607,7 +55607,7 @@
         <v>44349</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -55669,7 +55669,7 @@
         <v>45698.4930787037</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>44273</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -55783,7 +55783,7 @@
         <v>45692</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -55845,7 +55845,7 @@
         <v>45695.61160879629</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -55907,7 +55907,7 @@
         <v>44154</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -55964,7 +55964,7 @@
         <v>45602</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56021,7 +56021,7 @@
         <v>45847.65717592592</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56083,7 +56083,7 @@
         <v>45847.46462962963</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56140,7 +56140,7 @@
         <v>45698.57129629629</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56197,7 +56197,7 @@
         <v>45686.39777777778</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56259,7 +56259,7 @@
         <v>45849.4525462963</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -56316,7 +56316,7 @@
         <v>45238</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -56373,7 +56373,7 @@
         <v>45849.3859837963</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -56435,7 +56435,7 @@
         <v>44524</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -56492,7 +56492,7 @@
         <v>45748.59744212963</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -56549,7 +56549,7 @@
         <v>45607</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -56606,7 +56606,7 @@
         <v>45614.63606481482</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -56663,7 +56663,7 @@
         <v>45614.63701388889</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -56720,7 +56720,7 @@
         <v>44285</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -56777,7 +56777,7 @@
         <v>45848</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -56834,7 +56834,7 @@
         <v>45807.58930555556</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -56891,7 +56891,7 @@
         <v>44179</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -56948,7 +56948,7 @@
         <v>45720.40268518519</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57005,7 +57005,7 @@
         <v>45810.32105324074</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57062,7 +57062,7 @@
         <v>45140</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57119,7 +57119,7 @@
         <v>45090</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57176,7 +57176,7 @@
         <v>45466.62116898148</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57233,7 +57233,7 @@
         <v>45639</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -57290,7 +57290,7 @@
         <v>45764</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -57347,7 +57347,7 @@
         <v>45642.6366087963</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -57404,7 +57404,7 @@
         <v>44334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -57461,7 +57461,7 @@
         <v>45696.3440162037</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -57518,7 +57518,7 @@
         <v>45807.56728009259</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -57575,7 +57575,7 @@
         <v>45118.94061342593</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -57632,7 +57632,7 @@
         <v>45638.81375</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -57689,7 +57689,7 @@
         <v>45708</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -57751,7 +57751,7 @@
         <v>45693</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -57808,7 +57808,7 @@
         <v>45713.36836805556</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -57870,7 +57870,7 @@
         <v>45168</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -57927,7 +57927,7 @@
         <v>44792.27644675926</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -57984,7 +57984,7 @@
         <v>44750</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58041,7 +58041,7 @@
         <v>44721.39003472222</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58103,7 +58103,7 @@
         <v>45474.3981712963</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58160,7 +58160,7 @@
         <v>45737.36873842592</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58217,7 +58217,7 @@
         <v>44331</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -58274,7 +58274,7 @@
         <v>44726</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -58331,7 +58331,7 @@
         <v>45692</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -58393,7 +58393,7 @@
         <v>45811.54760416667</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -58450,7 +58450,7 @@
         <v>45853.6156712963</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -58512,7 +58512,7 @@
         <v>45695.47791666666</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -58569,7 +58569,7 @@
         <v>45854.66518518519</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -58626,7 +58626,7 @@
         <v>45810.31376157407</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -58683,7 +58683,7 @@
         <v>45812.32266203704</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -58740,7 +58740,7 @@
         <v>44855</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -58797,7 +58797,7 @@
         <v>44855</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -58854,7 +58854,7 @@
         <v>45694.34268518518</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -58916,7 +58916,7 @@
         <v>44880</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -58973,7 +58973,7 @@
         <v>45811.67769675926</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59030,7 +59030,7 @@
         <v>45204.40770833333</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59087,7 +59087,7 @@
         <v>45467</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59144,7 +59144,7 @@
         <v>44741</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59201,7 +59201,7 @@
         <v>45811.69912037037</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -59258,7 +59258,7 @@
         <v>45670</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -59315,7 +59315,7 @@
         <v>45854.65378472222</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -59372,7 +59372,7 @@
         <v>45614.65925925926</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -59429,7 +59429,7 @@
         <v>45519.60965277778</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -59486,7 +59486,7 @@
         <v>45750.42650462963</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -59543,7 +59543,7 @@
         <v>45813.44443287037</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -59600,7 +59600,7 @@
         <v>44726</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -59657,7 +59657,7 @@
         <v>45813.46969907408</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -59714,7 +59714,7 @@
         <v>45814</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -59771,7 +59771,7 @@
         <v>45814</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -59828,7 +59828,7 @@
         <v>45300</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -59885,7 +59885,7 @@
         <v>45713.36561342593</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -59947,7 +59947,7 @@
         <v>45713.38028935185</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60009,7 +60009,7 @@
         <v>45700.6833912037</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60066,7 +60066,7 @@
         <v>45744.59894675926</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60128,7 +60128,7 @@
         <v>45279</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60185,7 +60185,7 @@
         <v>45635</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -60242,7 +60242,7 @@
         <v>45238</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -60304,7 +60304,7 @@
         <v>45813.68361111111</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -60361,7 +60361,7 @@
         <v>45257</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -60418,7 +60418,7 @@
         <v>45247</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -60475,7 +60475,7 @@
         <v>45785.67431712963</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -60537,7 +60537,7 @@
         <v>45713.59623842593</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -60599,7 +60599,7 @@
         <v>45709</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>45855.61193287037</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -60718,7 +60718,7 @@
         <v>45818.36246527778</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -60780,7 +60780,7 @@
         <v>44757</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -60842,7 +60842,7 @@
         <v>45818.3293287037</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -60904,7 +60904,7 @@
         <v>45671.59114583334</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>45817.56761574074</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61018,7 +61018,7 @@
         <v>44711</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61080,7 +61080,7 @@
         <v>44377</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61137,7 +61137,7 @@
         <v>45815.50844907408</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61194,7 +61194,7 @@
         <v>45818.34474537037</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -61256,7 +61256,7 @@
         <v>45713.59163194444</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -61318,7 +61318,7 @@
         <v>45369</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>45274</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -61432,7 +61432,7 @@
         <v>45818.34473379629</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -61494,7 +61494,7 @@
         <v>44370</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -61551,7 +61551,7 @@
         <v>44427</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -61608,7 +61608,7 @@
         <v>45818.33532407408</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -61670,7 +61670,7 @@
         <v>45818.34833333334</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -61732,7 +61732,7 @@
         <v>45818.37056712963</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -61794,7 +61794,7 @@
         <v>45862.34668981482</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -61856,7 +61856,7 @@
         <v>45820</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -61913,7 +61913,7 @@
         <v>45173</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -61975,7 +61975,7 @@
         <v>45860</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62032,7 +62032,7 @@
         <v>45820</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62089,7 +62089,7 @@
         <v>45694.65905092593</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62146,7 +62146,7 @@
         <v>45203.44248842593</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62203,7 +62203,7 @@
         <v>45165.70483796296</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -62260,7 +62260,7 @@
         <v>45713.59952546296</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -62322,7 +62322,7 @@
         <v>45820.36233796296</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>45820.36512731481</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -62436,7 +62436,7 @@
         <v>45820.47200231482</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -62498,7 +62498,7 @@
         <v>45820</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -62555,7 +62555,7 @@
         <v>45653.57240740741</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -62617,7 +62617,7 @@
         <v>45862.42901620371</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -62674,7 +62674,7 @@
         <v>45820.36498842593</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -62731,7 +62731,7 @@
         <v>45820.36506944444</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -62788,7 +62788,7 @@
         <v>45861.6841087963</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -62850,7 +62850,7 @@
         <v>45448.67574074074</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -62912,7 +62912,7 @@
         <v>45821.39026620371</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -62969,7 +62969,7 @@
         <v>45692.60364583333</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63026,7 +63026,7 @@
         <v>45863.45778935185</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63083,7 +63083,7 @@
         <v>45708</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63145,7 +63145,7 @@
         <v>45863</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63202,7 +63202,7 @@
         <v>44847</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -63259,7 +63259,7 @@
         <v>45701</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -63321,7 +63321,7 @@
         <v>44847</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -63378,7 +63378,7 @@
         <v>44858</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -63435,7 +63435,7 @@
         <v>45713.59741898148</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -63497,7 +63497,7 @@
         <v>45863.58127314815</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -63559,7 +63559,7 @@
         <v>45180</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -63621,7 +63621,7 @@
         <v>45863.59111111111</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -63683,7 +63683,7 @@
         <v>45763.44112268519</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45764.47059027778</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -63797,7 +63797,7 @@
         <v>45750.6447800926</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -63859,7 +63859,7 @@
         <v>45757.56491898148</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -63916,7 +63916,7 @@
         <v>45867.41707175926</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -63973,7 +63973,7 @@
         <v>45867.46560185185</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64030,7 +64030,7 @@
         <v>45826.4705787037</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45022</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>44757</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64211,7 +64211,7 @@
         <v>45453</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64273,7 +64273,7 @@
         <v>45453.95237268518</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -64335,7 +64335,7 @@
         <v>45499.48672453704</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -64392,7 +64392,7 @@
         <v>45719</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -64449,7 +64449,7 @@
         <v>45687</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -64506,7 +64506,7 @@
         <v>45748.57269675926</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -64563,7 +64563,7 @@
         <v>45869.34439814815</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -64625,7 +64625,7 @@
         <v>45649.38149305555</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -64682,7 +64682,7 @@
         <v>45764.40834490741</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
         <v>45719.37307870371</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>45870</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -64858,7 +64858,7 @@
         <v>45827.34488425926</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -64920,7 +64920,7 @@
         <v>45483</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -64977,7 +64977,7 @@
         <v>44379.59675925926</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65034,7 +65034,7 @@
         <v>45257</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65091,7 +65091,7 @@
         <v>45348</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65148,7 +65148,7 @@
         <v>45832</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65205,7 +65205,7 @@
         <v>45832.34630787037</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65267,7 +65267,7 @@
         <v>45565.33152777778</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -65324,7 +65324,7 @@
         <v>45832.53935185185</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -65386,7 +65386,7 @@
         <v>45139</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>45832.53225694445</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>45572</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -65572,7 +65572,7 @@
         <v>44544.49326388889</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -65629,7 +65629,7 @@
         <v>45601</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -65686,7 +65686,7 @@
         <v>45758</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -65743,7 +65743,7 @@
         <v>45875.51046296296</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -65800,7 +65800,7 @@
         <v>44732</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -65857,7 +65857,7 @@
         <v>45833.34490740741</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -65919,7 +65919,7 @@
         <v>44865</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -65976,7 +65976,7 @@
         <v>45833.36050925926</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66033,7 +66033,7 @@
         <v>45833.36083333333</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66090,7 +66090,7 @@
         <v>45834.34726851852</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66152,7 +66152,7 @@
         <v>44228</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66209,7 +66209,7 @@
         <v>45834.61517361111</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -66271,7 +66271,7 @@
         <v>45876</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -66328,7 +66328,7 @@
         <v>45876</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -66385,7 +66385,7 @@
         <v>45876</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -66442,7 +66442,7 @@
         <v>45833.36111111111</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -66499,7 +66499,7 @@
         <v>45634.7925</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -66556,7 +66556,7 @@
         <v>45634.79854166666</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -66613,7 +66613,7 @@
         <v>45608.61923611111</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -66670,7 +66670,7 @@
         <v>45600.433125</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -66732,7 +66732,7 @@
         <v>45701.57363425926</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -66789,7 +66789,7 @@
         <v>45392.95844907407</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -66846,7 +66846,7 @@
         <v>45392</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -66903,7 +66903,7 @@
         <v>44335</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -66960,7 +66960,7 @@
         <v>44873</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67037,7 +67037,7 @@
         <v>44901.54615740741</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67099,7 +67099,7 @@
         <v>44133</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67156,7 +67156,7 @@
         <v>45749.38379629629</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67213,7 +67213,7 @@
         <v>44849.8044212963</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -67270,7 +67270,7 @@
         <v>45560.38056712963</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>44206</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>44764</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -67446,7 +67446,7 @@
         <v>44764</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -67503,7 +67503,7 @@
         <v>44875</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -67560,7 +67560,7 @@
         <v>44972.55690972223</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -67617,7 +67617,7 @@
         <v>44211</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -67674,7 +67674,7 @@
         <v>45469</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -67731,7 +67731,7 @@
         <v>45586.46927083333</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -67788,7 +67788,7 @@
         <v>45555.43584490741</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -67845,7 +67845,7 @@
         <v>45216.3965625</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -67902,7 +67902,7 @@
         <v>45246</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -67959,7 +67959,7 @@
         <v>45289</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68016,7 +68016,7 @@
         <v>45378</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68073,7 +68073,7 @@
         <v>45226</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68130,7 +68130,7 @@
         <v>44148</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68187,7 +68187,7 @@
         <v>45561.61509259259</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -68244,7 +68244,7 @@
         <v>45036</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -68301,7 +68301,7 @@
         <v>45036</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -68358,7 +68358,7 @@
         <v>45603.28460648148</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -68420,7 +68420,7 @@
         <v>45610.36561342593</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -68477,7 +68477,7 @@
         <v>45231</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -68534,7 +68534,7 @@
         <v>44795</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -68596,7 +68596,7 @@
         <v>44488.47928240741</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -68653,7 +68653,7 @@
         <v>45097</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -68710,7 +68710,7 @@
         <v>45226</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -68767,7 +68767,7 @@
         <v>44961</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -68824,7 +68824,7 @@
         <v>44391</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -68881,7 +68881,7 @@
         <v>45107</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -68938,7 +68938,7 @@
         <v>45621</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -68995,7 +68995,7 @@
         <v>45642.63666666667</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -69052,7 +69052,7 @@
         <v>45180.6391087963</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -69114,7 +69114,7 @@
         <v>45607.63211805555</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -69171,7 +69171,7 @@
         <v>44390</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -69228,7 +69228,7 @@
         <v>45602.65599537037</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -69285,7 +69285,7 @@
         <v>45190</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -69342,7 +69342,7 @@
         <v>45050</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -69404,7 +69404,7 @@
         <v>45453.45515046296</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -69461,7 +69461,7 @@
         <v>45056</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -69518,7 +69518,7 @@
         <v>45000</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -69575,7 +69575,7 @@
         <v>45602.57827546296</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -69632,7 +69632,7 @@
         <v>45721.55653935186</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -69689,7 +69689,7 @@
         <v>45189</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>

--- a/Översikt KROKOM.xlsx
+++ b/Översikt KROKOM.xlsx
@@ -567,7 +567,7 @@
         <v>45716</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44522</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45348</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44165</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45384</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>45254</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>45709</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>45637</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45603</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44378</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45478</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45845</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>44323</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>45121</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45155</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45646</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>44565</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>44363</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>45219</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>45453</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45630</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>45625</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45041</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>45790</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>45663</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>45553</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>45428</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>45644</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>45596.5093287037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>44306.52587962963</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44575</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>45792</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>44326</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>44581</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>45475</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>44780</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>45784.56270833333</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>44323</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45691</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>44475</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>45849.31563657407</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45646</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45646</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>45551</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>44231</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>45488.56961805555</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>45639</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45512</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45534</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45719.52238425926</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44795</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>45041</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45580</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45527</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>45454</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>45643</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44118</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>45219</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>44498</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>44552</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>45181</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>45169</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45457</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>44308</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44133</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>44585</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44698</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>44500</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>45316</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>45616</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>45839.68914351852</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>45267</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>45149</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45475</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>44271</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>44265</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>44534</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44494</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>44326</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>45370</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>45180</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>44834</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44477</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>45581</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>45252</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>45755.47527777778</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>45832.38581018519</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>44797</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>45474</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>44183</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>44515</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44557</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>45551</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>44150</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>45874.67765046296</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>45838.67858796296</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>45532</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>45615</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>44903</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44546</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>45726.46192129629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>44452</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45079</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>44540</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44162</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>44510.94930555556</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>44728</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>45624</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>45169</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>45527</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>45849.42818287037</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>44895</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>44553</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45595</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>44966</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>45764</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>44904</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>44174</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>45621</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>44879</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>45735</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45632</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45310</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45617</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>45526</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>45656.54600694445</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>45511.55719907407</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45271</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>45453.63133101852</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45216</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>44540</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45821.44299768518</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45372</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>44757</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45636</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>44841</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>45630</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>45233</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>44867</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>45216.67748842593</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>44757</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>44873</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>45313</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>45692</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>44355</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>44161</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>44524</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>44316</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>44230</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>44757</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>44378</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45268</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45376</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45793.4189699074</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45595</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>45804.60005787037</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>45805</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>45554</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>44209</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>44540</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>45877.67787037037</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45869</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45348</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>44279</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45647.6565625</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>45643.53393518519</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45656.59703703703</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>44879</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>45223</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>44099</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44154</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44090</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44512</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>44445</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>44512</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>44445</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44728</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17682,7 +17682,7 @@
         <v>44207</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44797</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>44742</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>44377</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>45123</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45622</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44603</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45595</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45595</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>45079</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>45271</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45595</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45847.46962962963</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45847.51078703703</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44568</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45645.67945601852</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45700</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44683</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>44630</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45153</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45819.65796296296</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45862.43403935185</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45862.4257175926</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>45826.45174768518</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45609</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45595</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45609</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45838.67815972222</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>45838</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45839.60460648148</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45702.47149305556</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>45841.52454861111</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>44568</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>44075</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>44568</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45020</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>45685.78776620371</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45098</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>45736.42743055556</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>45695.42197916667</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45686.27208333334</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>45750.42127314815</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>44540</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45407</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>45635</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45243</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>45180</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>44308</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45467</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>44313</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>44113</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>44103</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>44102</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>44214</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>44371</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>44748.94689814815</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44407</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44473.44813657407</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44473.508125</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44256</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44183</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44175</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44679</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>44665</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>44449</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>44173</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>44445</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44494</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>44788</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>44610</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>44376.87497685185</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>44377.44767361111</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44285</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44133</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44263</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44183</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44183</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44524</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44370</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>44591</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44123</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44714.438125</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44162</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44090</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44141</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44255</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44577.47756944445</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44287</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44533</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44749</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44126.94510416667</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>44831.37650462963</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>44512.94539351852</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>44200</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44172</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>44369.41452546296</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>44271.43831018519</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>44502.94153935185</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>44312</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>44306</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>44788</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>44502</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>44207</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>44851.57131944445</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>44209</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>44209</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44243</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44473</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44106</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44466.53040509259</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>44300</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>44539</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>44495</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>44495</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>44277.59521990741</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>44062</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44512</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>44172</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>44337</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>44214</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>44502.94140046297</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44693.41668981482</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44473.53681712963</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44714</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>44377</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>44459</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>44382.92065972222</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>44095</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>44728.94420138889</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>44358.63585648148</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44526</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44214</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>44524</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>44820</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>44076</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>44113</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44123</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>44610</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>44123</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>44473.53013888889</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44459</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>44337</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>44848</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>44875.41104166667</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44123</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44697.94231481481</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44519.63436342592</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>44727</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>44470</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>44214</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>44169</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>44279</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>44705</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>44209</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44284</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>44118.98730324074</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44307.42378472222</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44447</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>44468</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44470.39989583333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44285</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44848</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>44400.37204861111</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>44139</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44077</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44470</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45749</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>45720</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>44153</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -28948,7 +28948,7 @@
         <v>45035</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>44151</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29062,7 +29062,7 @@
         <v>45412.51260416667</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>45714.34859953704</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>45719.32584490741</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>45370.94969907407</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45531.62141203704</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>45254</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44858</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45411</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45747.47025462963</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45203.46523148148</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>44830</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45112</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         <v>44316</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -29848,7 +29848,7 @@
         <v>45133</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>44061</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>45253</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>44539</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>45560</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45698.39486111111</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>45245.5478125</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>44875</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>45362</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45373</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30428,7 +30428,7 @@
         <v>44834.95019675926</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -30490,7 +30490,7 @@
         <v>44825</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>45082</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45182</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>45370</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>45740</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>45415.45006944444</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45393</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>45760.81083333334</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45251.65152777778</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>44874</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31065,7 +31065,7 @@
         <v>45601.33743055556</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>45572.45601851852</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45244</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>44803</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45324</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45764.55260416667</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>44550</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45217</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44974</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>45713.60719907407</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>45165.69965277778</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>44901.59349537037</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45554</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>45203</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>45300</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>45342</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>45686.32671296296</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45471.63390046296</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45701</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45239.9681712963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>45700.37127314815</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>45700.37481481482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44483.42253472222</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>45474.69155092593</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>44389</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45386</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45362</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45414.486875</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>45243.37567129629</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>45552.57210648148</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45398</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45474</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45282</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45195</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>45715</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>45776</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>45478.42063657408</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>44516</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>45693</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45777</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>45712</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45152</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>45777</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>45777</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -33648,7 +33648,7 @@
         <v>45779.56659722222</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45779.63834490741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>44504</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>45779.57626157408</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45457.55922453704</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>44939</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>45551.34414351852</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>45265.52887731481</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>45779.65980324074</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>45779.42630787037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34223,7 +34223,7 @@
         <v>45779.5674074074</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>45748.3822337963</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45696</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>45783.44828703703</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         <v>45783</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -34518,7 +34518,7 @@
         <v>45783</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>45608.86341435185</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -34632,7 +34632,7 @@
         <v>45783.45121527778</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>45112</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>45418.94616898148</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>45783.43409722222</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -34860,7 +34860,7 @@
         <v>45713.37111111111</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45688.38393518519</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45454.57899305555</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>45740</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45117</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45579.66459490741</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>45392</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44480</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>45786.35219907408</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45594.463125</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45119</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45786</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>45785.52112268518</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>45785.5403125</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45785.54635416667</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>45180</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>45706</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45786</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45786.64972222222</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45786.65702546296</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36015,7 +36015,7 @@
         <v>45666.65987268519</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>45785</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45786.66140046297</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36186,7 +36186,7 @@
         <v>45715</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>45250</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45785.51092592593</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45467</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45789.58238425926</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45789.61349537037</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>45457.35388888889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>45109.44534722222</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>45226</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>45602.38614583333</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>45602.39862268518</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>45602.42878472222</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>44971</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>45632</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>45243.33297453704</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>45145.95255787037</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>45583.52885416667</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>44510.9491087963</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45834.34737268519</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>45833.63579861111</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>45833.49052083334</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45833.49057870371</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45706.59251157408</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45195</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45631.61869212963</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>45695.60015046296</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>45411.4666087963</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>45635.39820601852</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>45166</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>44391</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>45791</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>44582</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45791.3162037037</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>45721.66456018519</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>45484</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45614.63575231482</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45796.52836805556</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45392</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>45660.49618055556</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>45378</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45414.96341435185</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>44818</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>45686.33310185185</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45793.45204861111</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45713</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         <v>45476</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45698.40146990741</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45603.44815972223</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45643.64706018518</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45796.59857638889</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45706.55993055556</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45608</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45695.57171296296</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>44557</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45714.69212962963</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>44658</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -39468,7 +39468,7 @@
         <v>45588</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>45588</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>45798.63611111111</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>45798.63596064815</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>45800.57129629629</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>45800.57461805556</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>45800</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>45800.37061342593</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>45560.6599537037</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>45800.56810185185</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>45791</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45800.65177083333</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45800.64319444444</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>45684.62510416667</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45746</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45699</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>44988.94056712963</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45800</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>44141</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45803</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>45198.42734953704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>44686</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -40757,7 +40757,7 @@
         <v>45573.54893518519</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>45432.54027777778</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45182</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>45803.6837962963</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45096</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>45580.36991898148</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>45474.69074074074</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45225.60212962963</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>45803.69828703703</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45204</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45848.48070601852</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45687</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45695.4046875</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>45261</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45848.60371527778</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45695.42418981482</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45805.47425925926</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45721</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45847.51106481482</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>45805.54185185185</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45565.32449074074</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>44151</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42031,7 +42031,7 @@
         <v>45751.3734837963</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42088,7 +42088,7 @@
         <v>45751.57877314815</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>45554.59550925926</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42202,7 +42202,7 @@
         <v>45733</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>45805</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45656</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>45746.79134259259</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -42435,7 +42435,7 @@
         <v>45692</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45695.61160879629</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45602</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45716.55237268518</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45278.65582175926</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45847.65717592592</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -42797,7 +42797,7 @@
         <v>45467</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45117</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45847.46462962963</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45432.36971064815</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45446.68733796296</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45667.57217592592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45849.4525462963</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45849.3859837963</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>45699.66576388889</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>45190</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43382,7 +43382,7 @@
         <v>44911</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45686</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -43496,7 +43496,7 @@
         <v>45099.37211805556</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>45547.42736111111</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -43610,7 +43610,7 @@
         <v>45176</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>45848</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>45807.58930555556</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>45694.64416666667</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -43848,7 +43848,7 @@
         <v>45620.67667824074</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>45810.32105324074</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -43962,7 +43962,7 @@
         <v>45231</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>45662</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>45401.59133101852</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44138,7 +44138,7 @@
         <v>45525</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>45693.67361111111</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
         <v>45638.81385416666</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>45309.94650462963</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>45704.71069444445</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45692.58106481482</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45097</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>44873</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -44609,7 +44609,7 @@
         <v>45700.27895833334</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>45623.48571759259</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>44970</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>45807.56728009259</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45701.60901620371</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45118.94061342593</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>45694.43806712963</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45630</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45484</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45676</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45761.50909722222</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45477.35225694445</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>44203</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45216</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>44140</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>45474.3981712963</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>45721.5113425926</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>45737.36873842592</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45705</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>45614.63697916667</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>44715.48863425926</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -45826,7 +45826,7 @@
         <v>45532.48732638889</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>44522.46662037037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>45811.54760416667</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45853.6156712963</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45854.66518518519</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>45810.31376157407</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>45408</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45812.32266203704</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45693.48239583334</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>44922</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>45698.4930787037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>44154</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>45811.67769675926</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -46572,7 +46572,7 @@
         <v>45698.57129629629</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -46629,7 +46629,7 @@
         <v>45686.39777777778</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45811.69912037037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45238</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45854.65378472222</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45813.44443287037</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45748.59744212963</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45813.46969907408</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45814</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45814</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45511.95109953704</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45813.68361111111</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>44466.56642361111</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -47318,7 +47318,7 @@
         <v>44498</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>45635.67949074074</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>45608.43930555556</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45785.67431712963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45709</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>45855.61193287037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -47670,7 +47670,7 @@
         <v>45818.36246527778</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -47732,7 +47732,7 @@
         <v>44179</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>45818.3293287037</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -47851,7 +47851,7 @@
         <v>45720.40268518519</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45477.32728009259</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45817.56761574074</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45721.45563657407</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45815.50844907408</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45488.94857638889</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45475</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45818.34474537037</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45818.34473379629</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -48389,7 +48389,7 @@
         <v>45818.33532407408</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>45818.34833333334</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -48513,7 +48513,7 @@
         <v>45818.37056712963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>44600.37212962963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45693</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>45168</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -48746,7 +48746,7 @@
         <v>44792.27644675926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>44750</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -48860,7 +48860,7 @@
         <v>44721.39003472222</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>44362</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>45538.68200231482</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49036,7 +49036,7 @@
         <v>45862.34668981482</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45820</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>44592</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>44726</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45860</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45695.47791666666</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45820</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -49440,7 +49440,7 @@
         <v>44893</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -49497,7 +49497,7 @@
         <v>45820.36233796296</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45820.36512731481</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45820.47200231482</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -49673,7 +49673,7 @@
         <v>45820</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -49730,7 +49730,7 @@
         <v>44855</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>44855</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -49844,7 +49844,7 @@
         <v>44880</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -49901,7 +49901,7 @@
         <v>45406.05033564815</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -49963,7 +49963,7 @@
         <v>45862.42901620371</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50020,7 +50020,7 @@
         <v>45820.36498842593</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50077,7 +50077,7 @@
         <v>45820.36506944444</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50134,7 +50134,7 @@
         <v>45861.6841087963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50196,7 +50196,7 @@
         <v>44741</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>45821.39026620371</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50310,7 +50310,7 @@
         <v>45750.42650462963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -50367,7 +50367,7 @@
         <v>44726</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -50424,7 +50424,7 @@
         <v>45863.45778935185</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -50481,7 +50481,7 @@
         <v>45863</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -50538,7 +50538,7 @@
         <v>45300</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -50595,7 +50595,7 @@
         <v>44904</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -50652,7 +50652,7 @@
         <v>45863.58127314815</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>45713.36561342593</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -50776,7 +50776,7 @@
         <v>45713.38028935185</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45700.6833912037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45863.59111111111</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45764.47059027778</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45744.59894675926</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45279</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>44188</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45121</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51252,7 +51252,7 @@
         <v>45867.41707175926</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45867.46560185185</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -51366,7 +51366,7 @@
         <v>45826.4705787037</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>45496.41289351852</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>45618.53126157408</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45618.53633101852</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45601.38071759259</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>45238</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -51728,7 +51728,7 @@
         <v>45257</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>45554.59447916667</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45551.47325231481</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45700.30092592593</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -51966,7 +51966,7 @@
         <v>45247</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>45491.44971064815</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52080,7 +52080,7 @@
         <v>45713.59623842593</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52142,7 +52142,7 @@
         <v>45869.34439814815</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52204,7 +52204,7 @@
         <v>45550.66542824074</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52261,7 +52261,7 @@
         <v>44757</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>44214</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45671.59114583334</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>44498</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45870</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45561.61515046296</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>44938.93989583333</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>45827.34488425926</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -52727,7 +52727,7 @@
         <v>44711</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>45700.56194444445</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45750.60577546297</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45369</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>45274</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45572</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         <v>45687.48931712963</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         <v>45566.51501157408</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         <v>44207</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53255,7 +53255,7 @@
         <v>45832</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         <v>45832.34630787037</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -53374,7 +53374,7 @@
         <v>45203.44248842593</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -53431,7 +53431,7 @@
         <v>45832.53935185185</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -53493,7 +53493,7 @@
         <v>45832.53225694445</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -53555,7 +53555,7 @@
         <v>45165.70483796296</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         <v>45448.67574074074</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -53674,7 +53674,7 @@
         <v>45601</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -53731,7 +53731,7 @@
         <v>44847</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -53788,7 +53788,7 @@
         <v>45232.46239583333</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -53845,7 +53845,7 @@
         <v>44847</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -53902,7 +53902,7 @@
         <v>44858</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -53959,7 +53959,7 @@
         <v>45552.67611111111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54016,7 +54016,7 @@
         <v>45875.51046296296</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54073,7 +54073,7 @@
         <v>45833.34490740741</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54135,7 +54135,7 @@
         <v>45833.36050925926</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54192,7 +54192,7 @@
         <v>45833.36083333333</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54249,7 +54249,7 @@
         <v>45180</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54311,7 +54311,7 @@
         <v>45763.44112268519</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -54368,7 +54368,7 @@
         <v>45834.34726851852</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -54430,7 +54430,7 @@
         <v>45750.6447800926</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -54492,7 +54492,7 @@
         <v>45757.56491898148</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -54549,7 +54549,7 @@
         <v>45834.61517361111</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -54611,7 +54611,7 @@
         <v>45876</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -54668,7 +54668,7 @@
         <v>45876</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -54725,7 +54725,7 @@
         <v>45876</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -54782,7 +54782,7 @@
         <v>45833.36111111111</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>45022</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -54896,7 +54896,7 @@
         <v>45257</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -54953,7 +54953,7 @@
         <v>45348</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55010,7 +55010,7 @@
         <v>44887</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55072,7 +55072,7 @@
         <v>45877.46555555556</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55129,7 +55129,7 @@
         <v>45880</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55186,7 +55186,7 @@
         <v>45835.42712962963</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55243,7 +55243,7 @@
         <v>44631</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55300,7 +55300,7 @@
         <v>45565.33152777778</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -55357,7 +55357,7 @@
         <v>45836.34413194445</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -55419,7 +55419,7 @@
         <v>45139</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -55481,7 +55481,7 @@
         <v>45572</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -55543,7 +55543,7 @@
         <v>45877.57403935185</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -55605,7 +55605,7 @@
         <v>44970</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -55662,7 +55662,7 @@
         <v>45056</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -55719,7 +55719,7 @@
         <v>45056</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -55776,7 +55776,7 @@
         <v>44544.49326388889</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -55833,7 +55833,7 @@
         <v>44596</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -55890,7 +55890,7 @@
         <v>45534.57745370371</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>45840.58494212963</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56009,7 +56009,7 @@
         <v>45882.34510416666</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56071,7 +56071,7 @@
         <v>45840.40717592592</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>45839.61541666667</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45839.61563657408</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>45881.39909722222</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56314,7 +56314,7 @@
         <v>45719</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56371,7 +56371,7 @@
         <v>45882.69851851852</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -56433,7 +56433,7 @@
         <v>45764</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -56490,7 +56490,7 @@
         <v>45839.72320601852</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -56547,7 +56547,7 @@
         <v>45839.61582175926</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -56609,7 +56609,7 @@
         <v>45839.61594907408</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>45881.40521990741</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45758</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -56785,7 +56785,7 @@
         <v>45881.51081018519</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>44732</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -56904,7 +56904,7 @@
         <v>44865</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -56961,7 +56961,7 @@
         <v>45883.61028935185</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57018,7 +57018,7 @@
         <v>44186</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>45878</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45842</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>45841.67834490741</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57256,7 +57256,7 @@
         <v>45707.55246527777</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57318,7 +57318,7 @@
         <v>45720.60774305555</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>45842.39587962963</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -57442,7 +57442,7 @@
         <v>45842.40013888889</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -57504,7 +57504,7 @@
         <v>45615.61302083333</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -57566,7 +57566,7 @@
         <v>44228</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -57623,7 +57623,7 @@
         <v>45634.7925</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45634.79854166666</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>45883.37883101852</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>45842</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>45748</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -57913,7 +57913,7 @@
         <v>45608.61923611111</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -57970,7 +57970,7 @@
         <v>45600.433125</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58032,7 +58032,7 @@
         <v>45701.57363425926</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58089,7 +58089,7 @@
         <v>45841.46925925926</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58151,7 +58151,7 @@
         <v>45343.95162037037</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58213,7 +58213,7 @@
         <v>45392.95844907407</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58270,7 +58270,7 @@
         <v>45392</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58327,7 +58327,7 @@
         <v>44335</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58384,7 +58384,7 @@
         <v>45842.6099537037</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -58441,7 +58441,7 @@
         <v>44873</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -58518,7 +58518,7 @@
         <v>45841.43987268519</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -58575,7 +58575,7 @@
         <v>45182</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -58632,7 +58632,7 @@
         <v>45723.50841435185</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -58689,7 +58689,7 @@
         <v>44901.54615740741</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>45615.59521990741</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>44133</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -58865,7 +58865,7 @@
         <v>45749.38379629629</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45401.59810185185</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -58979,7 +58979,7 @@
         <v>44741</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>45460.44076388889</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>45695.45013888889</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59155,7 +59155,7 @@
         <v>45707.33935185185</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59217,7 +59217,7 @@
         <v>45772.62052083333</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59274,7 +59274,7 @@
         <v>45246</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59331,7 +59331,7 @@
         <v>44849.8044212963</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>45560.38056712963</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -59450,7 +59450,7 @@
         <v>44788</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -59507,7 +59507,7 @@
         <v>44601.35342592592</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -59564,7 +59564,7 @@
         <v>44206</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -59621,7 +59621,7 @@
         <v>45216</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -59678,7 +59678,7 @@
         <v>45316</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -59735,7 +59735,7 @@
         <v>45772.58283564815</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -59792,7 +59792,7 @@
         <v>44764</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -59849,7 +59849,7 @@
         <v>44764</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -59906,7 +59906,7 @@
         <v>45772.59200231481</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -59963,7 +59963,7 @@
         <v>44732</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60020,7 +60020,7 @@
         <v>44875</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>44972.55690972223</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60134,7 +60134,7 @@
         <v>44211</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60191,7 +60191,7 @@
         <v>45117</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60253,7 +60253,7 @@
         <v>45123.61459490741</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60315,7 +60315,7 @@
         <v>45600.49616898148</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60372,7 +60372,7 @@
         <v>45469</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -60429,7 +60429,7 @@
         <v>45762.60907407408</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -60491,7 +60491,7 @@
         <v>45117</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45586.46927083333</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45555.43584490741</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45574.43403935185</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         <v>45618.54398148148</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -60781,7 +60781,7 @@
         <v>45510.58033564815</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>45216.3965625</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -60900,7 +60900,7 @@
         <v>45246</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -60957,7 +60957,7 @@
         <v>45289</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61014,7 +61014,7 @@
         <v>45378</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61071,7 +61071,7 @@
         <v>45226</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61128,7 +61128,7 @@
         <v>44148</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>45561.61509259259</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61242,7 +61242,7 @@
         <v>45457.38799768518</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61299,7 +61299,7 @@
         <v>44349</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61361,7 +61361,7 @@
         <v>44273</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -61418,7 +61418,7 @@
         <v>45036</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -61475,7 +61475,7 @@
         <v>45036</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -61532,7 +61532,7 @@
         <v>45603.28460648148</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -61594,7 +61594,7 @@
         <v>44524</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -61651,7 +61651,7 @@
         <v>45610.36561342593</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -61708,7 +61708,7 @@
         <v>45231</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -61765,7 +61765,7 @@
         <v>45607</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -61822,7 +61822,7 @@
         <v>44795</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -61884,7 +61884,7 @@
         <v>45614.63606481482</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -61941,7 +61941,7 @@
         <v>45614.63701388889</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>44488.47928240741</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62055,7 +62055,7 @@
         <v>44285</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62112,7 +62112,7 @@
         <v>45097</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62169,7 +62169,7 @@
         <v>45226</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62226,7 +62226,7 @@
         <v>44961</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62283,7 +62283,7 @@
         <v>45140</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62340,7 +62340,7 @@
         <v>45090</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -62397,7 +62397,7 @@
         <v>45466.62116898148</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -62454,7 +62454,7 @@
         <v>44391</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -62511,7 +62511,7 @@
         <v>45639</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -62568,7 +62568,7 @@
         <v>45642.6366087963</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -62625,7 +62625,7 @@
         <v>44334</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -62682,7 +62682,7 @@
         <v>45696.3440162037</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -62739,7 +62739,7 @@
         <v>45638.81375</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -62796,7 +62796,7 @@
         <v>45107</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -62853,7 +62853,7 @@
         <v>45708</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -62915,7 +62915,7 @@
         <v>45713.36836805556</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -62977,7 +62977,7 @@
         <v>45621</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>45642.63666666667</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63091,7 +63091,7 @@
         <v>44331</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63148,7 +63148,7 @@
         <v>45692</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63210,7 +63210,7 @@
         <v>45180.6391087963</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63272,7 +63272,7 @@
         <v>45607.63211805555</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63329,7 +63329,7 @@
         <v>45694.34268518518</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -63391,7 +63391,7 @@
         <v>45204.40770833333</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -63448,7 +63448,7 @@
         <v>45467</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -63505,7 +63505,7 @@
         <v>44390</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -63562,7 +63562,7 @@
         <v>45670</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         <v>45614.65925925926</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -63676,7 +63676,7 @@
         <v>45602.65599537037</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -63733,7 +63733,7 @@
         <v>45519.60965277778</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -63790,7 +63790,7 @@
         <v>45190</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -63847,7 +63847,7 @@
         <v>45050</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -63909,7 +63909,7 @@
         <v>45635</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -63966,7 +63966,7 @@
         <v>45453.45515046296</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64023,7 +64023,7 @@
         <v>45056</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64080,7 +64080,7 @@
         <v>44377</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64137,7 +64137,7 @@
         <v>45713.59163194444</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>44370</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64256,7 +64256,7 @@
         <v>44427</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64313,7 +64313,7 @@
         <v>45000</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64370,7 +64370,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -64432,7 +64432,7 @@
         <v>45694.65905092593</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -64489,7 +64489,7 @@
         <v>45602.57827546296</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -64546,7 +64546,7 @@
         <v>45713.59952546296</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -64608,7 +64608,7 @@
         <v>45653.57240740741</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -64670,7 +64670,7 @@
         <v>45692.60364583333</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -64727,7 +64727,7 @@
         <v>45721.55653935186</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -64784,7 +64784,7 @@
         <v>45708</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -64846,7 +64846,7 @@
         <v>45189</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -64903,7 +64903,7 @@
         <v>45701</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -64965,7 +64965,7 @@
         <v>45713.59741898148</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65027,7 +65027,7 @@
         <v>45452.56446759259</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65089,7 +65089,7 @@
         <v>45679.70027777777</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65146,7 +65146,7 @@
         <v>45600.58076388889</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65203,7 +65203,7 @@
         <v>44757</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65265,7 +65265,7 @@
         <v>45453</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65327,7 +65327,7 @@
         <v>45453.95237268518</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65389,7 +65389,7 @@
         <v>45499.48672453704</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -65446,7 +65446,7 @@
         <v>45687</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -65503,7 +65503,7 @@
         <v>45560.69164351852</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -65560,7 +65560,7 @@
         <v>45748.57269675926</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -65617,7 +65617,7 @@
         <v>45649.38149305555</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -65674,7 +65674,7 @@
         <v>44908</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -65736,7 +65736,7 @@
         <v>45764.40834490741</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -65793,7 +65793,7 @@
         <v>45719.37307870371</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -65855,7 +65855,7 @@
         <v>45586.53618055556</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -65912,7 +65912,7 @@
         <v>45459.55150462963</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -65974,7 +65974,7 @@
         <v>45483</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>44379.59675925926</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66088,7 +66088,7 @@
         <v>45607</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66145,7 +66145,7 @@
         <v>45485</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66202,7 +66202,7 @@
         <v>45665.57373842593</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66259,7 +66259,7 @@
         <v>45770.64677083334</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66316,7 +66316,7 @@
         <v>45615.61121527778</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -66378,7 +66378,7 @@
         <v>45608.61606481481</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -66435,7 +66435,7 @@
         <v>45674</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -66492,7 +66492,7 @@
         <v>45593.38568287037</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -66549,7 +66549,7 @@
         <v>45672.53806712963</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -66611,7 +66611,7 @@
         <v>45189.60987268519</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -66668,7 +66668,7 @@
         <v>45758.58943287037</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -66730,7 +66730,7 @@
         <v>45670</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -66787,7 +66787,7 @@
         <v>45649.4634375</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -66844,7 +66844,7 @@
         <v>45245</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -66906,7 +66906,7 @@
         <v>45643.65354166667</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -66963,7 +66963,7 @@
         <v>45630.47099537037</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67020,7 +67020,7 @@
         <v>45698.45653935185</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67077,7 +67077,7 @@
         <v>45310</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67134,7 +67134,7 @@
         <v>45695</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67196,7 +67196,7 @@
         <v>45160.66704861111</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67258,7 +67258,7 @@
         <v>45547.42732638889</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67315,7 +67315,7 @@
         <v>45721.54896990741</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -67372,7 +67372,7 @@
         <v>45721</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -67429,7 +67429,7 @@
         <v>45203</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -67486,7 +67486,7 @@
         <v>45602</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -67543,7 +67543,7 @@
         <v>45532.58101851852</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -67600,7 +67600,7 @@
         <v>45055</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -67657,7 +67657,7 @@
         <v>45758.66180555556</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -67714,7 +67714,7 @@
         <v>45758.67065972222</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -67771,7 +67771,7 @@
         <v>45369</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -67828,7 +67828,7 @@
         <v>45692.64298611111</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -67885,7 +67885,7 @@
         <v>45726.37850694444</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -67947,7 +67947,7 @@
         <v>45763.46918981482</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68004,7 +68004,7 @@
         <v>45209</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68061,7 +68061,7 @@
         <v>45746</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68123,7 +68123,7 @@
         <v>45371</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68180,7 +68180,7 @@
         <v>45090</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68237,7 +68237,7 @@
         <v>45554.59538194445</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68294,7 +68294,7 @@
         <v>45726.56341435185</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -68356,7 +68356,7 @@
         <v>45726.5827199074</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -68413,7 +68413,7 @@
         <v>45726.61520833334</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -68475,7 +68475,7 @@
         <v>45705.33446759259</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -68537,7 +68537,7 @@
         <v>44887</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -68599,7 +68599,7 @@
         <v>45751.37320601852</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -68656,7 +68656,7 @@
         <v>45118</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -68713,7 +68713,7 @@
         <v>44140</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -68770,7 +68770,7 @@
         <v>45597.49638888889</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -68827,7 +68827,7 @@
         <v>45279</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -68884,7 +68884,7 @@
         <v>45055</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -68941,7 +68941,7 @@
         <v>44866</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -68998,7 +68998,7 @@
         <v>45407</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -69055,7 +69055,7 @@
         <v>45649.45143518518</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -69112,7 +69112,7 @@
         <v>45452.55271990741</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -69174,7 +69174,7 @@
         <v>45748.36445601852</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -69231,7 +69231,7 @@
         <v>45748.37173611111</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -69288,7 +69288,7 @@
         <v>45371</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -69345,7 +69345,7 @@
         <v>44456</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -69402,7 +69402,7 @@
         <v>45744</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -69459,7 +69459,7 @@
         <v>45740.60405092593</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -69521,7 +69521,7 @@
         <v>44965</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -69583,7 +69583,7 @@
         <v>45751.6877662037</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -69645,7 +69645,7 @@
         <v>45751.28243055556</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -69707,7 +69707,7 @@
         <v>45740.60347222222</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -69769,7 +69769,7 @@
         <v>45266</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -69826,7 +69826,7 @@
         <v>45245</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -69883,7 +69883,7 @@
         <v>45691.61996527778</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -69945,7 +69945,7 @@
         <v>45377</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -70002,7 +70002,7 @@
         <v>45560.45841435185</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -70064,7 +70064,7 @@
         <v>45260</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -70121,7 +70121,7 @@
         <v>44540</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -70178,7 +70178,7 @@
         <v>45721.4546412037</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -70235,7 +70235,7 @@
         <v>45446.47634259259</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -70297,7 +70297,7 @@
         <v>45686.35247685185</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -70359,7 +70359,7 @@
         <v>45484</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -70421,7 +70421,7 @@
         <v>45527.39858796296</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -70478,7 +70478,7 @@
         <v>45586</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -70535,7 +70535,7 @@
         <v>45478.60708333334</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -70592,7 +70592,7 @@
         <v>45042</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -70649,7 +70649,7 @@
         <v>45090</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>

--- a/Översikt KROKOM.xlsx
+++ b/Översikt KROKOM.xlsx
@@ -567,7 +567,7 @@
         <v>45716</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44522</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45348</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44165</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45384</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>45254</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>45709</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>45637</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45603</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44378</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45478</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45845</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>44323</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>45121</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45155</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45646</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>44565</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>44363</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>45219</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>45453</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45630</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>45625</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45041</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>45790</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>45663</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>45553</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>45428</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>45644</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>45596.5093287037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>44306.52587962963</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44575</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>45792</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>44326</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>44581</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>45475</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>44780</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>45784.56270833333</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>44323</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45691</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>44475</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>45849.31563657407</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45646</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45646</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>45551</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>44231</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>45488.56961805555</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>45639</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45512</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45534</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45719.52238425926</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44795</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>45041</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45580</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45527</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>45454</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>45643</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44118</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>45219</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>44498</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>44552</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>45181</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>45169</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45457</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>44308</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44133</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>44585</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44698</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>44500</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>45316</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>45616</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>45839.68914351852</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>45267</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>45149</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45475</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>44271</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>44265</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>44534</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44494</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>44326</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>45370</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>45180</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>44834</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44477</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>45581</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>45252</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>45755.47527777778</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>45832.38581018519</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>44797</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>45474</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>44183</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>44515</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44557</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>45551</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>44150</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>45874.67765046296</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>45838.67858796296</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>45532</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>45615</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>44903</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44546</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>45726.46192129629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>44452</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45079</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>44540</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44162</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>44510.94930555556</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>44728</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>45624</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>45169</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>45527</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>45849.42818287037</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>44895</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>44553</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45595</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>44966</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>45764</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>44904</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>44174</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>45621</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>44879</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>45735</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45632</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45310</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45617</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>45526</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>45656.54600694445</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>45511.55719907407</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45271</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>45453.63133101852</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45216</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>44540</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45821.44299768518</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45372</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>44757</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45636</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>44841</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>45630</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>45233</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>44867</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>45216.67748842593</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>44757</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>44873</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>45313</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>45692</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>44355</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>44161</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>44524</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>44316</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>44230</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>44757</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>44378</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45268</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45376</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45793.4189699074</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45595</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>45804.60005787037</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>45805</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>45554</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>44209</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>44540</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>45877.67787037037</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45869</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45348</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>44279</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45647.6565625</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>45643.53393518519</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45656.59703703703</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>44879</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>45223</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>44099</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44154</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44090</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44512</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>44445</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>44512</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>44445</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44728</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17682,7 +17682,7 @@
         <v>44207</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44797</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>44742</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>44377</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>45123</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45622</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44603</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45595</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45595</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>45079</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>45271</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45595</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45847.46962962963</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45847.51078703703</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44568</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45645.67945601852</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45700</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44683</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>44630</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45153</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45819.65796296296</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45862.43403935185</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45862.4257175926</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>45826.45174768518</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45609</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45595</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45609</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45838.67815972222</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>45838</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45839.60460648148</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45702.47149305556</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>45841.52454861111</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>44568</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>44075</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>44568</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45020</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>45685.78776620371</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45098</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>45736.42743055556</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>45695.42197916667</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45686.27208333334</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>45750.42127314815</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>44540</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45407</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>45635</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45243</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>45180</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>44308</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45467</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>44313</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>44113</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>44103</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>44102</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>44214</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>44371</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>44748.94689814815</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44407</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44473.44813657407</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44473.508125</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44256</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44183</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44175</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44679</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>44665</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>44449</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>44173</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>44445</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44494</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>44788</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>44610</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>44376.87497685185</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>44377.44767361111</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44285</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44133</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44263</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44183</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44183</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44524</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44370</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>44591</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44123</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44714.438125</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44162</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44090</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44141</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44255</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44577.47756944445</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44287</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44533</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44749</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44126.94510416667</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>44831.37650462963</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>44512.94539351852</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>44200</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44172</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>44369.41452546296</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>44271.43831018519</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>44502.94153935185</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>44312</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>44306</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>44788</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>44502</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>44207</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>44851.57131944445</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>44209</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>44209</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44243</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44473</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44106</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44466.53040509259</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>44300</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>44539</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>44495</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>44495</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>44277.59521990741</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>44062</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44512</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>44172</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>44337</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>44214</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>44502.94140046297</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44693.41668981482</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44473.53681712963</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44714</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>44377</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>44459</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>44382.92065972222</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>44095</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>44728.94420138889</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>44358.63585648148</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44526</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44214</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>44524</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>44820</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>44076</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>44113</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44123</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>44610</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>44123</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>44473.53013888889</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44459</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>44337</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>44848</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>44875.41104166667</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44123</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44697.94231481481</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44519.63436342592</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>44727</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>44470</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>44214</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>44169</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>44279</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>44705</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>44209</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44284</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>44118.98730324074</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44307.42378472222</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44447</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>44468</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44470.39989583333</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44285</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44848</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>44400.37204861111</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>44139</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44077</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44470</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45749</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>45720</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>44153</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -28948,7 +28948,7 @@
         <v>45035</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>44151</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29062,7 +29062,7 @@
         <v>45412.51260416667</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>45714.34859953704</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>45719.32584490741</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>45370.94969907407</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45531.62141203704</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>45254</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44858</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45411</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45747.47025462963</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45203.46523148148</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>44830</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45112</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         <v>44316</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -29848,7 +29848,7 @@
         <v>45133</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>44061</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>45253</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>44539</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>45560</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45698.39486111111</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>45245.5478125</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>44875</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>45362</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45373</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30428,7 +30428,7 @@
         <v>44834.95019675926</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -30490,7 +30490,7 @@
         <v>44825</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>45082</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45182</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>45370</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>45740</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>45415.45006944444</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45393</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>45760.81083333334</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45251.65152777778</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>44874</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31065,7 +31065,7 @@
         <v>45601.33743055556</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>45572.45601851852</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45244</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>44803</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45324</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45764.55260416667</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>44550</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45217</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44974</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>45713.60719907407</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>45165.69965277778</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>44901.59349537037</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45554</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>45203</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>45300</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>45342</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>45686.32671296296</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45471.63390046296</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45701</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45239.9681712963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>45700.37127314815</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>45700.37481481482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44483.42253472222</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>45474.69155092593</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>44389</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45386</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45362</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45414.486875</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>45243.37567129629</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>45552.57210648148</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45398</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45474</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45282</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45195</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>45715</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>45776</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>45478.42063657408</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>44516</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>45693</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45777</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>45712</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45152</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>45777</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>45777</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -33648,7 +33648,7 @@
         <v>45779.56659722222</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45779.63834490741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>44504</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>45779.57626157408</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45457.55922453704</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>44939</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>45551.34414351852</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>45265.52887731481</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>45779.65980324074</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>45779.42630787037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34223,7 +34223,7 @@
         <v>45779.5674074074</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>45748.3822337963</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45696</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>45783.44828703703</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         <v>45783</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -34518,7 +34518,7 @@
         <v>45783</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>45608.86341435185</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -34632,7 +34632,7 @@
         <v>45783.45121527778</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>45112</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>45418.94616898148</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>45783.43409722222</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -34860,7 +34860,7 @@
         <v>45713.37111111111</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45688.38393518519</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45454.57899305555</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>45740</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45117</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45579.66459490741</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>45392</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44480</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>45786.35219907408</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45594.463125</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45119</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45786</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>45785.52112268518</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>45785.5403125</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45785.54635416667</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>45180</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>45706</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45786</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45786.64972222222</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45786.65702546296</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36015,7 +36015,7 @@
         <v>45666.65987268519</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>45785</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45786.66140046297</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36186,7 +36186,7 @@
         <v>45715</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>45250</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45785.51092592593</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45467</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45789.58238425926</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45789.61349537037</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>45457.35388888889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>45109.44534722222</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>45226</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>45602.38614583333</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>45602.39862268518</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>45602.42878472222</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>44971</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>45632</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>45243.33297453704</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>45145.95255787037</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>45583.52885416667</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>44510.9491087963</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45834.34737268519</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>45833.63579861111</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>45833.49052083334</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45833.49057870371</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45706.59251157408</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45195</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45631.61869212963</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>45695.60015046296</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>45411.4666087963</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>45635.39820601852</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>45166</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>44391</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>45791</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>44582</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45791.3162037037</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>45721.66456018519</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>45484</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45614.63575231482</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45796.52836805556</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45392</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>45660.49618055556</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>45378</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45414.96341435185</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>44818</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>45686.33310185185</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45793.45204861111</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45713</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         <v>45476</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45698.40146990741</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45603.44815972223</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45643.64706018518</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45796.59857638889</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45706.55993055556</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45608</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45695.57171296296</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>44557</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45714.69212962963</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>44658</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -39468,7 +39468,7 @@
         <v>45588</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>45588</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>45798.63611111111</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>45798.63596064815</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>45800.57129629629</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>45800.57461805556</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>45800</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>45800.37061342593</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>45560.6599537037</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>45800.56810185185</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>45791</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45800.65177083333</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45800.64319444444</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>45684.62510416667</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45746</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45699</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>44988.94056712963</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45800</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>44141</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45803</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>45198.42734953704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>44686</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -40757,7 +40757,7 @@
         <v>45573.54893518519</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>45432.54027777778</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45182</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>45803.6837962963</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45096</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>45580.36991898148</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>45474.69074074074</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45225.60212962963</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>45803.69828703703</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45204</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45848.48070601852</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45687</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45695.4046875</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>45261</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45848.60371527778</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45695.42418981482</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45805.47425925926</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45721</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45847.51106481482</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>45805.54185185185</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45565.32449074074</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>44151</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42031,7 +42031,7 @@
         <v>45751.3734837963</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42088,7 +42088,7 @@
         <v>45751.57877314815</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>45554.59550925926</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42202,7 +42202,7 @@
         <v>45733</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>45805</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45656</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>45746.79134259259</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -42435,7 +42435,7 @@
         <v>45692</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45695.61160879629</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45602</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45716.55237268518</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45278.65582175926</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45847.65717592592</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -42797,7 +42797,7 @@
         <v>45467</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45117</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45847.46462962963</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45432.36971064815</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45446.68733796296</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45667.57217592592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45849.4525462963</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45849.3859837963</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>45699.66576388889</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>45190</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43382,7 +43382,7 @@
         <v>44911</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45686</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -43496,7 +43496,7 @@
         <v>45099.37211805556</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>45547.42736111111</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -43610,7 +43610,7 @@
         <v>45176</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>45848</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>45807.58930555556</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>45694.64416666667</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -43848,7 +43848,7 @@
         <v>45620.67667824074</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>45810.32105324074</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -43962,7 +43962,7 @@
         <v>45231</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>45662</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>45401.59133101852</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44138,7 +44138,7 @@
         <v>45525</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>45693.67361111111</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
         <v>45638.81385416666</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>45309.94650462963</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>45704.71069444445</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45692.58106481482</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45097</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>44873</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -44609,7 +44609,7 @@
         <v>45700.27895833334</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>45623.48571759259</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>44970</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>45807.56728009259</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45701.60901620371</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45118.94061342593</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>45694.43806712963</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45630</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45484</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45676</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45761.50909722222</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45477.35225694445</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>44203</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45216</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>44140</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>45474.3981712963</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>45721.5113425926</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>45737.36873842592</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45705</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>45614.63697916667</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>44715.48863425926</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -45826,7 +45826,7 @@
         <v>45532.48732638889</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>44522.46662037037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>45811.54760416667</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45853.6156712963</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45854.66518518519</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>45810.31376157407</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>45408</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45812.32266203704</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45693.48239583334</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>44922</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>45698.4930787037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>44154</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>45811.67769675926</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -46572,7 +46572,7 @@
         <v>45698.57129629629</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -46629,7 +46629,7 @@
         <v>45686.39777777778</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45811.69912037037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45238</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45854.65378472222</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45813.44443287037</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45748.59744212963</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45813.46969907408</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45814</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45814</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45511.95109953704</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45813.68361111111</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>44466.56642361111</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -47318,7 +47318,7 @@
         <v>44498</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>45635.67949074074</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>45608.43930555556</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45785.67431712963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45709</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>45855.61193287037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -47670,7 +47670,7 @@
         <v>45818.36246527778</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -47732,7 +47732,7 @@
         <v>44179</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>45818.3293287037</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -47851,7 +47851,7 @@
         <v>45720.40268518519</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45477.32728009259</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45817.56761574074</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45721.45563657407</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45815.50844907408</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45488.94857638889</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45475</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45818.34474537037</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45818.34473379629</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -48389,7 +48389,7 @@
         <v>45818.33532407408</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>45818.34833333334</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -48513,7 +48513,7 @@
         <v>45818.37056712963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>44600.37212962963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45693</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>45168</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -48746,7 +48746,7 @@
         <v>44792.27644675926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>44750</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -48860,7 +48860,7 @@
         <v>44721.39003472222</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>44362</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>45538.68200231482</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49036,7 +49036,7 @@
         <v>45862.34668981482</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45820</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>44592</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>44726</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45860</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45695.47791666666</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45820</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -49440,7 +49440,7 @@
         <v>44893</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -49497,7 +49497,7 @@
         <v>45820.36233796296</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45820.36512731481</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45820.47200231482</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -49673,7 +49673,7 @@
         <v>45820</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -49730,7 +49730,7 @@
         <v>44855</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>44855</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -49844,7 +49844,7 @@
         <v>44880</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -49901,7 +49901,7 @@
         <v>45406.05033564815</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -49963,7 +49963,7 @@
         <v>45862.42901620371</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50020,7 +50020,7 @@
         <v>45820.36498842593</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50077,7 +50077,7 @@
         <v>45820.36506944444</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50134,7 +50134,7 @@
         <v>45861.6841087963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50196,7 +50196,7 @@
         <v>44741</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>45821.39026620371</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50310,7 +50310,7 @@
         <v>45750.42650462963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -50367,7 +50367,7 @@
         <v>44726</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -50424,7 +50424,7 @@
         <v>45863.45778935185</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -50481,7 +50481,7 @@
         <v>45863</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -50538,7 +50538,7 @@
         <v>45300</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -50595,7 +50595,7 @@
         <v>44904</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -50652,7 +50652,7 @@
         <v>45863.58127314815</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>45713.36561342593</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -50776,7 +50776,7 @@
         <v>45713.38028935185</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45700.6833912037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45863.59111111111</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45764.47059027778</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45744.59894675926</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45279</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>44188</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45121</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51252,7 +51252,7 @@
         <v>45867.41707175926</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45867.46560185185</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -51366,7 +51366,7 @@
         <v>45826.4705787037</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>45496.41289351852</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>45618.53126157408</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45618.53633101852</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45601.38071759259</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>45238</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -51728,7 +51728,7 @@
         <v>45257</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>45554.59447916667</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45551.47325231481</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45700.30092592593</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -51966,7 +51966,7 @@
         <v>45247</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>45491.44971064815</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52080,7 +52080,7 @@
         <v>45713.59623842593</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52142,7 +52142,7 @@
         <v>45869.34439814815</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52204,7 +52204,7 @@
         <v>45550.66542824074</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52261,7 +52261,7 @@
         <v>44757</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>44214</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45671.59114583334</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>44498</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45870</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45561.61515046296</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>44938.93989583333</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>45827.34488425926</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -52727,7 +52727,7 @@
         <v>44711</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>45700.56194444445</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45750.60577546297</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45369</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>45274</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45572</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         <v>45687.48931712963</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         <v>45566.51501157408</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         <v>44207</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53255,7 +53255,7 @@
         <v>45832</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         <v>45832.34630787037</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -53374,7 +53374,7 @@
         <v>45203.44248842593</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -53431,7 +53431,7 @@
         <v>45832.53935185185</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -53493,7 +53493,7 @@
         <v>45832.53225694445</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -53555,7 +53555,7 @@
         <v>45165.70483796296</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         <v>45448.67574074074</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -53674,7 +53674,7 @@
         <v>45601</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -53731,7 +53731,7 @@
         <v>44847</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -53788,7 +53788,7 @@
         <v>45232.46239583333</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -53845,7 +53845,7 @@
         <v>44847</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -53902,7 +53902,7 @@
         <v>44858</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -53959,7 +53959,7 @@
         <v>45552.67611111111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54016,7 +54016,7 @@
         <v>45875.51046296296</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54073,7 +54073,7 @@
         <v>45833.34490740741</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54135,7 +54135,7 @@
         <v>45833.36050925926</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54192,7 +54192,7 @@
         <v>45833.36083333333</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54249,7 +54249,7 @@
         <v>45180</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54311,7 +54311,7 @@
         <v>45763.44112268519</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -54368,7 +54368,7 @@
         <v>45834.34726851852</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -54430,7 +54430,7 @@
         <v>45750.6447800926</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -54492,7 +54492,7 @@
         <v>45757.56491898148</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -54549,7 +54549,7 @@
         <v>45834.61517361111</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -54611,7 +54611,7 @@
         <v>45876</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -54668,7 +54668,7 @@
         <v>45876</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -54725,7 +54725,7 @@
         <v>45876</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -54782,7 +54782,7 @@
         <v>45833.36111111111</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>45022</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -54896,7 +54896,7 @@
         <v>45257</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -54953,7 +54953,7 @@
         <v>45348</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55010,7 +55010,7 @@
         <v>44887</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55072,7 +55072,7 @@
         <v>45877.46555555556</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55129,7 +55129,7 @@
         <v>45880</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55186,7 +55186,7 @@
         <v>45835.42712962963</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55243,7 +55243,7 @@
         <v>44631</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55300,7 +55300,7 @@
         <v>45565.33152777778</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -55357,7 +55357,7 @@
         <v>45836.34413194445</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -55419,7 +55419,7 @@
         <v>45139</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -55481,7 +55481,7 @@
         <v>45572</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -55543,7 +55543,7 @@
         <v>45877.57403935185</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -55605,7 +55605,7 @@
         <v>44970</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -55662,7 +55662,7 @@
         <v>45056</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -55719,7 +55719,7 @@
         <v>45056</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -55776,7 +55776,7 @@
         <v>44544.49326388889</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -55833,7 +55833,7 @@
         <v>44596</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -55890,7 +55890,7 @@
         <v>45534.57745370371</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>45840.58494212963</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56009,7 +56009,7 @@
         <v>45882.34510416666</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56071,7 +56071,7 @@
         <v>45840.40717592592</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>45839.61541666667</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45839.61563657408</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>45881.39909722222</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56314,7 +56314,7 @@
         <v>45719</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56371,7 +56371,7 @@
         <v>45882.69851851852</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -56433,7 +56433,7 @@
         <v>45764</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -56490,7 +56490,7 @@
         <v>45839.72320601852</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -56547,7 +56547,7 @@
         <v>45839.61582175926</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -56609,7 +56609,7 @@
         <v>45839.61594907408</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>45881.40521990741</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45758</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -56785,7 +56785,7 @@
         <v>45881.51081018519</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>44732</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -56904,7 +56904,7 @@
         <v>44865</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -56961,7 +56961,7 @@
         <v>45883.61028935185</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57018,7 +57018,7 @@
         <v>44186</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>45878</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45842</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>45841.67834490741</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57256,7 +57256,7 @@
         <v>45707.55246527777</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57318,7 +57318,7 @@
         <v>45720.60774305555</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>45842.39587962963</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -57442,7 +57442,7 @@
         <v>45842.40013888889</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -57504,7 +57504,7 @@
         <v>45615.61302083333</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -57566,7 +57566,7 @@
         <v>44228</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -57623,7 +57623,7 @@
         <v>45634.7925</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45634.79854166666</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>45883.37883101852</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>45842</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>45748</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -57913,7 +57913,7 @@
         <v>45608.61923611111</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -57970,7 +57970,7 @@
         <v>45600.433125</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58032,7 +58032,7 @@
         <v>45701.57363425926</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58089,7 +58089,7 @@
         <v>45841.46925925926</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58151,7 +58151,7 @@
         <v>45343.95162037037</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58213,7 +58213,7 @@
         <v>45392.95844907407</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58270,7 +58270,7 @@
         <v>45392</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58327,7 +58327,7 @@
         <v>44335</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58384,7 +58384,7 @@
         <v>45842.6099537037</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -58441,7 +58441,7 @@
         <v>44873</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -58518,7 +58518,7 @@
         <v>45841.43987268519</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -58575,7 +58575,7 @@
         <v>45182</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -58632,7 +58632,7 @@
         <v>45723.50841435185</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -58689,7 +58689,7 @@
         <v>44901.54615740741</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>45615.59521990741</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>44133</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -58865,7 +58865,7 @@
         <v>45749.38379629629</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45401.59810185185</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -58979,7 +58979,7 @@
         <v>44741</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>45460.44076388889</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>45695.45013888889</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59155,7 +59155,7 @@
         <v>45707.33935185185</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59217,7 +59217,7 @@
         <v>45772.62052083333</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59274,7 +59274,7 @@
         <v>45246</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59331,7 +59331,7 @@
         <v>44849.8044212963</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>45560.38056712963</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -59450,7 +59450,7 @@
         <v>44788</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -59507,7 +59507,7 @@
         <v>44601.35342592592</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -59564,7 +59564,7 @@
         <v>44206</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -59621,7 +59621,7 @@
         <v>45216</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -59678,7 +59678,7 @@
         <v>45316</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -59735,7 +59735,7 @@
         <v>45772.58283564815</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -59792,7 +59792,7 @@
         <v>44764</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -59849,7 +59849,7 @@
         <v>44764</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -59906,7 +59906,7 @@
         <v>45772.59200231481</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -59963,7 +59963,7 @@
         <v>44732</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60020,7 +60020,7 @@
         <v>44875</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>44972.55690972223</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60134,7 +60134,7 @@
         <v>44211</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60191,7 +60191,7 @@
         <v>45117</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60253,7 +60253,7 @@
         <v>45123.61459490741</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60315,7 +60315,7 @@
         <v>45600.49616898148</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60372,7 +60372,7 @@
         <v>45469</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -60429,7 +60429,7 @@
         <v>45762.60907407408</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -60491,7 +60491,7 @@
         <v>45117</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45586.46927083333</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45555.43584490741</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45574.43403935185</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         <v>45618.54398148148</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -60781,7 +60781,7 @@
         <v>45510.58033564815</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>45216.3965625</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -60900,7 +60900,7 @@
         <v>45246</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -60957,7 +60957,7 @@
         <v>45289</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61014,7 +61014,7 @@
         <v>45378</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61071,7 +61071,7 @@
         <v>45226</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61128,7 +61128,7 @@
         <v>44148</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>45561.61509259259</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61242,7 +61242,7 @@
         <v>45457.38799768518</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61299,7 +61299,7 @@
         <v>44349</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61361,7 +61361,7 @@
         <v>44273</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -61418,7 +61418,7 @@
         <v>45036</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -61475,7 +61475,7 @@
         <v>45036</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -61532,7 +61532,7 @@
         <v>45603.28460648148</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -61594,7 +61594,7 @@
         <v>44524</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -61651,7 +61651,7 @@
         <v>45610.36561342593</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -61708,7 +61708,7 @@
         <v>45231</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -61765,7 +61765,7 @@
         <v>45607</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -61822,7 +61822,7 @@
         <v>44795</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -61884,7 +61884,7 @@
         <v>45614.63606481482</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -61941,7 +61941,7 @@
         <v>45614.63701388889</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>44488.47928240741</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62055,7 +62055,7 @@
         <v>44285</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62112,7 +62112,7 @@
         <v>45097</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62169,7 +62169,7 @@
         <v>45226</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62226,7 +62226,7 @@
         <v>44961</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62283,7 +62283,7 @@
         <v>45140</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62340,7 +62340,7 @@
         <v>45090</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -62397,7 +62397,7 @@
         <v>45466.62116898148</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -62454,7 +62454,7 @@
         <v>44391</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -62511,7 +62511,7 @@
         <v>45639</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -62568,7 +62568,7 @@
         <v>45642.6366087963</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -62625,7 +62625,7 @@
         <v>44334</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -62682,7 +62682,7 @@
         <v>45696.3440162037</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -62739,7 +62739,7 @@
         <v>45638.81375</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -62796,7 +62796,7 @@
         <v>45107</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -62853,7 +62853,7 @@
         <v>45708</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -62915,7 +62915,7 @@
         <v>45713.36836805556</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -62977,7 +62977,7 @@
         <v>45621</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>45642.63666666667</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63091,7 +63091,7 @@
         <v>44331</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63148,7 +63148,7 @@
         <v>45692</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63210,7 +63210,7 @@
         <v>45180.6391087963</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63272,7 +63272,7 @@
         <v>45607.63211805555</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63329,7 +63329,7 @@
         <v>45694.34268518518</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -63391,7 +63391,7 @@
         <v>45204.40770833333</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -63448,7 +63448,7 @@
         <v>45467</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -63505,7 +63505,7 @@
         <v>44390</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -63562,7 +63562,7 @@
         <v>45670</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         <v>45614.65925925926</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -63676,7 +63676,7 @@
         <v>45602.65599537037</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -63733,7 +63733,7 @@
         <v>45519.60965277778</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -63790,7 +63790,7 @@
         <v>45190</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -63847,7 +63847,7 @@
         <v>45050</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -63909,7 +63909,7 @@
         <v>45635</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -63966,7 +63966,7 @@
         <v>45453.45515046296</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64023,7 +64023,7 @@
         <v>45056</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64080,7 +64080,7 @@
         <v>44377</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64137,7 +64137,7 @@
         <v>45713.59163194444</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>44370</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64256,7 +64256,7 @@
         <v>44427</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64313,7 +64313,7 @@
         <v>45000</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64370,7 +64370,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -64432,7 +64432,7 @@
         <v>45694.65905092593</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -64489,7 +64489,7 @@
         <v>45602.57827546296</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -64546,7 +64546,7 @@
         <v>45713.59952546296</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -64608,7 +64608,7 @@
         <v>45653.57240740741</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -64670,7 +64670,7 @@
         <v>45692.60364583333</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -64727,7 +64727,7 @@
         <v>45721.55653935186</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -64784,7 +64784,7 @@
         <v>45708</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -64846,7 +64846,7 @@
         <v>45189</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -64903,7 +64903,7 @@
         <v>45701</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -64965,7 +64965,7 @@
         <v>45713.59741898148</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65027,7 +65027,7 @@
         <v>45452.56446759259</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65089,7 +65089,7 @@
         <v>45679.70027777777</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65146,7 +65146,7 @@
         <v>45600.58076388889</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65203,7 +65203,7 @@
         <v>44757</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65265,7 +65265,7 @@
         <v>45453</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65327,7 +65327,7 @@
         <v>45453.95237268518</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65389,7 +65389,7 @@
         <v>45499.48672453704</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -65446,7 +65446,7 @@
         <v>45687</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -65503,7 +65503,7 @@
         <v>45560.69164351852</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -65560,7 +65560,7 @@
         <v>45748.57269675926</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -65617,7 +65617,7 @@
         <v>45649.38149305555</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -65674,7 +65674,7 @@
         <v>44908</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -65736,7 +65736,7 @@
         <v>45764.40834490741</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -65793,7 +65793,7 @@
         <v>45719.37307870371</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -65855,7 +65855,7 @@
         <v>45586.53618055556</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -65912,7 +65912,7 @@
         <v>45459.55150462963</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -65974,7 +65974,7 @@
         <v>45483</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>44379.59675925926</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66088,7 +66088,7 @@
         <v>45607</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66145,7 +66145,7 @@
         <v>45485</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66202,7 +66202,7 @@
         <v>45665.57373842593</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66259,7 +66259,7 @@
         <v>45770.64677083334</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66316,7 +66316,7 @@
         <v>45615.61121527778</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -66378,7 +66378,7 @@
         <v>45608.61606481481</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -66435,7 +66435,7 @@
         <v>45674</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -66492,7 +66492,7 @@
         <v>45593.38568287037</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -66549,7 +66549,7 @@
         <v>45672.53806712963</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -66611,7 +66611,7 @@
         <v>45189.60987268519</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -66668,7 +66668,7 @@
         <v>45758.58943287037</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -66730,7 +66730,7 @@
         <v>45670</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -66787,7 +66787,7 @@
         <v>45649.4634375</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -66844,7 +66844,7 @@
         <v>45245</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -66906,7 +66906,7 @@
         <v>45643.65354166667</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -66963,7 +66963,7 @@
         <v>45630.47099537037</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67020,7 +67020,7 @@
         <v>45698.45653935185</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67077,7 +67077,7 @@
         <v>45310</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67134,7 +67134,7 @@
         <v>45695</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67196,7 +67196,7 @@
         <v>45160.66704861111</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67258,7 +67258,7 @@
         <v>45547.42732638889</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67315,7 +67315,7 @@
         <v>45721.54896990741</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -67372,7 +67372,7 @@
         <v>45721</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -67429,7 +67429,7 @@
         <v>45203</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -67486,7 +67486,7 @@
         <v>45602</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -67543,7 +67543,7 @@
         <v>45532.58101851852</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -67600,7 +67600,7 @@
         <v>45055</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -67657,7 +67657,7 @@
         <v>45758.66180555556</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -67714,7 +67714,7 @@
         <v>45758.67065972222</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -67771,7 +67771,7 @@
         <v>45369</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -67828,7 +67828,7 @@
         <v>45692.64298611111</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -67885,7 +67885,7 @@
         <v>45726.37850694444</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -67947,7 +67947,7 @@
         <v>45763.46918981482</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68004,7 +68004,7 @@
         <v>45209</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68061,7 +68061,7 @@
         <v>45746</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68123,7 +68123,7 @@
         <v>45371</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68180,7 +68180,7 @@
         <v>45090</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68237,7 +68237,7 @@
         <v>45554.59538194445</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68294,7 +68294,7 @@
         <v>45726.56341435185</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -68356,7 +68356,7 @@
         <v>45726.5827199074</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -68413,7 +68413,7 @@
         <v>45726.61520833334</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -68475,7 +68475,7 @@
         <v>45705.33446759259</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -68537,7 +68537,7 @@
         <v>44887</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -68599,7 +68599,7 @@
         <v>45751.37320601852</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -68656,7 +68656,7 @@
         <v>45118</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -68713,7 +68713,7 @@
         <v>44140</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -68770,7 +68770,7 @@
         <v>45597.49638888889</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -68827,7 +68827,7 @@
         <v>45279</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -68884,7 +68884,7 @@
         <v>45055</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -68941,7 +68941,7 @@
         <v>44866</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -68998,7 +68998,7 @@
         <v>45407</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -69055,7 +69055,7 @@
         <v>45649.45143518518</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -69112,7 +69112,7 @@
         <v>45452.55271990741</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -69174,7 +69174,7 @@
         <v>45748.36445601852</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -69231,7 +69231,7 @@
         <v>45748.37173611111</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -69288,7 +69288,7 @@
         <v>45371</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -69345,7 +69345,7 @@
         <v>44456</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -69402,7 +69402,7 @@
         <v>45744</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -69459,7 +69459,7 @@
         <v>45740.60405092593</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -69521,7 +69521,7 @@
         <v>44965</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -69583,7 +69583,7 @@
         <v>45751.6877662037</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -69645,7 +69645,7 @@
         <v>45751.28243055556</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -69707,7 +69707,7 @@
         <v>45740.60347222222</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -69769,7 +69769,7 @@
         <v>45266</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -69826,7 +69826,7 @@
         <v>45245</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -69883,7 +69883,7 @@
         <v>45691.61996527778</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -69945,7 +69945,7 @@
         <v>45377</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -70002,7 +70002,7 @@
         <v>45560.45841435185</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -70064,7 +70064,7 @@
         <v>45260</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -70121,7 +70121,7 @@
         <v>44540</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -70178,7 +70178,7 @@
         <v>45721.4546412037</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -70235,7 +70235,7 @@
         <v>45446.47634259259</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -70297,7 +70297,7 @@
         <v>45686.35247685185</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -70359,7 +70359,7 @@
         <v>45484</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -70421,7 +70421,7 @@
         <v>45527.39858796296</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -70478,7 +70478,7 @@
         <v>45586</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -70535,7 +70535,7 @@
         <v>45478.60708333334</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -70592,7 +70592,7 @@
         <v>45042</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -70649,7 +70649,7 @@
         <v>45090</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>

--- a/Översikt KROKOM.xlsx
+++ b/Översikt KROKOM.xlsx
@@ -567,7 +567,7 @@
         <v>45716</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44522</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45348</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44165</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45384</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>45254</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>45709</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>45637</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45603</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44378</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45845</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45478</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45121</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>44323</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>44565</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45646</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>45155</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>45453</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>44363</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45630</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45887.44892361111</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45219</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>45625</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>45041</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>45790</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>45663</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>45553</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>45849</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>45596.5093287037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>45428</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45644</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>44306.52587962963</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>44575</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45792</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>44581</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>45475</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>44326</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>44780</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>45784.56270833333</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44323</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>45691</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>44475</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45551</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>44231</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45646</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45646</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45041</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>45719.52238425926</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>45639</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>44795</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45534</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>45488.56961805555</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>45512</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>45219</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>45580</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>45527</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45454</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>44498</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>45643</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44118</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>44552</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>45181</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44308</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>45457</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>44133</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>45169</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>44698</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>44585</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>45267</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>45316</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>45475</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45149</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44500</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>45839.68914351852</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>45616</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44271</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44265</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>44534</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44494</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44326</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>45474</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44477</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44797</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44834</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45180</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>45370</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>45252</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>45832.38581018519</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>45581</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>45755.47527777778</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44183</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>44515</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45726.46192129629</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44903</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>45532</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>44540</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45079</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45551</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45874.67765046296</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>44452</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>45838.67858796296</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44546</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>45615</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44150</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>45888.55305555555</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>44162</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44510.94930555556</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>44728</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44904</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>45617</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>45735</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>44553</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>44966</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44895</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>45310</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>45169</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45624</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>44879</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>45632</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>44174</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45595</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45764</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>45527</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
         <v>45849.42818287037</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>45621</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>45526</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45313</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>45216.67748842593</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>44841</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44867</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>44757</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45636</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45216</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>45511.55719907407</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44757</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>44540</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>44873</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>45271</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45453.63133101852</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>45656.54600694445</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45233</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45821.44299768518</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>45692</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45372</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>45887.6989699074</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>45630</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>44355</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>44161</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>44378</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>44524</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44316</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>44230</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44209</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44757</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45643.53393518519</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44540</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45595</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45268</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45793.4189699074</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>45348</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45656.59703703703</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45804.60005787037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45805</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45863.59111111111</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>45647.6565625</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>45877.67787037037</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>44279</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>44879</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>45869</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45223</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45554</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45376</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45862</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>44099</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44154</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>44090</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>44512</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44445</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>44512</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>44445</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>44728</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>44207</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44797</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44742</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45750.42127314815</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>44377</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>45123</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45685.78776620371</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45407</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>44568</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44683</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>44308</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45243</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>45595</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45622</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45098</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>45079</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>44568</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>45271</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45595</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45595</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>44568</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>45180</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>44075</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45635</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45645.67945601852</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45020</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45819.65796296296</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>45862.4257175926</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45686.27208333334</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45862.43403935185</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>44540</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>45826.45174768518</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45609</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45595</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45609</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>44630</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>45839.60460648148</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45838</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45838.67815972222</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>45841.52454861111</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45467</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45153</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>44603</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45695.42197916667</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>45847.46962962963</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>45847.51078703703</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45700</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45736.42743055556</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>45702.47149305556</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>44313</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>44113</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>44103</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>44102</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44214</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44371</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>44748.94689814815</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>44407</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44473.44813657407</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44256</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44473.508125</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44183</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44175</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>44679</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>44449</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44665</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>44173</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>44445</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>44494</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>44610</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44376.87497685185</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>44377.44767361111</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>44788</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>44285</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>44133</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>44263</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>44183</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>44183</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>44524</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>44370</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>44591</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>44123</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>44714.438125</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>44162</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>44090</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>44141</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24538,7 +24538,7 @@
         <v>44255</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>44533</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>44577.47756944445</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>44287</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>44749</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>44126.94510416667</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44831.37650462963</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44200</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44172</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>44512.94539351852</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>44369.41452546296</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>44271.43831018519</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>44502.94153935185</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>44312</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>44306</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>44788</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>44502</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>44207</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>44851.57131944445</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44209</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44209</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44243</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>44473</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44106</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>44466.53040509259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>44300</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>44539</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>44495</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>44495</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>44277.59521990741</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>44512</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>44172</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44337</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>44214</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>44693.41668981482</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>44502.94140046297</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>44139</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>44077</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>44473.53681712963</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>44714</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>44153</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44377</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44728.94420138889</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>44858</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>44151</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>44459</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>44382.92065972222</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44526</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44095</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44358.63585648148</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44214</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44524</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>44820</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44076</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44123</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>44610</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44337</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>44473.53013888889</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44459</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>44113</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44123</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>44697.94231481481</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>44519.63436342592</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44123</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44848</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44875.41104166667</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44169</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44214</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44705</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44279</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>44727</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44209</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44307.42378472222</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44468</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44284</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44470</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44447</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>45726.56341435185</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45460.44076388889</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>44470.39989583333</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45692.64298611111</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45538.68200231482</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>44118.98730324074</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45726.5827199074</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>45751.37320601852</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>45706</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>44939</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45554.59538194445</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45457.38799768518</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45246</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -29820,7 +29820,7 @@
         <v>44873</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>45750.60577546297</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45560.6599537037</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>44285</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30068,7 +30068,7 @@
         <v>44873</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>44875</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>44631</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45772.58283564815</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>45772.59200231481</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>45772.62052083333</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30410,7 +30410,7 @@
         <v>45713.36836805556</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45695.42418981482</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45254</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44848</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44400.37204861111</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>45090</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44972.55690972223</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>45618.54398148148</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>45022</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>45189.60987268519</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>45055</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>45310</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>45190</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>45601.38071759259</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>44370</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>44803</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>45758</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45550.66542824074</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45721.55653935186</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>45758.58943287037</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>45707.55246527777</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>45393</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>45107</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>44140</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>45411</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>45708</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>44938.93989583333</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>45588</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>44207</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>45042</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45532.58101851852</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>45618.53126157408</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>45618.53633101852</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32326,7 +32326,7 @@
         <v>45392</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44911</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45090</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44596</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>45748.36445601852</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>45748.37173611111</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>45510.58033564815</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>44908</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>44875</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45588</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>45695</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -32973,7 +32973,7 @@
         <v>45662</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33030,7 +33030,7 @@
         <v>45457.35388888889</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>44715.48863425926</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>45412.51260416667</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>44389</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>44186</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>45216</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>45119</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>45459.55150462963</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>45279</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>44686</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>45701.57363425926</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>44866</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>45749.38379629629</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45265.52887731481</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45713.59623842593</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -33905,7 +33905,7 @@
         <v>44847</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45639</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45649.4634375</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>45511.95109953704</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>45721.66456018519</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>44732</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>44732</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>45165.69965277778</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45719.37307870371</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>45432.54027777778</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>45720.60774305555</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>45226</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34599,7 +34599,7 @@
         <v>45758.66180555556</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -34656,7 +34656,7 @@
         <v>45713.38028935185</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>45253</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>44557</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45740.60405092593</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>45203</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45603.44815972223</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45123.61459490741</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45602</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44726</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45686.39777777778</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>45371</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>45693.67361111111</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>45694.43806712963</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>45706.59251157408</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>45180.6391087963</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>45484</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>45484</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>45770.64677083334</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>45687</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>45056</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44524</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45000</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>44516</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>44795</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>45189</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>45713.59952546296</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>45693.48239583334</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45713.60719907407</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>45670</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45386</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45630.47099537037</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>44214</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>44874</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44316</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>45467</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -36716,7 +36716,7 @@
         <v>45713.36561342593</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>45198.42734953704</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45231</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45638.81385416666</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>45600.433125</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45534.57745370371</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>45343.95162037037</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>45701</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>45278.65582175926</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45761.50909722222</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45716.55237268518</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>45694.65905092593</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45699</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45748.59744212963</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>44539</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45519.60965277778</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>45414.486875</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>44391</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -37782,7 +37782,7 @@
         <v>45247</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>45452.56446759259</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>45721.5113425926</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>44483.42253472222</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45748.3822337963</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45414.96341435185</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45748</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45602.38614583333</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45226</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45573.54893518519</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45608.43930555556</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45777</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>45777</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45777</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>45527.39858796296</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -38667,7 +38667,7 @@
         <v>45712</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -38724,7 +38724,7 @@
         <v>45776</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -38781,7 +38781,7 @@
         <v>45600.58076388889</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>45715</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>44480</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -38957,7 +38957,7 @@
         <v>45369</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -39014,7 +39014,7 @@
         <v>45726.61520833334</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -39076,7 +39076,7 @@
         <v>45693</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>45561.61509259259</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>45779.42630787037</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39247,7 +39247,7 @@
         <v>45779.56659722222</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>45779.65980324074</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>44148</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45614.63697916667</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45757.56491898148</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39532,7 +39532,7 @@
         <v>45665.57373842593</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -39589,7 +39589,7 @@
         <v>45779.57626157408</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>45779.5674074074</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45692</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45779.63834490741</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>44887</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>45783.45121527778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>45783</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>45762.60907407408</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45688.38393518519</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -40117,7 +40117,7 @@
         <v>44550</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>45783</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40231,7 +40231,7 @@
         <v>45714.69212962963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>45554.59447916667</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>45525</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40412,7 +40412,7 @@
         <v>45583.52885416667</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>45750.42650462963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40526,7 +40526,7 @@
         <v>45232.46239583333</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>45783.43409722222</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>45491.44971064815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45696</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>45763.46918981482</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45783.44828703703</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45477.32728009259</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>44726</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45785</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45740</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45785.51092592593</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>45653.57240740741</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>45785.5403125</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>45165.70483796296</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41344,7 +41344,7 @@
         <v>45691.61996527778</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>44721.39003472222</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45642.6366087963</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45785.54635416667</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>44922</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45713.37111111111</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45785.52112268518</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>44855</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>44855</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>45204</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>45117</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>44188</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
         <v>45551.47325231481</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45371</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45786.65702546296</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>45362</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>45786.66140046297</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>45746</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45715</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45786.35219907408</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45638.81375</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>44285</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45411.4666087963</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>44510.9491087963</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45602.57827546296</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>45453</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45453.95237268518</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>44466.56642361111</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45238</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45740.60347222222</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45531.62141203704</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45140</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45789.58238425926</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45789.61349537037</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45250</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45786</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45243.37567129629</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>44228</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45203</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45786.64972222222</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45720.40268518519</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>45786</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -43793,7 +43793,7 @@
         <v>45260</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>45182</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>44391</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>44141</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45117</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45632</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -44140,7 +44140,7 @@
         <v>45833.49052083334</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>45833.49057870371</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>44757</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>45195</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>45204.40770833333</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>44711</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>45117</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45791.3162037037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -44616,7 +44616,7 @@
         <v>44750</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>45631.61869212963</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>44904</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>45791</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45833.63579861111</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>45695.60015046296</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>45693</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45245</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>45166</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>45467</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>44203</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45253,7 +45253,7 @@
         <v>45834.34737268519</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>45701.60901620371</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>45160.66704861111</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>45266</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45407</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45572</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45793.45204861111</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45594.463125</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45698.40146990741</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45608</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45686.33310185185</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45695.57171296296</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45300</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45362</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45488.94857638889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45643.64706018518</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45289</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>45706.55993055556</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>45698.4930787037</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>45572.45601851852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45378</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45282</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44582</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>45796.59857638889</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45145.95255787037</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45796.52836805556</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44847</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>45483</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>45392.95844907407</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45392</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
         <v>45656</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -47065,7 +47065,7 @@
         <v>45686.35247685185</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45798.63596064815</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -47189,7 +47189,7 @@
         <v>45749</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47246,7 +47246,7 @@
         <v>45791</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47303,7 +47303,7 @@
         <v>45474.69074074074</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45649.45143518518</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45621</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45475</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -47531,7 +47531,7 @@
         <v>45667.57217592592</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -47588,7 +47588,7 @@
         <v>44880</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45694.34268518518</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>45758.67065972222</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -47764,7 +47764,7 @@
         <v>45721.4546412037</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -47821,7 +47821,7 @@
         <v>44498</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -47878,7 +47878,7 @@
         <v>45238</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -47935,7 +47935,7 @@
         <v>44390</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -47992,7 +47992,7 @@
         <v>45670</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>44427</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -48106,7 +48106,7 @@
         <v>45623.48571759259</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45274</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45257</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>44379.59675925926</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45484</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48396,7 +48396,7 @@
         <v>45798.63611111111</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48458,7 +48458,7 @@
         <v>44658</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -48515,7 +48515,7 @@
         <v>45684.62510416667</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -48577,7 +48577,7 @@
         <v>45746</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -48639,7 +48639,7 @@
         <v>45726.37850694444</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>45121</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45803.69828703703</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45800.64319444444</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45751.6877662037</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45803.6837962963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>45800.37061342593</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45800.65177083333</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45803</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45679.70027777777</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45800</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45800.57129629629</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45800.57461805556</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45800</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49452,7 +49452,7 @@
         <v>45800.56810185185</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45408</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>45432.36971064815</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45231</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45721</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>45692</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -49861,7 +49861,7 @@
         <v>45721</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -49918,7 +49918,7 @@
         <v>45245</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -49975,7 +49975,7 @@
         <v>45602</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -50032,7 +50032,7 @@
         <v>44971</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -50089,7 +50089,7 @@
         <v>45687</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>44901.59349537037</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50213,7 +50213,7 @@
         <v>45695.61160879629</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>45671.59114583334</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
         <v>45180</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45805</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45805.54185185185</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45698.39486111111</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45807.58930555556</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45466.62116898148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45615.61121527778</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -50741,7 +50741,7 @@
         <v>45246</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -50798,7 +50798,7 @@
         <v>45751.3734837963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -50855,7 +50855,7 @@
         <v>45751.57877314815</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -50912,7 +50912,7 @@
         <v>45807.56728009259</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>45261</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -51026,7 +51026,7 @@
         <v>45406.05033564815</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>44179</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>45733</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         <v>44349</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45607</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45737.36873842592</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>45810.31376157407</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         <v>45810.32105324074</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>45601.33743055556</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -51554,7 +51554,7 @@
         <v>45176</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -51616,7 +51616,7 @@
         <v>45811.67769675926</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -51673,7 +51673,7 @@
         <v>44334</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -51730,7 +51730,7 @@
         <v>44498</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -51787,7 +51787,7 @@
         <v>45190</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -51844,7 +51844,7 @@
         <v>45853.6156712963</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -51906,7 +51906,7 @@
         <v>45180</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>44757</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>45471.63390046296</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -52087,7 +52087,7 @@
         <v>45597.49638888889</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -52144,7 +52144,7 @@
         <v>44858</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52201,7 +52201,7 @@
         <v>45635</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52258,7 +52258,7 @@
         <v>45245.5478125</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>45811.69912037037</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52377,7 +52377,7 @@
         <v>45118.94061342593</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52434,7 +52434,7 @@
         <v>45694.64416666667</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45610.36561342593</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>45764.40834490741</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45117</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45586</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>44901.54615740741</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -52786,7 +52786,7 @@
         <v>44865</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>45552.67611111111</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45099.37211805556</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45109.44534722222</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -53019,7 +53019,7 @@
         <v>45701</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -53076,7 +53076,7 @@
         <v>44741</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -53133,7 +53133,7 @@
         <v>45763.44112268519</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>45615.61302083333</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>44540</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53309,7 +53309,7 @@
         <v>45746.79134259259</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53366,7 +53366,7 @@
         <v>44154</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53423,7 +53423,7 @@
         <v>45496.41289351852</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45474.3981712963</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45811.54760416667</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45719.32584490741</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45607.63211805555</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>45855.61193287037</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45373</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45279</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>45785.67431712963</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>45709</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45474.69155092593</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45713</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -54127,7 +54127,7 @@
         <v>45173</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45813.44443287037</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45721.54896990741</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45813.46969907408</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45813.68361111111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45854.66518518519</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45812.32266203704</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45309.94650462963</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45560.38056712963</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45300</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45854.65378472222</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45814</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45699.66576388889</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -54883,7 +54883,7 @@
         <v>45700.30092592593</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>45097</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45635.67949074074</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45226</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45708</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>45814</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55240,7 +55240,7 @@
         <v>45565.32449074074</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55297,7 +55297,7 @@
         <v>45614.63606481482</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55354,7 +55354,7 @@
         <v>45614.63701388889</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>45056</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55468,7 +55468,7 @@
         <v>45817.56761574074</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>45454.57899305555</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>45815.50844907408</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>45499.48672453704</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45398</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -55753,7 +55753,7 @@
         <v>45216.3965625</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         <v>45239.9681712963</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -55867,7 +55867,7 @@
         <v>44788</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -55924,7 +55924,7 @@
         <v>44830</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -55986,7 +55986,7 @@
         <v>45152</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>45818.3293287037</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -56110,7 +56110,7 @@
         <v>45818.33532407408</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56172,7 +56172,7 @@
         <v>45818.34833333334</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56234,7 +56234,7 @@
         <v>45672.53806712963</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56296,7 +56296,7 @@
         <v>45674</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56353,7 +56353,7 @@
         <v>44600.37212962963</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56410,7 +56410,7 @@
         <v>45764.55260416667</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56467,7 +56467,7 @@
         <v>45666.65987268519</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56524,7 +56524,7 @@
         <v>45818.34473379629</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -56586,7 +56586,7 @@
         <v>45446.68733796296</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -56648,7 +56648,7 @@
         <v>45818.36246527778</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -56710,7 +56710,7 @@
         <v>44522.46662037037</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -56767,7 +56767,7 @@
         <v>45700.6833912037</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -56824,7 +56824,7 @@
         <v>44331</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -56881,7 +56881,7 @@
         <v>45818.34474537037</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -56943,7 +56943,7 @@
         <v>45818.37056712963</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -57005,7 +57005,7 @@
         <v>45139</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -57067,7 +57067,7 @@
         <v>45861.6841087963</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>45863.45778935185</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57186,7 +57186,7 @@
         <v>45614.63575231482</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57243,7 +57243,7 @@
         <v>45820</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57300,7 +57300,7 @@
         <v>45820</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57357,7 +57357,7 @@
         <v>45820.36512731481</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57414,7 +57414,7 @@
         <v>45820</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57471,7 +57471,7 @@
         <v>45863.58127314815</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57533,7 +57533,7 @@
         <v>45547.42736111111</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -57590,7 +57590,7 @@
         <v>45820.36498842593</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -57647,7 +57647,7 @@
         <v>45820.36506944444</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -57704,7 +57704,7 @@
         <v>45862.34668981482</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -57766,7 +57766,7 @@
         <v>45862.42901620371</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -57823,7 +57823,7 @@
         <v>45821.39026620371</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -57880,7 +57880,7 @@
         <v>44893</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -57937,7 +57937,7 @@
         <v>45686</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -57994,7 +57994,7 @@
         <v>45112</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -58051,7 +58051,7 @@
         <v>45860</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -58108,7 +58108,7 @@
         <v>45820.47200231482</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58170,7 +58170,7 @@
         <v>45764.47059027778</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58227,7 +58227,7 @@
         <v>45820.36233796296</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58284,7 +58284,7 @@
         <v>45863</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58341,7 +58341,7 @@
         <v>45747.47025462963</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58403,7 +58403,7 @@
         <v>44764</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58460,7 +58460,7 @@
         <v>44764</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58517,7 +58517,7 @@
         <v>45036</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -58574,7 +58574,7 @@
         <v>45036</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -58631,7 +58631,7 @@
         <v>45586.53618055556</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -58688,7 +58688,7 @@
         <v>45867.46560185185</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -58745,7 +58745,7 @@
         <v>45615.59521990741</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -58802,7 +58802,7 @@
         <v>45723.50841435185</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -58859,7 +58859,7 @@
         <v>45867.41707175926</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -58916,7 +58916,7 @@
         <v>44834.95019675926</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -58978,7 +58978,7 @@
         <v>45448.67574074074</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -59040,7 +59040,7 @@
         <v>45600.49616898148</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -59097,7 +59097,7 @@
         <v>45695.4046875</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59159,7 +59159,7 @@
         <v>45348</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59216,7 +59216,7 @@
         <v>45370.94969907407</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59278,7 +59278,7 @@
         <v>45721.45563657407</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59340,7 +59340,7 @@
         <v>45216</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59397,7 +59397,7 @@
         <v>45572</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         <v>45209</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         <v>45826.4705787037</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -59578,7 +59578,7 @@
         <v>45082</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -59640,7 +59640,7 @@
         <v>45700.56194444445</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -59702,7 +59702,7 @@
         <v>45574.43403935185</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -59759,7 +59759,7 @@
         <v>45869.34439814815</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -59821,7 +59821,7 @@
         <v>45700.27895833334</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -59883,7 +59883,7 @@
         <v>45827.34488425926</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -59945,7 +59945,7 @@
         <v>45096</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -60002,7 +60002,7 @@
         <v>44211</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -60059,7 +60059,7 @@
         <v>45560.45841435185</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -60121,7 +60121,7 @@
         <v>44965</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60183,7 +60183,7 @@
         <v>45870</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60240,7 +60240,7 @@
         <v>45112</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60297,7 +60297,7 @@
         <v>45601</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60354,7 +60354,7 @@
         <v>45875.51046296296</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60411,7 +60411,7 @@
         <v>45740</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60468,7 +60468,7 @@
         <v>45696.3440162037</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60525,7 +60525,7 @@
         <v>45217</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -60582,7 +60582,7 @@
         <v>45698.57129629629</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -60639,7 +60639,7 @@
         <v>44140</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -60696,7 +60696,7 @@
         <v>45832.34630787037</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -60758,7 +60758,7 @@
         <v>45832.53225694445</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -60820,7 +60820,7 @@
         <v>45377</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -60877,7 +60877,7 @@
         <v>45832</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -60934,7 +60934,7 @@
         <v>45833.34490740741</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -60996,7 +60996,7 @@
         <v>45551.34414351852</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -61053,7 +61053,7 @@
         <v>45342</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -61115,7 +61115,7 @@
         <v>45579.66459490741</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61172,7 +61172,7 @@
         <v>45833.36050925926</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61229,7 +61229,7 @@
         <v>45833.36083333333</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61286,7 +61286,7 @@
         <v>45720</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61343,7 +61343,7 @@
         <v>45832.53935185185</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61405,7 +61405,7 @@
         <v>45833.36111111111</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61462,7 +61462,7 @@
         <v>45834.61517361111</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61524,7 +61524,7 @@
         <v>45050</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -61586,7 +61586,7 @@
         <v>45055</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -61643,7 +61643,7 @@
         <v>45705.33446759259</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -61705,7 +61705,7 @@
         <v>45602.39862268518</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -61762,7 +61762,7 @@
         <v>45602.42878472222</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -61819,7 +61819,7 @@
         <v>45118</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -61876,7 +61876,7 @@
         <v>45695.47791666666</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>45705</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -61990,7 +61990,7 @@
         <v>45835.42712962963</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -62047,7 +62047,7 @@
         <v>45547.42732638889</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -62104,7 +62104,7 @@
         <v>45554</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -62166,7 +62166,7 @@
         <v>44206</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62223,7 +62223,7 @@
         <v>45713.59163194444</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62285,7 +62285,7 @@
         <v>45608.86341435185</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62342,7 +62342,7 @@
         <v>45251.65152777778</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62399,7 +62399,7 @@
         <v>45877.46555555556</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62456,7 +62456,7 @@
         <v>45056</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62513,7 +62513,7 @@
         <v>45182</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -62570,7 +62570,7 @@
         <v>45485</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -62627,7 +62627,7 @@
         <v>45698.45653935185</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -62684,7 +62684,7 @@
         <v>44592</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -62741,7 +62741,7 @@
         <v>45097</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -62798,7 +62798,7 @@
         <v>44362</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -62855,7 +62855,7 @@
         <v>45607</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -62912,7 +62912,7 @@
         <v>45476</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -62969,7 +62969,7 @@
         <v>45608.61606481481</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -63026,7 +63026,7 @@
         <v>44741</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -63083,7 +63083,7 @@
         <v>45316</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -63140,7 +63140,7 @@
         <v>45748.57269675926</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63197,7 +63197,7 @@
         <v>45401.59133101852</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>45392</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63316,7 +63316,7 @@
         <v>44133</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63373,7 +63373,7 @@
         <v>45560</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63435,7 +63435,7 @@
         <v>45713.59741898148</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63497,7 +63497,7 @@
         <v>45876</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>45876</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -63611,7 +63611,7 @@
         <v>45834.34726851852</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -63673,7 +63673,7 @@
         <v>44970</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -63730,7 +63730,7 @@
         <v>45555.43584490741</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>44544.49326388889</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -63844,7 +63844,7 @@
         <v>45877.57403935185</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>45418.94616898148</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -63963,7 +63963,7 @@
         <v>45457.55922453704</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -64025,7 +64025,7 @@
         <v>45401.59810185185</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -64082,7 +64082,7 @@
         <v>45839.61541666667</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -64144,7 +64144,7 @@
         <v>45880</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64201,7 +64201,7 @@
         <v>45839.61594907408</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64263,7 +64263,7 @@
         <v>45719</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64320,7 +64320,7 @@
         <v>45764</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64377,7 +64377,7 @@
         <v>45614.65925925926</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64434,7 +64434,7 @@
         <v>45839.72320601852</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45035</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64548,7 +64548,7 @@
         <v>45881.39909722222</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -64605,7 +64605,7 @@
         <v>44273</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -64662,7 +64662,7 @@
         <v>45836.34413194445</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -64724,7 +64724,7 @@
         <v>45881.40521990741</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -64781,7 +64781,7 @@
         <v>45580.36991898148</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -64843,7 +64843,7 @@
         <v>45881.51081018519</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -64905,7 +64905,7 @@
         <v>44887</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -64967,7 +64967,7 @@
         <v>45839.61582175926</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -65029,7 +65029,7 @@
         <v>45478.42063657408</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -65086,7 +65086,7 @@
         <v>45378</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -65143,7 +65143,7 @@
         <v>45566.51501157408</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         <v>45760.81083333334</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65257,7 +65257,7 @@
         <v>45642.63666666667</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65314,7 +65314,7 @@
         <v>45839.61563657408</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65376,7 +65376,7 @@
         <v>45840.58494212963</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65433,7 +65433,7 @@
         <v>45133</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65490,7 +65490,7 @@
         <v>45878</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65552,7 +65552,7 @@
         <v>45687.48931712963</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -65609,7 +65609,7 @@
         <v>45882.34510416666</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -65671,7 +65671,7 @@
         <v>45883.61028935185</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -65728,7 +65728,7 @@
         <v>45090</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -65785,7 +65785,7 @@
         <v>44818</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -65842,7 +65842,7 @@
         <v>45841.46925925926</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -65904,7 +65904,7 @@
         <v>45195</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -65961,7 +65961,7 @@
         <v>45841.43987268519</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -66018,7 +66018,7 @@
         <v>45882.69851851852</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -66080,7 +66080,7 @@
         <v>45841.67834490741</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -66142,7 +66142,7 @@
         <v>45203.46523148148</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66199,7 +66199,7 @@
         <v>45602.65599537037</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66256,7 +66256,7 @@
         <v>45603.28460648148</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66318,7 +66318,7 @@
         <v>45840.40717592592</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66380,7 +66380,7 @@
         <v>45883.37883101852</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66437,7 +66437,7 @@
         <v>45452.55271990741</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66499,7 +66499,7 @@
         <v>44988.94056712963</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -66561,7 +66561,7 @@
         <v>45750.6447800926</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -66623,7 +66623,7 @@
         <v>45842</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -66680,7 +66680,7 @@
         <v>45887.44883101852</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -66737,7 +66737,7 @@
         <v>45225.60212962963</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -66794,7 +66794,7 @@
         <v>45643.65354166667</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -66851,7 +66851,7 @@
         <v>45887.55252314815</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -66913,7 +66913,7 @@
         <v>45842.6099537037</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -66970,7 +66970,7 @@
         <v>45842</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -67027,7 +67027,7 @@
         <v>45887.58372685185</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -67084,7 +67084,7 @@
         <v>44792.27644675926</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -67141,7 +67141,7 @@
         <v>45887.59064814815</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67198,7 +67198,7 @@
         <v>45842.39587962963</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67260,7 +67260,7 @@
         <v>44151</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67317,7 +67317,7 @@
         <v>44377</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67374,7 +67374,7 @@
         <v>45695.45013888889</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67436,7 +67436,7 @@
         <v>45620.67667824074</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67493,7 +67493,7 @@
         <v>44974</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -67555,7 +67555,7 @@
         <v>45842.40013888889</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -67617,7 +67617,7 @@
         <v>45554.59550925926</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -67674,7 +67674,7 @@
         <v>45257</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -67731,7 +67731,7 @@
         <v>45182</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -67788,7 +67788,7 @@
         <v>45168</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -67845,7 +67845,7 @@
         <v>45692.60364583333</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -67902,7 +67902,7 @@
         <v>45552.57210648148</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -67959,7 +67959,7 @@
         <v>45876</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -68016,7 +68016,7 @@
         <v>45467</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -68073,7 +68073,7 @@
         <v>44488.47928240741</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -68130,7 +68130,7 @@
         <v>45889.37520833333</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68192,7 +68192,7 @@
         <v>45751.28243055556</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68254,7 +68254,7 @@
         <v>44825</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68311,7 +68311,7 @@
         <v>45477.35225694445</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68373,7 +68373,7 @@
         <v>45889.38626157407</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68435,7 +68435,7 @@
         <v>45847.51106481482</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68492,7 +68492,7 @@
         <v>45369</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -68549,7 +68549,7 @@
         <v>45203.44248842593</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -68606,7 +68606,7 @@
         <v>45370</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -68663,7 +68663,7 @@
         <v>45243.33297453704</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -68725,7 +68725,7 @@
         <v>45847.65717592592</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -68787,7 +68787,7 @@
         <v>45847.46462962963</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -68844,7 +68844,7 @@
         <v>45707.33935185185</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -68906,7 +68906,7 @@
         <v>45888.72445601852</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -68968,7 +68968,7 @@
         <v>45888.72766203704</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -69030,7 +69030,7 @@
         <v>45608.61923611111</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -69087,7 +69087,7 @@
         <v>45848</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -69144,7 +69144,7 @@
         <v>45848.60371527778</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -69201,7 +69201,7 @@
         <v>45848.48070601852</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -69258,7 +69258,7 @@
         <v>45849.4525462963</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -69315,7 +69315,7 @@
         <v>45704.71069444445</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -69377,7 +69377,7 @@
         <v>45630</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -69434,7 +69434,7 @@
         <v>45817</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -69491,7 +69491,7 @@
         <v>45634.7925</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -69548,7 +69548,7 @@
         <v>45634.79854166666</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -69605,7 +69605,7 @@
         <v>45453.45515046296</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -69662,7 +69662,7 @@
         <v>45714.34859953704</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -69744,7 +69744,7 @@
         <v>45849.3859837963</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -69806,7 +69806,7 @@
         <v>45744.59894675926</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -69868,7 +69868,7 @@
         <v>44456</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -69925,7 +69925,7 @@
         <v>45478.60708333334</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -69982,7 +69982,7 @@
         <v>44504</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -70039,7 +70039,7 @@
         <v>45415.45006944444</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -70096,7 +70096,7 @@
         <v>44961</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -70153,7 +70153,7 @@
         <v>45686.32671296296</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -70215,7 +70215,7 @@
         <v>45660.49618055556</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -70272,7 +70272,7 @@
         <v>45561.61515046296</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -70329,7 +70329,7 @@
         <v>45560.69164351852</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -70386,7 +70386,7 @@
         <v>45700.37127314815</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -70443,7 +70443,7 @@
         <v>45700.37481481482</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -70505,7 +70505,7 @@
         <v>45692.58106481482</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -70562,7 +70562,7 @@
         <v>45565.33152777778</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -70619,7 +70619,7 @@
         <v>45635.39820601852</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -70676,7 +70676,7 @@
         <v>45593.38568287037</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -70733,7 +70733,7 @@
         <v>45586.46927083333</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -70790,7 +70790,7 @@
         <v>45532.48732638889</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -70847,7 +70847,7 @@
         <v>44601.35342592592</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -70904,7 +70904,7 @@
         <v>45469</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -70961,7 +70961,7 @@
         <v>44335</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -71018,7 +71018,7 @@
         <v>45474</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -71075,7 +71075,7 @@
         <v>45244</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -71132,7 +71132,7 @@
         <v>45676</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -71189,7 +71189,7 @@
         <v>45446.47634259259</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -71251,7 +71251,7 @@
         <v>45649.38149305555</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -71308,7 +71308,7 @@
         <v>45324</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -71365,7 +71365,7 @@
         <v>45744</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -71422,7 +71422,7 @@
         <v>44849.8044212963</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>

--- a/Översikt KROKOM.xlsx
+++ b/Översikt KROKOM.xlsx
@@ -567,7 +567,7 @@
         <v>45716</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44522</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45348</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44165</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45384</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>45254</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>45709</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>45637</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45603</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44378</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45845</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45478</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45121</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>44323</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>44565</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45646</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>45155</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>45453</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>44363</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45630</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45887.44892361111</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45219</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>45625</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>45041</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>45790</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>45663</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>45553</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>45849</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>45596.5093287037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>45428</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45644</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>44306.52587962963</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>44575</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45792</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>44581</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>45475</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>44326</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>44780</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>45784.56270833333</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44323</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>45691</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>44475</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45551</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>44231</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45646</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45646</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45041</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>45719.52238425926</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>45639</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>44795</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45534</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>45488.56961805555</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>45512</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>45219</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>45580</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>45527</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45454</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>44498</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>45643</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44118</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>44552</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>45181</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44308</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>45457</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>44133</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>45169</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>44698</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>44585</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>45267</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>45316</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>45475</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45149</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44500</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>45839.68914351852</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>45616</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44271</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44265</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>44534</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44494</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44326</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>45474</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44477</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44797</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44834</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45180</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>45370</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>45252</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>45832.38581018519</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>45581</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>45755.47527777778</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44183</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>44515</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45726.46192129629</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44903</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>45532</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>44540</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45079</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45551</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45874.67765046296</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>44452</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>45838.67858796296</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44546</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>45615</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44150</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>45888.55305555555</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>44162</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44510.94930555556</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>44728</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44904</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>45617</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>45735</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>44553</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>44966</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44895</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>45310</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>45169</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45624</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>44879</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>45632</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>44174</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45595</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45764</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>45527</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
         <v>45849.42818287037</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>45621</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>45526</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45313</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>45216.67748842593</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>44841</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44867</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>44757</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45636</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45216</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>45511.55719907407</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44757</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>44540</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>44873</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>45271</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45453.63133101852</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>45656.54600694445</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45233</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45821.44299768518</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>45692</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45372</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>45887.6989699074</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>45630</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>44355</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>44161</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>44378</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>44524</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44316</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>44230</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44209</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44757</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45643.53393518519</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44540</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45595</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45268</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45793.4189699074</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>45348</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45656.59703703703</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45804.60005787037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45805</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45863.59111111111</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>45647.6565625</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>45877.67787037037</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>44279</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>44879</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>45869</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45223</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45554</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45376</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45862</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>44099</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44154</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>44090</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>44512</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44445</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>44512</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>44445</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>44728</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>44207</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44797</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44742</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45750.42127314815</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>44377</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>45123</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45685.78776620371</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45407</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>44568</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44683</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>44308</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45243</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>45595</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45622</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45098</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>45079</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>44568</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>45271</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45595</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45595</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>44568</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>45180</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>44075</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45635</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45645.67945601852</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45020</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45819.65796296296</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>45862.4257175926</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45686.27208333334</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45862.43403935185</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>44540</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>45826.45174768518</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45609</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45595</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45609</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>44630</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>45839.60460648148</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45838</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45838.67815972222</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>45841.52454861111</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45467</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45153</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>44603</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45695.42197916667</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>45847.46962962963</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>45847.51078703703</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45700</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45736.42743055556</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>45702.47149305556</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>44313</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>44113</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>44103</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>44102</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44214</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44371</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>44748.94689814815</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>44407</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44473.44813657407</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44256</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44473.508125</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44183</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44175</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>44679</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>44449</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44665</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>44173</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>44445</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>44494</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>44610</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44376.87497685185</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>44377.44767361111</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>44788</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>44285</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>44133</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>44263</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>44183</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>44183</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>44524</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>44370</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>44591</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>44123</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>44714.438125</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>44162</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>44090</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>44141</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24538,7 +24538,7 @@
         <v>44255</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>44533</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>44577.47756944445</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>44287</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>44749</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>44126.94510416667</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44831.37650462963</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44200</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44172</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>44512.94539351852</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>44369.41452546296</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>44271.43831018519</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>44502.94153935185</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>44312</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>44306</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>44788</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>44502</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>44207</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>44851.57131944445</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44209</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44209</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44243</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>44473</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44106</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>44466.53040509259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>44300</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>44539</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>44495</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>44495</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>44277.59521990741</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>44512</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>44172</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44337</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>44214</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>44693.41668981482</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>44502.94140046297</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>44139</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>44077</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>44473.53681712963</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>44714</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>44153</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44377</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44728.94420138889</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>44858</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>44151</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>44459</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>44382.92065972222</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44526</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44095</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44358.63585648148</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44214</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44524</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>44820</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44076</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44123</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>44610</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44337</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>44473.53013888889</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44459</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>44113</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44123</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>44697.94231481481</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>44519.63436342592</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44123</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44848</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44875.41104166667</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44169</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44214</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44705</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44279</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>44727</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44209</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44307.42378472222</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44468</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44284</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44470</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44447</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>45726.56341435185</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45460.44076388889</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>44470.39989583333</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45692.64298611111</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45538.68200231482</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>44118.98730324074</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45726.5827199074</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>45751.37320601852</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>45706</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>44939</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45554.59538194445</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45457.38799768518</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45246</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -29820,7 +29820,7 @@
         <v>44873</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>45750.60577546297</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45560.6599537037</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>44285</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30068,7 +30068,7 @@
         <v>44873</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>44875</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>44631</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45772.58283564815</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>45772.59200231481</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>45772.62052083333</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30410,7 +30410,7 @@
         <v>45713.36836805556</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45695.42418981482</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45254</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44848</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44400.37204861111</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>45090</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44972.55690972223</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>45618.54398148148</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>45022</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>45189.60987268519</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>45055</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>45310</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>45190</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>45601.38071759259</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>44370</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>44803</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>45758</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45550.66542824074</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45721.55653935186</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>45758.58943287037</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>45707.55246527777</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>45393</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>45107</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>44140</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>45411</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>45708</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>44938.93989583333</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>45588</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>44207</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>45042</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45532.58101851852</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>45618.53126157408</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>45618.53633101852</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32326,7 +32326,7 @@
         <v>45392</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44911</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45090</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44596</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>45748.36445601852</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>45748.37173611111</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>45510.58033564815</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>44908</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>44875</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45588</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>45695</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -32973,7 +32973,7 @@
         <v>45662</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33030,7 +33030,7 @@
         <v>45457.35388888889</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>44715.48863425926</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>45412.51260416667</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>44389</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>44186</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>45216</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>45119</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>45459.55150462963</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>45279</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>44686</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>45701.57363425926</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>44866</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>45749.38379629629</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45265.52887731481</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45713.59623842593</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -33905,7 +33905,7 @@
         <v>44847</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45639</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45649.4634375</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>45511.95109953704</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>45721.66456018519</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>44732</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>44732</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>45165.69965277778</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45719.37307870371</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>45432.54027777778</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>45720.60774305555</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>45226</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34599,7 +34599,7 @@
         <v>45758.66180555556</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -34656,7 +34656,7 @@
         <v>45713.38028935185</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>45253</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>44557</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45740.60405092593</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>45203</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45603.44815972223</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45123.61459490741</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45602</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44726</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45686.39777777778</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>45371</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>45693.67361111111</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>45694.43806712963</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>45706.59251157408</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>45180.6391087963</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>45484</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>45484</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>45770.64677083334</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>45687</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>45056</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44524</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45000</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>44516</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>44795</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>45189</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>45713.59952546296</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>45693.48239583334</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45713.60719907407</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>45670</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45386</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45630.47099537037</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>44214</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>44874</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44316</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>45467</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -36716,7 +36716,7 @@
         <v>45713.36561342593</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>45198.42734953704</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45231</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45638.81385416666</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>45600.433125</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45534.57745370371</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>45343.95162037037</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>45701</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>45278.65582175926</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45761.50909722222</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45716.55237268518</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>45694.65905092593</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45699</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45748.59744212963</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>44539</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45519.60965277778</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>45414.486875</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>44391</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -37782,7 +37782,7 @@
         <v>45247</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>45452.56446759259</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>45721.5113425926</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>44483.42253472222</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45748.3822337963</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45414.96341435185</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45748</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45602.38614583333</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45226</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45573.54893518519</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45608.43930555556</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45777</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>45777</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45777</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>45527.39858796296</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -38667,7 +38667,7 @@
         <v>45712</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -38724,7 +38724,7 @@
         <v>45776</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -38781,7 +38781,7 @@
         <v>45600.58076388889</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>45715</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>44480</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -38957,7 +38957,7 @@
         <v>45369</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -39014,7 +39014,7 @@
         <v>45726.61520833334</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -39076,7 +39076,7 @@
         <v>45693</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>45561.61509259259</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>45779.42630787037</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39247,7 +39247,7 @@
         <v>45779.56659722222</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>45779.65980324074</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>44148</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45614.63697916667</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45757.56491898148</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39532,7 +39532,7 @@
         <v>45665.57373842593</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -39589,7 +39589,7 @@
         <v>45779.57626157408</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>45779.5674074074</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45692</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45779.63834490741</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>44887</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>45783.45121527778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>45783</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>45762.60907407408</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45688.38393518519</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -40117,7 +40117,7 @@
         <v>44550</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>45783</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40231,7 +40231,7 @@
         <v>45714.69212962963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>45554.59447916667</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>45525</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40412,7 +40412,7 @@
         <v>45583.52885416667</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>45750.42650462963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40526,7 +40526,7 @@
         <v>45232.46239583333</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>45783.43409722222</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>45491.44971064815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45696</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>45763.46918981482</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45783.44828703703</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45477.32728009259</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>44726</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45785</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45740</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45785.51092592593</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>45653.57240740741</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>45785.5403125</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>45165.70483796296</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41344,7 +41344,7 @@
         <v>45691.61996527778</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>44721.39003472222</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45642.6366087963</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45785.54635416667</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>44922</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45713.37111111111</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45785.52112268518</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>44855</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>44855</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>45204</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>45117</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>44188</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
         <v>45551.47325231481</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45371</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45786.65702546296</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>45362</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>45786.66140046297</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>45746</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45715</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45786.35219907408</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45638.81375</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>44285</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45411.4666087963</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>44510.9491087963</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45602.57827546296</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>45453</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45453.95237268518</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>44466.56642361111</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45238</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45740.60347222222</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45531.62141203704</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45140</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45789.58238425926</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45789.61349537037</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45250</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45786</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45243.37567129629</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>44228</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45203</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45786.64972222222</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45720.40268518519</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>45786</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -43793,7 +43793,7 @@
         <v>45260</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>45182</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>44391</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>44141</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45117</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45632</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -44140,7 +44140,7 @@
         <v>45833.49052083334</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>45833.49057870371</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>44757</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>45195</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>45204.40770833333</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>44711</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>45117</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45791.3162037037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -44616,7 +44616,7 @@
         <v>44750</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>45631.61869212963</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>44904</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>45791</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45833.63579861111</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>45695.60015046296</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>45693</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45245</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>45166</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>45467</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>44203</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45253,7 +45253,7 @@
         <v>45834.34737268519</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>45701.60901620371</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>45160.66704861111</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>45266</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45407</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45572</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45793.45204861111</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45594.463125</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45698.40146990741</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45608</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45686.33310185185</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45695.57171296296</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45300</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45362</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45488.94857638889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45643.64706018518</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45289</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>45706.55993055556</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>45698.4930787037</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>45572.45601851852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45378</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45282</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>44582</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>45796.59857638889</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45145.95255787037</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45796.52836805556</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44847</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>45483</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>45392.95844907407</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45392</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
         <v>45656</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -47065,7 +47065,7 @@
         <v>45686.35247685185</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45798.63596064815</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -47189,7 +47189,7 @@
         <v>45749</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47246,7 +47246,7 @@
         <v>45791</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47303,7 +47303,7 @@
         <v>45474.69074074074</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45649.45143518518</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45621</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45475</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -47531,7 +47531,7 @@
         <v>45667.57217592592</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -47588,7 +47588,7 @@
         <v>44880</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45694.34268518518</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>45758.67065972222</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -47764,7 +47764,7 @@
         <v>45721.4546412037</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -47821,7 +47821,7 @@
         <v>44498</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -47878,7 +47878,7 @@
         <v>45238</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -47935,7 +47935,7 @@
         <v>44390</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -47992,7 +47992,7 @@
         <v>45670</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>44427</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -48106,7 +48106,7 @@
         <v>45623.48571759259</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45274</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45257</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>44379.59675925926</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45484</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48396,7 +48396,7 @@
         <v>45798.63611111111</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48458,7 +48458,7 @@
         <v>44658</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -48515,7 +48515,7 @@
         <v>45684.62510416667</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -48577,7 +48577,7 @@
         <v>45746</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -48639,7 +48639,7 @@
         <v>45726.37850694444</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>45121</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45803.69828703703</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45800.64319444444</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45751.6877662037</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45803.6837962963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>45800.37061342593</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45800.65177083333</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45803</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45679.70027777777</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45800</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45800.57129629629</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45800.57461805556</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45800</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49452,7 +49452,7 @@
         <v>45800.56810185185</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45408</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>45432.36971064815</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45231</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45721</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>45692</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -49861,7 +49861,7 @@
         <v>45721</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -49918,7 +49918,7 @@
         <v>45245</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -49975,7 +49975,7 @@
         <v>45602</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -50032,7 +50032,7 @@
         <v>44971</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -50089,7 +50089,7 @@
         <v>45687</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>44901.59349537037</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50213,7 +50213,7 @@
         <v>45695.61160879629</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>45671.59114583334</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
         <v>45180</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45805</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45805.54185185185</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45698.39486111111</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45807.58930555556</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45466.62116898148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45615.61121527778</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -50741,7 +50741,7 @@
         <v>45246</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -50798,7 +50798,7 @@
         <v>45751.3734837963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -50855,7 +50855,7 @@
         <v>45751.57877314815</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -50912,7 +50912,7 @@
         <v>45807.56728009259</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>45261</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -51026,7 +51026,7 @@
         <v>45406.05033564815</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>44179</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>45733</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         <v>44349</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>45607</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45737.36873842592</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>45810.31376157407</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         <v>45810.32105324074</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>45601.33743055556</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -51554,7 +51554,7 @@
         <v>45176</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -51616,7 +51616,7 @@
         <v>45811.67769675926</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -51673,7 +51673,7 @@
         <v>44334</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -51730,7 +51730,7 @@
         <v>44498</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -51787,7 +51787,7 @@
         <v>45190</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -51844,7 +51844,7 @@
         <v>45853.6156712963</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -51906,7 +51906,7 @@
         <v>45180</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>44757</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>45471.63390046296</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -52087,7 +52087,7 @@
         <v>45597.49638888889</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -52144,7 +52144,7 @@
         <v>44858</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52201,7 +52201,7 @@
         <v>45635</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52258,7 +52258,7 @@
         <v>45245.5478125</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>45811.69912037037</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52377,7 +52377,7 @@
         <v>45118.94061342593</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52434,7 +52434,7 @@
         <v>45694.64416666667</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45610.36561342593</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>45764.40834490741</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45117</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45586</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>44901.54615740741</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -52786,7 +52786,7 @@
         <v>44865</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>45552.67611111111</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45099.37211805556</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45109.44534722222</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -53019,7 +53019,7 @@
         <v>45701</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -53076,7 +53076,7 @@
         <v>44741</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -53133,7 +53133,7 @@
         <v>45763.44112268519</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>45615.61302083333</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>44540</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53309,7 +53309,7 @@
         <v>45746.79134259259</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53366,7 +53366,7 @@
         <v>44154</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53423,7 +53423,7 @@
         <v>45496.41289351852</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45474.3981712963</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45811.54760416667</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45719.32584490741</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45607.63211805555</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>45855.61193287037</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45373</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45279</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>45785.67431712963</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>45709</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45474.69155092593</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45713</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -54127,7 +54127,7 @@
         <v>45173</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45813.44443287037</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45721.54896990741</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45813.46969907408</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45813.68361111111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45854.66518518519</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45812.32266203704</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45309.94650462963</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45560.38056712963</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45300</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45854.65378472222</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45814</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45699.66576388889</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -54883,7 +54883,7 @@
         <v>45700.30092592593</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>45097</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45635.67949074074</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45226</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45708</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>45814</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55240,7 +55240,7 @@
         <v>45565.32449074074</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55297,7 +55297,7 @@
         <v>45614.63606481482</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55354,7 +55354,7 @@
         <v>45614.63701388889</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>45056</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55468,7 +55468,7 @@
         <v>45817.56761574074</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>45454.57899305555</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>45815.50844907408</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>45499.48672453704</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45398</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -55753,7 +55753,7 @@
         <v>45216.3965625</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         <v>45239.9681712963</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -55867,7 +55867,7 @@
         <v>44788</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -55924,7 +55924,7 @@
         <v>44830</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -55986,7 +55986,7 @@
         <v>45152</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>45818.3293287037</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -56110,7 +56110,7 @@
         <v>45818.33532407408</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56172,7 +56172,7 @@
         <v>45818.34833333334</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56234,7 +56234,7 @@
         <v>45672.53806712963</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56296,7 +56296,7 @@
         <v>45674</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56353,7 +56353,7 @@
         <v>44600.37212962963</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56410,7 +56410,7 @@
         <v>45764.55260416667</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56467,7 +56467,7 @@
         <v>45666.65987268519</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56524,7 +56524,7 @@
         <v>45818.34473379629</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -56586,7 +56586,7 @@
         <v>45446.68733796296</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -56648,7 +56648,7 @@
         <v>45818.36246527778</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -56710,7 +56710,7 @@
         <v>44522.46662037037</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -56767,7 +56767,7 @@
         <v>45700.6833912037</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -56824,7 +56824,7 @@
         <v>44331</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -56881,7 +56881,7 @@
         <v>45818.34474537037</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -56943,7 +56943,7 @@
         <v>45818.37056712963</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -57005,7 +57005,7 @@
         <v>45139</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -57067,7 +57067,7 @@
         <v>45861.6841087963</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>45863.45778935185</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57186,7 +57186,7 @@
         <v>45614.63575231482</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57243,7 +57243,7 @@
         <v>45820</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57300,7 +57300,7 @@
         <v>45820</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57357,7 +57357,7 @@
         <v>45820.36512731481</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57414,7 +57414,7 @@
         <v>45820</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57471,7 +57471,7 @@
         <v>45863.58127314815</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57533,7 +57533,7 @@
         <v>45547.42736111111</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -57590,7 +57590,7 @@
         <v>45820.36498842593</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -57647,7 +57647,7 @@
         <v>45820.36506944444</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -57704,7 +57704,7 @@
         <v>45862.34668981482</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -57766,7 +57766,7 @@
         <v>45862.42901620371</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -57823,7 +57823,7 @@
         <v>45821.39026620371</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -57880,7 +57880,7 @@
         <v>44893</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -57937,7 +57937,7 @@
         <v>45686</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -57994,7 +57994,7 @@
         <v>45112</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -58051,7 +58051,7 @@
         <v>45860</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -58108,7 +58108,7 @@
         <v>45820.47200231482</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58170,7 +58170,7 @@
         <v>45764.47059027778</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58227,7 +58227,7 @@
         <v>45820.36233796296</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58284,7 +58284,7 @@
         <v>45863</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58341,7 +58341,7 @@
         <v>45747.47025462963</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58403,7 +58403,7 @@
         <v>44764</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58460,7 +58460,7 @@
         <v>44764</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58517,7 +58517,7 @@
         <v>45036</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -58574,7 +58574,7 @@
         <v>45036</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -58631,7 +58631,7 @@
         <v>45586.53618055556</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -58688,7 +58688,7 @@
         <v>45867.46560185185</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -58745,7 +58745,7 @@
         <v>45615.59521990741</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -58802,7 +58802,7 @@
         <v>45723.50841435185</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -58859,7 +58859,7 @@
         <v>45867.41707175926</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -58916,7 +58916,7 @@
         <v>44834.95019675926</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -58978,7 +58978,7 @@
         <v>45448.67574074074</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -59040,7 +59040,7 @@
         <v>45600.49616898148</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -59097,7 +59097,7 @@
         <v>45695.4046875</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59159,7 +59159,7 @@
         <v>45348</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59216,7 +59216,7 @@
         <v>45370.94969907407</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59278,7 +59278,7 @@
         <v>45721.45563657407</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59340,7 +59340,7 @@
         <v>45216</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59397,7 +59397,7 @@
         <v>45572</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         <v>45209</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         <v>45826.4705787037</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -59578,7 +59578,7 @@
         <v>45082</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -59640,7 +59640,7 @@
         <v>45700.56194444445</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -59702,7 +59702,7 @@
         <v>45574.43403935185</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -59759,7 +59759,7 @@
         <v>45869.34439814815</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -59821,7 +59821,7 @@
         <v>45700.27895833334</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -59883,7 +59883,7 @@
         <v>45827.34488425926</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -59945,7 +59945,7 @@
         <v>45096</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -60002,7 +60002,7 @@
         <v>44211</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -60059,7 +60059,7 @@
         <v>45560.45841435185</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -60121,7 +60121,7 @@
         <v>44965</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60183,7 +60183,7 @@
         <v>45870</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60240,7 +60240,7 @@
         <v>45112</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60297,7 +60297,7 @@
         <v>45601</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60354,7 +60354,7 @@
         <v>45875.51046296296</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60411,7 +60411,7 @@
         <v>45740</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60468,7 +60468,7 @@
         <v>45696.3440162037</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60525,7 +60525,7 @@
         <v>45217</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -60582,7 +60582,7 @@
         <v>45698.57129629629</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -60639,7 +60639,7 @@
         <v>44140</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -60696,7 +60696,7 @@
         <v>45832.34630787037</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -60758,7 +60758,7 @@
         <v>45832.53225694445</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -60820,7 +60820,7 @@
         <v>45377</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -60877,7 +60877,7 @@
         <v>45832</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -60934,7 +60934,7 @@
         <v>45833.34490740741</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -60996,7 +60996,7 @@
         <v>45551.34414351852</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -61053,7 +61053,7 @@
         <v>45342</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -61115,7 +61115,7 @@
         <v>45579.66459490741</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61172,7 +61172,7 @@
         <v>45833.36050925926</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61229,7 +61229,7 @@
         <v>45833.36083333333</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61286,7 +61286,7 @@
         <v>45720</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61343,7 +61343,7 @@
         <v>45832.53935185185</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61405,7 +61405,7 @@
         <v>45833.36111111111</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61462,7 +61462,7 @@
         <v>45834.61517361111</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61524,7 +61524,7 @@
         <v>45050</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -61586,7 +61586,7 @@
         <v>45055</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -61643,7 +61643,7 @@
         <v>45705.33446759259</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -61705,7 +61705,7 @@
         <v>45602.39862268518</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -61762,7 +61762,7 @@
         <v>45602.42878472222</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -61819,7 +61819,7 @@
         <v>45118</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -61876,7 +61876,7 @@
         <v>45695.47791666666</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>45705</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -61990,7 +61990,7 @@
         <v>45835.42712962963</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -62047,7 +62047,7 @@
         <v>45547.42732638889</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -62104,7 +62104,7 @@
         <v>45554</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -62166,7 +62166,7 @@
         <v>44206</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62223,7 +62223,7 @@
         <v>45713.59163194444</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62285,7 +62285,7 @@
         <v>45608.86341435185</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62342,7 +62342,7 @@
         <v>45251.65152777778</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62399,7 +62399,7 @@
         <v>45877.46555555556</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62456,7 +62456,7 @@
         <v>45056</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62513,7 +62513,7 @@
         <v>45182</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -62570,7 +62570,7 @@
         <v>45485</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -62627,7 +62627,7 @@
         <v>45698.45653935185</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -62684,7 +62684,7 @@
         <v>44592</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -62741,7 +62741,7 @@
         <v>45097</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -62798,7 +62798,7 @@
         <v>44362</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -62855,7 +62855,7 @@
         <v>45607</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -62912,7 +62912,7 @@
         <v>45476</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -62969,7 +62969,7 @@
         <v>45608.61606481481</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -63026,7 +63026,7 @@
         <v>44741</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -63083,7 +63083,7 @@
         <v>45316</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -63140,7 +63140,7 @@
         <v>45748.57269675926</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63197,7 +63197,7 @@
         <v>45401.59133101852</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>45392</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63316,7 +63316,7 @@
         <v>44133</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63373,7 +63373,7 @@
         <v>45560</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63435,7 +63435,7 @@
         <v>45713.59741898148</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63497,7 +63497,7 @@
         <v>45876</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>45876</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -63611,7 +63611,7 @@
         <v>45834.34726851852</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -63673,7 +63673,7 @@
         <v>44970</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -63730,7 +63730,7 @@
         <v>45555.43584490741</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>44544.49326388889</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -63844,7 +63844,7 @@
         <v>45877.57403935185</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>45418.94616898148</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -63963,7 +63963,7 @@
         <v>45457.55922453704</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -64025,7 +64025,7 @@
         <v>45401.59810185185</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -64082,7 +64082,7 @@
         <v>45839.61541666667</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -64144,7 +64144,7 @@
         <v>45880</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64201,7 +64201,7 @@
         <v>45839.61594907408</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64263,7 +64263,7 @@
         <v>45719</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64320,7 +64320,7 @@
         <v>45764</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64377,7 +64377,7 @@
         <v>45614.65925925926</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64434,7 +64434,7 @@
         <v>45839.72320601852</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45035</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64548,7 +64548,7 @@
         <v>45881.39909722222</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -64605,7 +64605,7 @@
         <v>44273</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -64662,7 +64662,7 @@
         <v>45836.34413194445</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -64724,7 +64724,7 @@
         <v>45881.40521990741</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -64781,7 +64781,7 @@
         <v>45580.36991898148</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -64843,7 +64843,7 @@
         <v>45881.51081018519</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -64905,7 +64905,7 @@
         <v>44887</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -64967,7 +64967,7 @@
         <v>45839.61582175926</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -65029,7 +65029,7 @@
         <v>45478.42063657408</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -65086,7 +65086,7 @@
         <v>45378</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -65143,7 +65143,7 @@
         <v>45566.51501157408</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         <v>45760.81083333334</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65257,7 +65257,7 @@
         <v>45642.63666666667</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65314,7 +65314,7 @@
         <v>45839.61563657408</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65376,7 +65376,7 @@
         <v>45840.58494212963</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65433,7 +65433,7 @@
         <v>45133</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65490,7 +65490,7 @@
         <v>45878</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65552,7 +65552,7 @@
         <v>45687.48931712963</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -65609,7 +65609,7 @@
         <v>45882.34510416666</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -65671,7 +65671,7 @@
         <v>45883.61028935185</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -65728,7 +65728,7 @@
         <v>45090</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -65785,7 +65785,7 @@
         <v>44818</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -65842,7 +65842,7 @@
         <v>45841.46925925926</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -65904,7 +65904,7 @@
         <v>45195</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -65961,7 +65961,7 @@
         <v>45841.43987268519</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -66018,7 +66018,7 @@
         <v>45882.69851851852</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -66080,7 +66080,7 @@
         <v>45841.67834490741</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -66142,7 +66142,7 @@
         <v>45203.46523148148</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66199,7 +66199,7 @@
         <v>45602.65599537037</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66256,7 +66256,7 @@
         <v>45603.28460648148</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66318,7 +66318,7 @@
         <v>45840.40717592592</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66380,7 +66380,7 @@
         <v>45883.37883101852</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66437,7 +66437,7 @@
         <v>45452.55271990741</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66499,7 +66499,7 @@
         <v>44988.94056712963</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -66561,7 +66561,7 @@
         <v>45750.6447800926</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -66623,7 +66623,7 @@
         <v>45842</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -66680,7 +66680,7 @@
         <v>45887.44883101852</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -66737,7 +66737,7 @@
         <v>45225.60212962963</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -66794,7 +66794,7 @@
         <v>45643.65354166667</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -66851,7 +66851,7 @@
         <v>45887.55252314815</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -66913,7 +66913,7 @@
         <v>45842.6099537037</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -66970,7 +66970,7 @@
         <v>45842</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -67027,7 +67027,7 @@
         <v>45887.58372685185</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -67084,7 +67084,7 @@
         <v>44792.27644675926</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -67141,7 +67141,7 @@
         <v>45887.59064814815</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67198,7 +67198,7 @@
         <v>45842.39587962963</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67260,7 +67260,7 @@
         <v>44151</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67317,7 +67317,7 @@
         <v>44377</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67374,7 +67374,7 @@
         <v>45695.45013888889</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67436,7 +67436,7 @@
         <v>45620.67667824074</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67493,7 +67493,7 @@
         <v>44974</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -67555,7 +67555,7 @@
         <v>45842.40013888889</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -67617,7 +67617,7 @@
         <v>45554.59550925926</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -67674,7 +67674,7 @@
         <v>45257</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -67731,7 +67731,7 @@
         <v>45182</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -67788,7 +67788,7 @@
         <v>45168</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -67845,7 +67845,7 @@
         <v>45692.60364583333</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -67902,7 +67902,7 @@
         <v>45552.57210648148</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -67959,7 +67959,7 @@
         <v>45876</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -68016,7 +68016,7 @@
         <v>45467</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -68073,7 +68073,7 @@
         <v>44488.47928240741</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -68130,7 +68130,7 @@
         <v>45889.37520833333</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68192,7 +68192,7 @@
         <v>45751.28243055556</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68254,7 +68254,7 @@
         <v>44825</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68311,7 +68311,7 @@
         <v>45477.35225694445</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68373,7 +68373,7 @@
         <v>45889.38626157407</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68435,7 +68435,7 @@
         <v>45847.51106481482</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68492,7 +68492,7 @@
         <v>45369</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -68549,7 +68549,7 @@
         <v>45203.44248842593</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -68606,7 +68606,7 @@
         <v>45370</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -68663,7 +68663,7 @@
         <v>45243.33297453704</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -68725,7 +68725,7 @@
         <v>45847.65717592592</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -68787,7 +68787,7 @@
         <v>45847.46462962963</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -68844,7 +68844,7 @@
         <v>45707.33935185185</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -68906,7 +68906,7 @@
         <v>45888.72445601852</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -68968,7 +68968,7 @@
         <v>45888.72766203704</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -69030,7 +69030,7 @@
         <v>45608.61923611111</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -69087,7 +69087,7 @@
         <v>45848</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -69144,7 +69144,7 @@
         <v>45848.60371527778</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -69201,7 +69201,7 @@
         <v>45848.48070601852</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -69258,7 +69258,7 @@
         <v>45849.4525462963</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -69315,7 +69315,7 @@
         <v>45704.71069444445</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -69377,7 +69377,7 @@
         <v>45630</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -69434,7 +69434,7 @@
         <v>45817</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -69491,7 +69491,7 @@
         <v>45634.7925</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -69548,7 +69548,7 @@
         <v>45634.79854166666</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -69605,7 +69605,7 @@
         <v>45453.45515046296</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -69662,7 +69662,7 @@
         <v>45714.34859953704</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -69744,7 +69744,7 @@
         <v>45849.3859837963</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -69806,7 +69806,7 @@
         <v>45744.59894675926</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -69868,7 +69868,7 @@
         <v>44456</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -69925,7 +69925,7 @@
         <v>45478.60708333334</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -69982,7 +69982,7 @@
         <v>44504</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -70039,7 +70039,7 @@
         <v>45415.45006944444</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -70096,7 +70096,7 @@
         <v>44961</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -70153,7 +70153,7 @@
         <v>45686.32671296296</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -70215,7 +70215,7 @@
         <v>45660.49618055556</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -70272,7 +70272,7 @@
         <v>45561.61515046296</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -70329,7 +70329,7 @@
         <v>45560.69164351852</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -70386,7 +70386,7 @@
         <v>45700.37127314815</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -70443,7 +70443,7 @@
         <v>45700.37481481482</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -70505,7 +70505,7 @@
         <v>45692.58106481482</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -70562,7 +70562,7 @@
         <v>45565.33152777778</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -70619,7 +70619,7 @@
         <v>45635.39820601852</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -70676,7 +70676,7 @@
         <v>45593.38568287037</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -70733,7 +70733,7 @@
         <v>45586.46927083333</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -70790,7 +70790,7 @@
         <v>45532.48732638889</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -70847,7 +70847,7 @@
         <v>44601.35342592592</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -70904,7 +70904,7 @@
         <v>45469</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -70961,7 +70961,7 @@
         <v>44335</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -71018,7 +71018,7 @@
         <v>45474</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -71075,7 +71075,7 @@
         <v>45244</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -71132,7 +71132,7 @@
         <v>45676</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -71189,7 +71189,7 @@
         <v>45446.47634259259</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -71251,7 +71251,7 @@
         <v>45649.38149305555</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -71308,7 +71308,7 @@
         <v>45324</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -71365,7 +71365,7 @@
         <v>45744</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -71422,7 +71422,7 @@
         <v>44849.8044212963</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>

--- a/Översikt KROKOM.xlsx
+++ b/Översikt KROKOM.xlsx
@@ -567,7 +567,7 @@
         <v>45716</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44522</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45637</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45348</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44165</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>45384</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>45254</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>45709</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45603</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>44378</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>45845</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>45478</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>44323</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45121</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45155</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>45646</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>44565</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45887.44892361111</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>44363</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45219</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45453</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45630</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45625</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>45041</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45790</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>45553</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>45663</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>45849</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45644</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>45428</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>45596.5093287037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>44306.52587962963</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>44575</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>44326</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>45792</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>44581</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45475</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44780</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>44323</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>45691</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>45784.56270833333</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45646</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44231</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45646</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>44475</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>45551</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>45512</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45488.56961805555</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45534</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>45639</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>45719.52238425926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>44795</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>45041</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>45580</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>45527</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>45454</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>45643</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>45219</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44118</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44498</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44552</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>45457</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>45181</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>45169</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>44308</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44133</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44585</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>44698</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>44500</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>45316</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>45862.42901620371</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>45839.68914351852</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45616</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>45149</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>45267</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45475</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44271</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>44265</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>44534</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44494</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44326</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>45370</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44477</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>45180</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45862.43403935185</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>45862.4257175926</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>44834</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>45252</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45755.47527777778</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>45832.38581018519</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>44797</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>45581</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>45474</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44183</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>44515</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>44150</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45874.67765046296</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45838.67858796296</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>45888.55305555555</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45532</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>45551</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>45615</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>44903</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44546</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>44452</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>45079</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>44540</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45726.46192129629</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44162</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>44510.94930555556</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>44728</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>44895</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>45624</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>45169</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>44553</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45595</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>44904</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45764</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         <v>45527</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>45849.42818287037</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44174</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44966</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>44879</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45735</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45632</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>45621</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45310</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>45617</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45656.54600694445</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>45511.55719907407</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>44540</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45271</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>45453.63133101852</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45821.44299768518</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>45863.58127314815</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45216</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>45372</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>45636</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45887.6989699074</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45526</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45630</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>44757</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>45216.67748842593</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>44757</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>44873</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>44841</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45233</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>44867</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>45313</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45692</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>44355</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>44161</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>44378</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44524</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>44316</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44230</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44757</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45268</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45376</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45793.4189699074</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44540</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45804.60005787037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45554</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>44209</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45863.59111111111</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45348</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45877.67787037037</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>45869</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45862</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45595</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45896.34465277778</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45647</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45643.53393518519</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>45656.59703703703</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>44279</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>44879</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45223</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44099</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>44154</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>44090</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>44512</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>44445</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>44512</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>44445</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>44728</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44207</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>44797</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>44742</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>44377</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45123</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>45622</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>44603</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45595</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45079</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45271</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44630</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>45153</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45645.67945601852</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>44568</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>45819.65796296296</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>45826.45174768518</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45609</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45595</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>45609</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45700</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44683</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45838.67815972222</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>45838</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>45839.60460648148</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>45841.52454861111</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45020</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>45847.51078703703</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>45685.78776620371</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>45847.46962962963</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         <v>45098</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45595</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45595</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>45702.47149305556</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45695.42197916667</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45686.27208333334</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>44568</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45750.42127314815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44540</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>44075</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44568</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45180</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>45467</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45736.42743055556</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>45407</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>45635</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45243</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44308</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44313</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44113</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44102</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44103</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44214</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44371</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>44407</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>44748.94689814815</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>44473.44813657407</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>44473.508125</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>44256</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>44183</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>44175</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>44679</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44665</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44449</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44173</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44445</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44494</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44610</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44376.87497685185</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44377.44767361111</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44788</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44285</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44133</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44263</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44183</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44183</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44524</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44370</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44591</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44123</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>44714.438125</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>44162</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>44090</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44141</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>44255</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>44577.47756944445</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44287</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44533</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44749</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44126.94510416667</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44831.37650462963</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44200</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44172</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>44512.94539351852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>44369.41452546296</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>44271.43831018519</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44312</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44306</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>44502.94153935185</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>44788</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>44502</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>44207</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>44851.57131944445</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44209</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44209</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>44243</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>44473</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44106</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44466.53040509259</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>44300</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>44539</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>44495</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>44495</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>44277.59521990741</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>44512</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>44172</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>44337</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>44214</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>44502.94140046297</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>44693.41668981482</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>44858</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>44473.53681712963</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>44139</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>44470</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>44153</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>44077</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>44714</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>44151</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>44459</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>44382.92065972222</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>44377</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>44095</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44358.63585648148</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44728.94420138889</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>44526</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>44214</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>44524</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>44820</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>44113</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>44076</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>44473.53013888889</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44459</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>44123</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44848</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44337</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>44875.41104166667</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>44123</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44610</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44123</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>44727</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>44697.94231481481</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28658,7 +28658,7 @@
         <v>44519.63436342592</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>44470</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>44214</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>44279</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>44209</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>44169</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>44284</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>44705</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>44118.98730324074</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>44447</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>44307.42378472222</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>44470.39989583333</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44468</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44285</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>45370</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>44848</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>44400.37204861111</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>45251.65152777778</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45572.45601851852</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44803</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45713.60719907407</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>45342</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -29937,7 +29937,7 @@
         <v>45749</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>45720</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45035</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45700.37127314815</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45700.37481481482</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>45386</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45362</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>45414.486875</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45552.57210648148</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45254</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45195</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>45412.51260416667</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45714.34859953704</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45719.32584490741</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45370.94969907407</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>45203.46523148148</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45112</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>45531.62141203704</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45133</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>45698.39486111111</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>44539</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45411</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>45560</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>45747.47025462963</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>44830</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45362</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45245.5478125</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>44316</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>44825</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>45373</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>45253</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45415.45006944444</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45760.81083333334</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>45601.33743055556</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45244</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>45324</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>45182</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45764.55260416667</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>44875</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>45217</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>44834.95019675926</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>45165.69965277778</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>45203</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>45300</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>45082</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45686.32671296296</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>45393</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45701</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>45740</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>44874</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44550</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>45715</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>45776</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>44974</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>45693</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>45777</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>45712</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45777</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45777</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>44483.42253472222</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45779.56659722222</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>44901.59349537037</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33581,7 +33581,7 @@
         <v>45554</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45779.63834490741</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45779.57626157408</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45471.63390046296</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45474</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -33871,7 +33871,7 @@
         <v>45282</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -33928,7 +33928,7 @@
         <v>45239.9681712963</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45478.42063657408</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34042,7 +34042,7 @@
         <v>45779.65980324074</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>45474.69155092593</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>44389</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34218,7 +34218,7 @@
         <v>45779.42630787037</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>45779.5674074074</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>44516</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34389,7 +34389,7 @@
         <v>45243.37567129629</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45152</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>45398</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45696</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>45457.55922453704</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>45265.52887731481</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>45783.44828703703</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>45783</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -34860,7 +34860,7 @@
         <v>45748.3822337963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45454.57899305555</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45250</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35041,7 +35041,7 @@
         <v>45783</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45457.35388888889</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45226</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>44504</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45783.45121527778</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>45411.4666087963</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>45783.43409722222</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45713.37111111111</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>45688.38393518519</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45392</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45740</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>45414.96341435185</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>44939</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>45551.34414351852</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>45096</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>45580.36991898148</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45786.35219907408</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>45474.69074074074</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45786</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45785.52112268518</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>45785.5403125</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>45608.86341435185</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45785.54635416667</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45786</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45786.64972222222</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45786.65702546296</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>45112</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>45418.94616898148</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>45278.65582175926</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45785</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>45467</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>45786.66140046297</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>45715</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>45117</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>45432.36971064815</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45446.68733796296</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45785.51092592593</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>45467</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44911</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>45099.37211805556</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45117</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>45579.66459490741</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>45392</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>44480</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>45789.58238425926</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45789.61349537037</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45594.463125</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45119</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45180</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>45706</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>45666.65987268519</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>45632</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45525</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45834.34737268519</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>45833.63579861111</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>45833.49052083334</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45833.49057870371</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>45309.94650462963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>45109.44534722222</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>45195</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45631.61869212963</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45695.60015046296</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45602.38614583333</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45602.39862268518</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45602.42878472222</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>44971</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45243.33297453704</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>45145.95255787037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>45166</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>44391</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -39106,7 +39106,7 @@
         <v>45583.52885416667</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45791</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>45791.3162037037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>44510.9491087963</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>45706.59251157408</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>44873</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>45635.39820601852</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>44970</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45796.52836805556</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>45484</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>45378</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>45477.35225694445</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>44582</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>45721.66456018519</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>45484</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45686.33310185185</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45614.63575231482</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45793.45204861111</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45532.48732638889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>44522.46662037037</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>45698.40146990741</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45660.49618055556</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45796.59857638889</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45706.55993055556</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>44922</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45608</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>45695.57171296296</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>44818</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45713</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>45798.63611111111</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45798.63596064815</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45511.95109953704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>45476</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>45603.44815972223</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>45643.64706018518</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>45800.57129629629</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>45800.57461805556</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44466.56642361111</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44498</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>45800</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>45800.37061342593</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45635.67949074074</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>45608.43930555556</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>45800.56810185185</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>45791</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>44557</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>45800.65177083333</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>45800.64319444444</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>45714.69212962963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45684.62510416667</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>45746</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>44658</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>45800</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>45477.32728009259</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>45588</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>45721.45563657407</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42373,7 +42373,7 @@
         <v>45803.6837962963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>45488.94857638889</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42492,7 +42492,7 @@
         <v>45475</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>45803.69828703703</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>44600.37212962963</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42663,7 +42663,7 @@
         <v>45687</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -42725,7 +42725,7 @@
         <v>45261</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45721</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -42839,7 +42839,7 @@
         <v>45560.6599537037</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -42896,7 +42896,7 @@
         <v>45805.54185185185</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -42953,7 +42953,7 @@
         <v>44362</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>45538.68200231482</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>45751.3734837963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -43124,7 +43124,7 @@
         <v>45751.57877314815</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         <v>45733</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45805</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43295,7 +43295,7 @@
         <v>45692</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43357,7 +43357,7 @@
         <v>45695.61160879629</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45602</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>44592</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>44893</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>45406.05033564815</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>45699</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>44988.94056712963</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>44904</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>44141</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45198.42734953704</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>44188</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>45121</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>44686</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45573.54893518519</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45432.54027777778</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45182</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45807.58930555556</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45225.60212962963</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45810.32105324074</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45204</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45807.56728009259</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45118.94061342593</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45695.4046875</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45695.42418981482</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45474.3981712963</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>45565.32449074074</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>44151</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>45737.36873842592</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45811.54760416667</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45496.41289351852</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>45618.53126157408</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>45554.59550925926</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45618.53633101852</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45810.31376157407</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45812.32266203704</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45397,7 +45397,7 @@
         <v>45601.38071759259</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45554.59447916667</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45811.67769675926</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         <v>45656</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>45551.47325231481</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45700.30092592593</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>45746.79134259259</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -45816,7 +45816,7 @@
         <v>45811.69912037037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45491.44971064815</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>45716.55237268518</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>45813.44443287037</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -46049,7 +46049,7 @@
         <v>45550.66542824074</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>44214</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -46163,7 +46163,7 @@
         <v>45813.46969907408</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -46220,7 +46220,7 @@
         <v>45814</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -46277,7 +46277,7 @@
         <v>45814</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46334,7 +46334,7 @@
         <v>44498</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46391,7 +46391,7 @@
         <v>45561.61515046296</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46448,7 +46448,7 @@
         <v>44938.93989583333</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46505,7 +46505,7 @@
         <v>45813.68361111111</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45785.67431712963</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>45709</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45667.57217592592</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>45699.66576388889</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -46800,7 +46800,7 @@
         <v>45190</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -46857,7 +46857,7 @@
         <v>45700.56194444445</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45750.60577546297</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45686</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45818.36246527778</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45818.3293287037</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
         <v>45572</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45817.56761574074</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45687.48931712963</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>45566.51501157408</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45547.42736111111</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45176</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45694.64416666667</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>44207</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45815.50844907408</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45818.34474537037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45818.34473379629</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>45620.67667824074</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45818.33532407408</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45818.34833333334</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45818.37056712963</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45231</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>45862.34668981482</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45662</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>45820</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -48290,7 +48290,7 @@
         <v>45860</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>45232.46239583333</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45552.67611111111</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45820</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48518,7 +48518,7 @@
         <v>45820.36233796296</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>45820.36512731481</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45820.47200231482</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -48694,7 +48694,7 @@
         <v>45820</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45401.59133101852</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -48808,7 +48808,7 @@
         <v>45820.36498842593</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45820.36506944444</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>45861.6841087963</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45821.39026620371</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>44887</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -49103,7 +49103,7 @@
         <v>45693.67361111111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45863.45778935185</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -49222,7 +49222,7 @@
         <v>45638.81385416666</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>44631</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49336,7 +49336,7 @@
         <v>45863</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49393,7 +49393,7 @@
         <v>44970</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45056</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49507,7 +49507,7 @@
         <v>45056</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>45704.71069444445</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>45764.47059027778</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>44596</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -49740,7 +49740,7 @@
         <v>45534.57745370371</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45692.58106481482</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45097</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45867.41707175926</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45867.46560185185</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45700.27895833334</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>45826.4705787037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -50159,7 +50159,7 @@
         <v>45623.48571759259</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>45701.60901620371</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -50273,7 +50273,7 @@
         <v>44186</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50330,7 +50330,7 @@
         <v>45694.43806712963</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50387,7 +50387,7 @@
         <v>45676</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45761.50909722222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>45707.55246527777</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50563,7 +50563,7 @@
         <v>45720.60774305555</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50625,7 +50625,7 @@
         <v>45615.61302083333</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -50687,7 +50687,7 @@
         <v>44203</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -50744,7 +50744,7 @@
         <v>45216</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -50801,7 +50801,7 @@
         <v>44140</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -50858,7 +50858,7 @@
         <v>45869.34439814815</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -50920,7 +50920,7 @@
         <v>45721.5113425926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>45748</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45870</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>45705</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -51153,7 +51153,7 @@
         <v>45614.63697916667</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -51210,7 +51210,7 @@
         <v>45827.34488425926</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>44715.48863425926</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45343.95162037037</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45408</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51453,7 +51453,7 @@
         <v>45693.48239583334</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51510,7 +51510,7 @@
         <v>45698.4930787037</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51567,7 +51567,7 @@
         <v>44154</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51624,7 +51624,7 @@
         <v>45182</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>45832</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>45832.34630787037</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -51800,7 +51800,7 @@
         <v>45698.57129629629</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -51857,7 +51857,7 @@
         <v>45832.53935185185</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -51919,7 +51919,7 @@
         <v>45832.53225694445</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45615.59521990741</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45686.39777777778</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>45238</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -52157,7 +52157,7 @@
         <v>45601</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -52214,7 +52214,7 @@
         <v>45401.59810185185</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -52271,7 +52271,7 @@
         <v>45748.59744212963</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52328,7 +52328,7 @@
         <v>44741</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52385,7 +52385,7 @@
         <v>45460.44076388889</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>45707.33935185185</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52504,7 +52504,7 @@
         <v>45772.62052083333</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>45246</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52618,7 +52618,7 @@
         <v>45875.51046296296</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>44788</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -52732,7 +52732,7 @@
         <v>45833.34490740741</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>44179</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45720.40268518519</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>44601.35342592592</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>45833.36050925926</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45833.36083333333</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>45834.34726851852</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         <v>45693</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         <v>45168</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -53255,7 +53255,7 @@
         <v>44792.27644675926</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         <v>44750</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53369,7 +53369,7 @@
         <v>44721.39003472222</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53431,7 +53431,7 @@
         <v>45216</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53488,7 +53488,7 @@
         <v>45316</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53545,7 +53545,7 @@
         <v>45772.58283564815</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53602,7 +53602,7 @@
         <v>45772.59200231481</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -53659,7 +53659,7 @@
         <v>44732</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -53716,7 +53716,7 @@
         <v>44726</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -53773,7 +53773,7 @@
         <v>45834.61517361111</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -53835,7 +53835,7 @@
         <v>45876</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -53892,7 +53892,7 @@
         <v>45876</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -53949,7 +53949,7 @@
         <v>45833.36111111111</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -54006,7 +54006,7 @@
         <v>45117</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -54068,7 +54068,7 @@
         <v>45123.61459490741</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -54130,7 +54130,7 @@
         <v>45695.47791666666</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -54187,7 +54187,7 @@
         <v>44855</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -54244,7 +54244,7 @@
         <v>44855</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45877.46555555556</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54358,7 +54358,7 @@
         <v>45880</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54415,7 +54415,7 @@
         <v>45600.49616898148</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54472,7 +54472,7 @@
         <v>44880</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54529,7 +54529,7 @@
         <v>45835.42712962963</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54586,7 +54586,7 @@
         <v>45762.60907407408</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -54648,7 +54648,7 @@
         <v>45117</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -54710,7 +54710,7 @@
         <v>44741</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -54767,7 +54767,7 @@
         <v>45836.34413194445</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -54829,7 +54829,7 @@
         <v>45877.57403935185</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -54891,7 +54891,7 @@
         <v>45750.42650462963</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -54948,7 +54948,7 @@
         <v>44726</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -55005,7 +55005,7 @@
         <v>45300</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -55062,7 +55062,7 @@
         <v>45574.43403935185</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -55119,7 +55119,7 @@
         <v>45713.36561342593</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         <v>45713.38028935185</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -55243,7 +55243,7 @@
         <v>45882.34510416666</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55305,7 +55305,7 @@
         <v>45840.40717592592</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55367,7 +55367,7 @@
         <v>45700.6833912037</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55424,7 +55424,7 @@
         <v>45839.61541666667</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55486,7 +55486,7 @@
         <v>45839.61563657408</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55548,7 +55548,7 @@
         <v>45618.54398148148</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55605,7 +55605,7 @@
         <v>45881.39909722222</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -55662,7 +55662,7 @@
         <v>45744.59894675926</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45719</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>45279</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45882.69851851852</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -55900,7 +55900,7 @@
         <v>45764</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -55957,7 +55957,7 @@
         <v>45238</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -56019,7 +56019,7 @@
         <v>45839.72320601852</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -56076,7 +56076,7 @@
         <v>45839.61582175926</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>45839.61594907408</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -56200,7 +56200,7 @@
         <v>45257</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>45881.40521990741</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56314,7 +56314,7 @@
         <v>45881.51081018519</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56376,7 +56376,7 @@
         <v>45883.61028935185</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56433,7 +56433,7 @@
         <v>45247</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56490,7 +56490,7 @@
         <v>45713.59623842593</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56552,7 +56552,7 @@
         <v>44757</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56614,7 +56614,7 @@
         <v>45671.59114583334</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>44711</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -56733,7 +56733,7 @@
         <v>45369</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45274</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>45878</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>45841.67834490741</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -56971,7 +56971,7 @@
         <v>45842.39587962963</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -57033,7 +57033,7 @@
         <v>45842.40013888889</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>45510.58033564815</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>45883.37883101852</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>45457.38799768518</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45841.46925925926</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57333,7 +57333,7 @@
         <v>44349</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57395,7 +57395,7 @@
         <v>44273</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>45203.44248842593</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57509,7 +57509,7 @@
         <v>45842.6099537037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57566,7 +57566,7 @@
         <v>45841.43987268519</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57623,7 +57623,7 @@
         <v>45165.70483796296</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45887.44883101852</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>45887.59064814815</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>45842</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>44524</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -57908,7 +57908,7 @@
         <v>45448.67574074074</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -57970,7 +57970,7 @@
         <v>45607</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -58027,7 +58027,7 @@
         <v>45887.58372685185</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -58084,7 +58084,7 @@
         <v>45888.72766203704</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -58146,7 +58146,7 @@
         <v>45614.63606481482</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>45614.63701388889</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>44285</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58317,7 +58317,7 @@
         <v>45887.55252314815</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58379,7 +58379,7 @@
         <v>44847</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58436,7 +58436,7 @@
         <v>44847</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58493,7 +58493,7 @@
         <v>45842</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58550,7 +58550,7 @@
         <v>45695.45013888889</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58612,7 +58612,7 @@
         <v>44858</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>45888.72445601852</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -58731,7 +58731,7 @@
         <v>45876</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>45140</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>45090</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -58902,7 +58902,7 @@
         <v>45466.62116898148</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -58959,7 +58959,7 @@
         <v>45848.48070601852</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -59016,7 +59016,7 @@
         <v>45180</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -59078,7 +59078,7 @@
         <v>45763.44112268519</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>45848</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -59192,7 +59192,7 @@
         <v>45847.51106481482</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -59249,7 +59249,7 @@
         <v>45639</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59306,7 +59306,7 @@
         <v>45642.6366087963</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59363,7 +59363,7 @@
         <v>44334</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59420,7 +59420,7 @@
         <v>45847.65717592592</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59482,7 +59482,7 @@
         <v>45696.3440162037</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59539,7 +59539,7 @@
         <v>45750.6447800926</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59601,7 +59601,7 @@
         <v>45638.81375</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59658,7 +59658,7 @@
         <v>45889.38626157407</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -59720,7 +59720,7 @@
         <v>45708</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -59782,7 +59782,7 @@
         <v>45889.37520833333</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>45757.56491898148</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45713.36836805556</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -59963,7 +59963,7 @@
         <v>45847.46462962963</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -60020,7 +60020,7 @@
         <v>45848.60371527778</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>45022</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -60134,7 +60134,7 @@
         <v>45849.4525462963</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -60191,7 +60191,7 @@
         <v>44331</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -60248,7 +60248,7 @@
         <v>45692</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60310,7 +60310,7 @@
         <v>45257</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60367,7 +60367,7 @@
         <v>45348</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60424,7 +60424,7 @@
         <v>45849.3859837963</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60486,7 +60486,7 @@
         <v>45630</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60543,7 +60543,7 @@
         <v>45894.63693287037</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60605,7 +60605,7 @@
         <v>45588</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60662,7 +60662,7 @@
         <v>45894.43864583333</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -60719,7 +60719,7 @@
         <v>45817</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -60776,7 +60776,7 @@
         <v>45565.33152777778</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -60833,7 +60833,7 @@
         <v>45694.34268518518</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -60895,7 +60895,7 @@
         <v>45204.40770833333</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45467</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -61009,7 +61009,7 @@
         <v>45139</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -61071,7 +61071,7 @@
         <v>45572</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -61133,7 +61133,7 @@
         <v>45670</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -61190,7 +61190,7 @@
         <v>45614.65925925926</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -61247,7 +61247,7 @@
         <v>45895.36994212963</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61304,7 +61304,7 @@
         <v>45519.60965277778</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61361,7 +61361,7 @@
         <v>45896.34443287037</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61423,7 +61423,7 @@
         <v>45854.65378472222</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61480,7 +61480,7 @@
         <v>44544.49326388889</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61537,7 +61537,7 @@
         <v>45853.6156712963</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61599,7 +61599,7 @@
         <v>45635</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61656,7 +61656,7 @@
         <v>45483</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -61713,7 +61713,7 @@
         <v>45854.66518518519</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -61770,7 +61770,7 @@
         <v>45840.58494212963</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -61827,7 +61827,7 @@
         <v>44377</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -61884,7 +61884,7 @@
         <v>45723.50841435185</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -61941,7 +61941,7 @@
         <v>44732</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>44865</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -62055,7 +62055,7 @@
         <v>45713.59163194444</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -62117,7 +62117,7 @@
         <v>45855.61193287037</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -62179,7 +62179,7 @@
         <v>45897.46832175926</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -62236,7 +62236,7 @@
         <v>44370</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -62293,7 +62293,7 @@
         <v>44427</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62350,7 +62350,7 @@
         <v>45898.64267361111</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62407,7 +62407,7 @@
         <v>44228</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>45173</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62526,7 +62526,7 @@
         <v>45897.44951388889</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>45897.45311342592</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62640,7 +62640,7 @@
         <v>45897.49424768519</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -62697,7 +62697,7 @@
         <v>45694.65905092593</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -62754,7 +62754,7 @@
         <v>45713.59952546296</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -62816,7 +62816,7 @@
         <v>45634.7925</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -62873,7 +62873,7 @@
         <v>45634.79854166666</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -62930,7 +62930,7 @@
         <v>45608.61923611111</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -62987,7 +62987,7 @@
         <v>45653.57240740741</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -63049,7 +63049,7 @@
         <v>45600.433125</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -63111,7 +63111,7 @@
         <v>45701.57363425926</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -63168,7 +63168,7 @@
         <v>45392.95844907407</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -63225,7 +63225,7 @@
         <v>45392</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -63282,7 +63282,7 @@
         <v>45692.60364583333</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63339,7 +63339,7 @@
         <v>45708</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63401,7 +63401,7 @@
         <v>45701</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63463,7 +63463,7 @@
         <v>45713.59741898148</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63525,7 +63525,7 @@
         <v>44335</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63582,7 +63582,7 @@
         <v>44873</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63659,7 +63659,7 @@
         <v>44757</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -63721,7 +63721,7 @@
         <v>45453</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -63783,7 +63783,7 @@
         <v>45453.95237268518</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -63845,7 +63845,7 @@
         <v>45499.48672453704</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -63902,7 +63902,7 @@
         <v>45687</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -63959,7 +63959,7 @@
         <v>44901.54615740741</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -64021,7 +64021,7 @@
         <v>45748.57269675926</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -64078,7 +64078,7 @@
         <v>45649.38149305555</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -64135,7 +64135,7 @@
         <v>44133</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -64192,7 +64192,7 @@
         <v>45764.40834490741</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -64249,7 +64249,7 @@
         <v>45719.37307870371</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -64311,7 +64311,7 @@
         <v>45749.38379629629</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64368,7 +64368,7 @@
         <v>44379.59675925926</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64425,7 +64425,7 @@
         <v>44849.8044212963</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64482,7 +64482,7 @@
         <v>45560.38056712963</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64544,7 +64544,7 @@
         <v>45758.58943287037</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64606,7 +64606,7 @@
         <v>45670</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>44206</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64720,7 +64720,7 @@
         <v>45245</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -64782,7 +64782,7 @@
         <v>44764</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -64839,7 +64839,7 @@
         <v>44764</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -64896,7 +64896,7 @@
         <v>45698.45653935185</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -64953,7 +64953,7 @@
         <v>44875</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -65010,7 +65010,7 @@
         <v>44972.55690972223</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -65067,7 +65067,7 @@
         <v>44211</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -65124,7 +65124,7 @@
         <v>45695</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -65186,7 +65186,7 @@
         <v>45469</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -65243,7 +65243,7 @@
         <v>45721.54896990741</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -65300,7 +65300,7 @@
         <v>45721</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65357,7 +65357,7 @@
         <v>45586.46927083333</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65414,7 +65414,7 @@
         <v>45555.43584490741</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65471,7 +65471,7 @@
         <v>45203</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65528,7 +65528,7 @@
         <v>45216.3965625</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65585,7 +65585,7 @@
         <v>45246</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65642,7 +65642,7 @@
         <v>45289</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65699,7 +65699,7 @@
         <v>45378</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -65756,7 +65756,7 @@
         <v>45226</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -65813,7 +65813,7 @@
         <v>44148</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -65870,7 +65870,7 @@
         <v>45055</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -65927,7 +65927,7 @@
         <v>45561.61509259259</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -65984,7 +65984,7 @@
         <v>45763.46918981482</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -66041,7 +66041,7 @@
         <v>45036</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -66098,7 +66098,7 @@
         <v>45036</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -66155,7 +66155,7 @@
         <v>45603.28460648148</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -66217,7 +66217,7 @@
         <v>45610.36561342593</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -66274,7 +66274,7 @@
         <v>45705.33446759259</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66336,7 +66336,7 @@
         <v>44887</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66398,7 +66398,7 @@
         <v>45231</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66455,7 +66455,7 @@
         <v>45751.37320601852</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66512,7 +66512,7 @@
         <v>44795</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66574,7 +66574,7 @@
         <v>44140</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66631,7 +66631,7 @@
         <v>44488.47928240741</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -66688,7 +66688,7 @@
         <v>45097</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -66745,7 +66745,7 @@
         <v>45226</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -66802,7 +66802,7 @@
         <v>44961</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -66859,7 +66859,7 @@
         <v>45055</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -66916,7 +66916,7 @@
         <v>44391</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -66973,7 +66973,7 @@
         <v>45649.45143518518</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -67030,7 +67030,7 @@
         <v>45452.55271990741</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -67092,7 +67092,7 @@
         <v>44456</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -67149,7 +67149,7 @@
         <v>45744</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -67206,7 +67206,7 @@
         <v>45740.60405092593</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -67268,7 +67268,7 @@
         <v>45107</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67325,7 +67325,7 @@
         <v>45751.6877662037</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67387,7 +67387,7 @@
         <v>45751.28243055556</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67449,7 +67449,7 @@
         <v>45621</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67506,7 +67506,7 @@
         <v>45740.60347222222</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67568,7 +67568,7 @@
         <v>45642.63666666667</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67625,7 +67625,7 @@
         <v>45377</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -67682,7 +67682,7 @@
         <v>45560.45841435185</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -67744,7 +67744,7 @@
         <v>45180.6391087963</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -67806,7 +67806,7 @@
         <v>45260</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -67863,7 +67863,7 @@
         <v>44540</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -67920,7 +67920,7 @@
         <v>45607.63211805555</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -67977,7 +67977,7 @@
         <v>45686.35247685185</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -68039,7 +68039,7 @@
         <v>44390</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -68096,7 +68096,7 @@
         <v>45602.65599537037</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -68153,7 +68153,7 @@
         <v>45190</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -68210,7 +68210,7 @@
         <v>45042</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -68267,7 +68267,7 @@
         <v>45050</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68329,7 +68329,7 @@
         <v>45453.45515046296</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68386,7 +68386,7 @@
         <v>45056</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68443,7 +68443,7 @@
         <v>45000</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68500,7 +68500,7 @@
         <v>45602.57827546296</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68557,7 +68557,7 @@
         <v>45721.55653935186</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68614,7 +68614,7 @@
         <v>45189</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -68671,7 +68671,7 @@
         <v>45452.56446759259</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -68733,7 +68733,7 @@
         <v>45679.70027777777</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -68790,7 +68790,7 @@
         <v>45600.58076388889</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -68847,7 +68847,7 @@
         <v>45560.69164351852</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -68904,7 +68904,7 @@
         <v>44908</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -68966,7 +68966,7 @@
         <v>45586.53618055556</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -69023,7 +69023,7 @@
         <v>45459.55150462963</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -69085,7 +69085,7 @@
         <v>45607</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -69142,7 +69142,7 @@
         <v>45485</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -69199,7 +69199,7 @@
         <v>45665.57373842593</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -69256,7 +69256,7 @@
         <v>45770.64677083334</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -69313,7 +69313,7 @@
         <v>45615.61121527778</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -69375,7 +69375,7 @@
         <v>45608.61606481481</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -69432,7 +69432,7 @@
         <v>45674</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -69489,7 +69489,7 @@
         <v>45593.38568287037</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -69546,7 +69546,7 @@
         <v>45672.53806712963</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -69608,7 +69608,7 @@
         <v>45189.60987268519</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -69665,7 +69665,7 @@
         <v>45649.4634375</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -69722,7 +69722,7 @@
         <v>45643.65354166667</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -69779,7 +69779,7 @@
         <v>45630.47099537037</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -69836,7 +69836,7 @@
         <v>45310</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -69893,7 +69893,7 @@
         <v>45160.66704861111</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -69955,7 +69955,7 @@
         <v>45547.42732638889</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -70012,7 +70012,7 @@
         <v>45602</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -70069,7 +70069,7 @@
         <v>45532.58101851852</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -70126,7 +70126,7 @@
         <v>45758.66180555556</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -70183,7 +70183,7 @@
         <v>45758.67065972222</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -70240,7 +70240,7 @@
         <v>45369</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -70297,7 +70297,7 @@
         <v>45692.64298611111</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -70354,7 +70354,7 @@
         <v>45726.37850694444</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -70416,7 +70416,7 @@
         <v>45209</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -70473,7 +70473,7 @@
         <v>45746</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -70535,7 +70535,7 @@
         <v>45371</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -70592,7 +70592,7 @@
         <v>45090</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -70649,7 +70649,7 @@
         <v>45554.59538194445</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -70706,7 +70706,7 @@
         <v>45726.56341435185</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -70768,7 +70768,7 @@
         <v>45726.5827199074</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -70825,7 +70825,7 @@
         <v>45726.61520833334</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -70887,7 +70887,7 @@
         <v>45118</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -70944,7 +70944,7 @@
         <v>45597.49638888889</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -71001,7 +71001,7 @@
         <v>45279</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -71058,7 +71058,7 @@
         <v>44866</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -71115,7 +71115,7 @@
         <v>45407</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -71172,7 +71172,7 @@
         <v>45748.36445601852</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -71229,7 +71229,7 @@
         <v>45748.37173611111</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -71286,7 +71286,7 @@
         <v>45371</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -71343,7 +71343,7 @@
         <v>44965</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -71405,7 +71405,7 @@
         <v>45266</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -71462,7 +71462,7 @@
         <v>45245</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -71519,7 +71519,7 @@
         <v>45691.61996527778</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -71581,7 +71581,7 @@
         <v>45721.4546412037</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -71638,7 +71638,7 @@
         <v>45446.47634259259</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -71700,7 +71700,7 @@
         <v>45484</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -71762,7 +71762,7 @@
         <v>45527.39858796296</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -71819,7 +71819,7 @@
         <v>45586</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -71876,7 +71876,7 @@
         <v>45478.60708333334</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -71933,7 +71933,7 @@
         <v>45090</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>

--- a/Översikt KROKOM.xlsx
+++ b/Översikt KROKOM.xlsx
@@ -567,7 +567,7 @@
         <v>45716</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44522</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45637</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45348</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44165</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>45384</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>45254</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>45709</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45603</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>44378</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>45845</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>45478</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>44323</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45121</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45155</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>45646</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>44565</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45887.44892361111</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>44363</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45219</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45453</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45630</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45625</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>45041</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45790</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>45553</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>45663</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>45849</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45644</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>45428</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>45596.5093287037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>44306.52587962963</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>44575</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>44326</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>45792</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>44581</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45475</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44780</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>44323</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>45691</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>45784.56270833333</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45646</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44231</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45646</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>44475</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>45551</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>45512</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45488.56961805555</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45534</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>45639</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>45719.52238425926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>44795</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>45041</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>45580</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>45527</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>45454</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>45643</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>45219</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44118</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44498</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44552</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>45457</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>45181</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>45169</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>44308</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44133</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44585</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>44698</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>44500</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>45316</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>45862.42901620371</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>45839.68914351852</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45616</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>45149</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>45267</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45475</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44271</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>44265</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>44534</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44494</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44326</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>45370</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44477</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>45180</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45862.43403935185</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>45862.4257175926</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>44834</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>45252</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45755.47527777778</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>45832.38581018519</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>44797</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>45581</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>45474</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44183</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>44515</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>44150</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45874.67765046296</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45838.67858796296</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>45888.55305555555</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45532</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>45551</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>45615</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>44903</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44546</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>44452</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>45079</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>44540</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45726.46192129629</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44162</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>44510.94930555556</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>44728</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>44895</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>45624</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>45169</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>44553</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45595</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>44904</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45764</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         <v>45527</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>45849.42818287037</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44174</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44966</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>44879</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45735</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45632</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>45621</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45310</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>45617</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45656.54600694445</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>45511.55719907407</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>44540</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45271</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>45453.63133101852</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45821.44299768518</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>45863.58127314815</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45216</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>45372</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>45636</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45887.6989699074</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45526</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45630</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>44757</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>45216.67748842593</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>44757</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>44873</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>44841</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45233</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>44867</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>45313</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45692</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>44355</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>44161</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>44378</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44524</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>44316</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44230</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44757</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45268</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45376</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45793.4189699074</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44540</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45804.60005787037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45554</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>44209</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45863.59111111111</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45348</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45877.67787037037</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>45869</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45862</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45595</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45896.34465277778</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45647</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45643.53393518519</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>45656.59703703703</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>44279</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>44879</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45223</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44099</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>44154</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>44090</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>44512</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>44445</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>44512</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>44445</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>44728</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44207</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>44797</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>44742</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>44377</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45123</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>45622</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>44603</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45595</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45079</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45271</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44630</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>45153</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45645.67945601852</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>44568</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>45819.65796296296</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>45826.45174768518</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45609</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45595</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>45609</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45700</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44683</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45838.67815972222</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>45838</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>45839.60460648148</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>45841.52454861111</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45020</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>45847.51078703703</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>45685.78776620371</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>45847.46962962963</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         <v>45098</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45595</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45595</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>45702.47149305556</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45695.42197916667</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45686.27208333334</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>44568</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45750.42127314815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44540</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>44075</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44568</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45180</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>45467</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45736.42743055556</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>45407</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>45635</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45243</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44308</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44313</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44113</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44102</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44103</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44214</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44371</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>44407</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>44748.94689814815</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>44473.44813657407</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>44473.508125</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>44256</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>44183</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>44175</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>44679</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44665</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44449</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44173</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44445</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44494</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44610</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44376.87497685185</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44377.44767361111</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44788</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44285</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44133</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44263</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44183</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44183</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44524</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44370</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44591</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44123</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>44714.438125</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>44162</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>44090</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44141</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>44255</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>44577.47756944445</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44287</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44533</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44749</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44126.94510416667</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44831.37650462963</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44200</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44172</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>44512.94539351852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>44369.41452546296</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>44271.43831018519</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44312</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44306</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>44502.94153935185</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>44788</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>44502</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>44207</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>44851.57131944445</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44209</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44209</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>44243</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>44473</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44106</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44466.53040509259</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>44300</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>44539</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>44495</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>44495</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>44277.59521990741</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>44512</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>44172</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>44337</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>44214</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>44502.94140046297</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>44693.41668981482</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>44858</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>44473.53681712963</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>44139</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>44470</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>44153</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>44077</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>44714</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>44151</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>44459</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>44382.92065972222</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>44377</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>44095</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44358.63585648148</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44728.94420138889</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>44526</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>44214</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>44524</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>44820</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>44113</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>44076</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>44473.53013888889</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44459</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>44123</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44848</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44337</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>44875.41104166667</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>44123</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44610</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44123</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>44727</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>44697.94231481481</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28658,7 +28658,7 @@
         <v>44519.63436342592</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>44470</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>44214</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>44279</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>44209</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>44169</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>44284</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>44705</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>44118.98730324074</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>44447</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>44307.42378472222</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>44470.39989583333</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44468</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44285</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>45370</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>44848</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>44400.37204861111</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>45251.65152777778</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45572.45601851852</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44803</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45713.60719907407</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>45342</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -29937,7 +29937,7 @@
         <v>45749</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>45720</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45035</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45700.37127314815</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45700.37481481482</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>45386</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45362</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>45414.486875</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45552.57210648148</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45254</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45195</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>45412.51260416667</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45714.34859953704</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45719.32584490741</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45370.94969907407</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>45203.46523148148</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45112</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>45531.62141203704</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45133</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>45698.39486111111</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>44539</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45411</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>45560</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>45747.47025462963</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>44830</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45362</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45245.5478125</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>44316</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>44825</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>45373</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>45253</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45415.45006944444</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45760.81083333334</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>45601.33743055556</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45244</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>45324</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>45182</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45764.55260416667</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>44875</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>45217</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>44834.95019675926</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>45165.69965277778</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>45203</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>45300</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>45082</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45686.32671296296</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>45393</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45701</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>45740</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>44874</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44550</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>45715</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>45776</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>44974</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>45693</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>45777</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>45712</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45777</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45777</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>44483.42253472222</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45779.56659722222</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>44901.59349537037</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33581,7 +33581,7 @@
         <v>45554</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45779.63834490741</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45779.57626157408</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45471.63390046296</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45474</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -33871,7 +33871,7 @@
         <v>45282</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -33928,7 +33928,7 @@
         <v>45239.9681712963</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45478.42063657408</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34042,7 +34042,7 @@
         <v>45779.65980324074</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>45474.69155092593</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>44389</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34218,7 +34218,7 @@
         <v>45779.42630787037</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>45779.5674074074</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>44516</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34389,7 +34389,7 @@
         <v>45243.37567129629</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45152</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>45398</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45696</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>45457.55922453704</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>45265.52887731481</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>45783.44828703703</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>45783</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -34860,7 +34860,7 @@
         <v>45748.3822337963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45454.57899305555</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45250</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35041,7 +35041,7 @@
         <v>45783</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45457.35388888889</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45226</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>44504</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45783.45121527778</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>45411.4666087963</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>45783.43409722222</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45713.37111111111</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>45688.38393518519</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45392</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45740</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>45414.96341435185</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>44939</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>45551.34414351852</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>45096</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>45580.36991898148</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45786.35219907408</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>45474.69074074074</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45786</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45785.52112268518</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>45785.5403125</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>45608.86341435185</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45785.54635416667</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45786</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45786.64972222222</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45786.65702546296</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>45112</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>45418.94616898148</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>45278.65582175926</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45785</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>45467</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>45786.66140046297</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>45715</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>45117</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>45432.36971064815</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45446.68733796296</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45785.51092592593</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>45467</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44911</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>45099.37211805556</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45117</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>45579.66459490741</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>45392</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>44480</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>45789.58238425926</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45789.61349537037</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45594.463125</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45119</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45180</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>45706</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>45666.65987268519</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>45632</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45525</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45834.34737268519</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>45833.63579861111</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>45833.49052083334</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45833.49057870371</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>45309.94650462963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>45109.44534722222</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>45195</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45631.61869212963</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45695.60015046296</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45602.38614583333</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45602.39862268518</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45602.42878472222</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>44971</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45243.33297453704</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>45145.95255787037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>45166</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>44391</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -39106,7 +39106,7 @@
         <v>45583.52885416667</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45791</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>45791.3162037037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>44510.9491087963</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>45706.59251157408</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>44873</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>45635.39820601852</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>44970</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45796.52836805556</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>45484</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>45378</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>45477.35225694445</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>44582</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>45721.66456018519</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>45484</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45686.33310185185</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45614.63575231482</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45793.45204861111</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45532.48732638889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>44522.46662037037</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>45698.40146990741</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45660.49618055556</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45796.59857638889</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45706.55993055556</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>44922</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45608</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>45695.57171296296</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>44818</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45713</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>45798.63611111111</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45798.63596064815</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45511.95109953704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>45476</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>45603.44815972223</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>45643.64706018518</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>45800.57129629629</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>45800.57461805556</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44466.56642361111</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44498</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>45800</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>45800.37061342593</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45635.67949074074</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>45608.43930555556</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>45800.56810185185</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>45791</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>44557</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>45800.65177083333</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>45800.64319444444</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>45714.69212962963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45684.62510416667</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>45746</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>44658</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>45800</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>45477.32728009259</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>45588</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>45721.45563657407</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42373,7 +42373,7 @@
         <v>45803.6837962963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>45488.94857638889</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42492,7 +42492,7 @@
         <v>45475</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>45803.69828703703</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>44600.37212962963</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42663,7 +42663,7 @@
         <v>45687</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -42725,7 +42725,7 @@
         <v>45261</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45721</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -42839,7 +42839,7 @@
         <v>45560.6599537037</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -42896,7 +42896,7 @@
         <v>45805.54185185185</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -42953,7 +42953,7 @@
         <v>44362</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>45538.68200231482</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>45751.3734837963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -43124,7 +43124,7 @@
         <v>45751.57877314815</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         <v>45733</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45805</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43295,7 +43295,7 @@
         <v>45692</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43357,7 +43357,7 @@
         <v>45695.61160879629</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45602</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>44592</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>44893</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>45406.05033564815</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>45699</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>44988.94056712963</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>44904</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>44141</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45198.42734953704</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>44188</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>45121</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>44686</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45573.54893518519</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45432.54027777778</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45182</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45807.58930555556</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45225.60212962963</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45810.32105324074</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45204</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45807.56728009259</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45118.94061342593</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45695.4046875</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45695.42418981482</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45474.3981712963</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>45565.32449074074</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>44151</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>45737.36873842592</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45811.54760416667</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45496.41289351852</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>45618.53126157408</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>45554.59550925926</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45618.53633101852</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45810.31376157407</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45812.32266203704</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45397,7 +45397,7 @@
         <v>45601.38071759259</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45554.59447916667</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45811.67769675926</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         <v>45656</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>45551.47325231481</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45700.30092592593</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>45746.79134259259</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -45816,7 +45816,7 @@
         <v>45811.69912037037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45491.44971064815</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>45716.55237268518</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>45813.44443287037</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -46049,7 +46049,7 @@
         <v>45550.66542824074</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>44214</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -46163,7 +46163,7 @@
         <v>45813.46969907408</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -46220,7 +46220,7 @@
         <v>45814</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -46277,7 +46277,7 @@
         <v>45814</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46334,7 +46334,7 @@
         <v>44498</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46391,7 +46391,7 @@
         <v>45561.61515046296</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46448,7 +46448,7 @@
         <v>44938.93989583333</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46505,7 +46505,7 @@
         <v>45813.68361111111</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45785.67431712963</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>45709</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45667.57217592592</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>45699.66576388889</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -46800,7 +46800,7 @@
         <v>45190</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -46857,7 +46857,7 @@
         <v>45700.56194444445</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45750.60577546297</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45686</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45818.36246527778</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45818.3293287037</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
         <v>45572</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45817.56761574074</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45687.48931712963</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>45566.51501157408</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45547.42736111111</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45176</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45694.64416666667</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>44207</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45815.50844907408</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45818.34474537037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45818.34473379629</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>45620.67667824074</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45818.33532407408</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45818.34833333334</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45818.37056712963</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45231</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>45862.34668981482</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45662</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>45820</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -48290,7 +48290,7 @@
         <v>45860</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>45232.46239583333</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45552.67611111111</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45820</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48518,7 +48518,7 @@
         <v>45820.36233796296</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>45820.36512731481</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45820.47200231482</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -48694,7 +48694,7 @@
         <v>45820</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45401.59133101852</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -48808,7 +48808,7 @@
         <v>45820.36498842593</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45820.36506944444</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>45861.6841087963</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45821.39026620371</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>44887</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -49103,7 +49103,7 @@
         <v>45693.67361111111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45863.45778935185</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -49222,7 +49222,7 @@
         <v>45638.81385416666</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>44631</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49336,7 +49336,7 @@
         <v>45863</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49393,7 +49393,7 @@
         <v>44970</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45056</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49507,7 +49507,7 @@
         <v>45056</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>45704.71069444445</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>45764.47059027778</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>44596</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -49740,7 +49740,7 @@
         <v>45534.57745370371</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45692.58106481482</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45097</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45867.41707175926</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45867.46560185185</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45700.27895833334</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>45826.4705787037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -50159,7 +50159,7 @@
         <v>45623.48571759259</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>45701.60901620371</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -50273,7 +50273,7 @@
         <v>44186</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50330,7 +50330,7 @@
         <v>45694.43806712963</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50387,7 +50387,7 @@
         <v>45676</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45761.50909722222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>45707.55246527777</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50563,7 +50563,7 @@
         <v>45720.60774305555</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50625,7 +50625,7 @@
         <v>45615.61302083333</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -50687,7 +50687,7 @@
         <v>44203</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -50744,7 +50744,7 @@
         <v>45216</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -50801,7 +50801,7 @@
         <v>44140</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -50858,7 +50858,7 @@
         <v>45869.34439814815</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -50920,7 +50920,7 @@
         <v>45721.5113425926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>45748</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45870</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>45705</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -51153,7 +51153,7 @@
         <v>45614.63697916667</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -51210,7 +51210,7 @@
         <v>45827.34488425926</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>44715.48863425926</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45343.95162037037</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45408</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51453,7 +51453,7 @@
         <v>45693.48239583334</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51510,7 +51510,7 @@
         <v>45698.4930787037</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51567,7 +51567,7 @@
         <v>44154</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51624,7 +51624,7 @@
         <v>45182</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>45832</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>45832.34630787037</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -51800,7 +51800,7 @@
         <v>45698.57129629629</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -51857,7 +51857,7 @@
         <v>45832.53935185185</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -51919,7 +51919,7 @@
         <v>45832.53225694445</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45615.59521990741</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45686.39777777778</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>45238</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -52157,7 +52157,7 @@
         <v>45601</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -52214,7 +52214,7 @@
         <v>45401.59810185185</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -52271,7 +52271,7 @@
         <v>45748.59744212963</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52328,7 +52328,7 @@
         <v>44741</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52385,7 +52385,7 @@
         <v>45460.44076388889</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>45707.33935185185</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52504,7 +52504,7 @@
         <v>45772.62052083333</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>45246</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52618,7 +52618,7 @@
         <v>45875.51046296296</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>44788</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -52732,7 +52732,7 @@
         <v>45833.34490740741</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>44179</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45720.40268518519</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>44601.35342592592</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>45833.36050925926</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45833.36083333333</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>45834.34726851852</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         <v>45693</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         <v>45168</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -53255,7 +53255,7 @@
         <v>44792.27644675926</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         <v>44750</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53369,7 +53369,7 @@
         <v>44721.39003472222</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53431,7 +53431,7 @@
         <v>45216</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53488,7 +53488,7 @@
         <v>45316</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53545,7 +53545,7 @@
         <v>45772.58283564815</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53602,7 +53602,7 @@
         <v>45772.59200231481</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -53659,7 +53659,7 @@
         <v>44732</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -53716,7 +53716,7 @@
         <v>44726</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -53773,7 +53773,7 @@
         <v>45834.61517361111</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -53835,7 +53835,7 @@
         <v>45876</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -53892,7 +53892,7 @@
         <v>45876</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -53949,7 +53949,7 @@
         <v>45833.36111111111</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -54006,7 +54006,7 @@
         <v>45117</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -54068,7 +54068,7 @@
         <v>45123.61459490741</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -54130,7 +54130,7 @@
         <v>45695.47791666666</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -54187,7 +54187,7 @@
         <v>44855</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -54244,7 +54244,7 @@
         <v>44855</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45877.46555555556</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54358,7 +54358,7 @@
         <v>45880</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54415,7 +54415,7 @@
         <v>45600.49616898148</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54472,7 +54472,7 @@
         <v>44880</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54529,7 +54529,7 @@
         <v>45835.42712962963</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54586,7 +54586,7 @@
         <v>45762.60907407408</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -54648,7 +54648,7 @@
         <v>45117</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -54710,7 +54710,7 @@
         <v>44741</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -54767,7 +54767,7 @@
         <v>45836.34413194445</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -54829,7 +54829,7 @@
         <v>45877.57403935185</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -54891,7 +54891,7 @@
         <v>45750.42650462963</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -54948,7 +54948,7 @@
         <v>44726</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -55005,7 +55005,7 @@
         <v>45300</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -55062,7 +55062,7 @@
         <v>45574.43403935185</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -55119,7 +55119,7 @@
         <v>45713.36561342593</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         <v>45713.38028935185</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -55243,7 +55243,7 @@
         <v>45882.34510416666</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55305,7 +55305,7 @@
         <v>45840.40717592592</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55367,7 +55367,7 @@
         <v>45700.6833912037</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55424,7 +55424,7 @@
         <v>45839.61541666667</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55486,7 +55486,7 @@
         <v>45839.61563657408</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55548,7 +55548,7 @@
         <v>45618.54398148148</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55605,7 +55605,7 @@
         <v>45881.39909722222</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -55662,7 +55662,7 @@
         <v>45744.59894675926</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45719</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>45279</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45882.69851851852</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -55900,7 +55900,7 @@
         <v>45764</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -55957,7 +55957,7 @@
         <v>45238</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -56019,7 +56019,7 @@
         <v>45839.72320601852</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -56076,7 +56076,7 @@
         <v>45839.61582175926</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>45839.61594907408</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -56200,7 +56200,7 @@
         <v>45257</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>45881.40521990741</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56314,7 +56314,7 @@
         <v>45881.51081018519</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56376,7 +56376,7 @@
         <v>45883.61028935185</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56433,7 +56433,7 @@
         <v>45247</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56490,7 +56490,7 @@
         <v>45713.59623842593</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56552,7 +56552,7 @@
         <v>44757</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56614,7 +56614,7 @@
         <v>45671.59114583334</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>44711</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -56733,7 +56733,7 @@
         <v>45369</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45274</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>45878</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>45841.67834490741</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -56971,7 +56971,7 @@
         <v>45842.39587962963</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -57033,7 +57033,7 @@
         <v>45842.40013888889</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>45510.58033564815</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>45883.37883101852</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>45457.38799768518</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45841.46925925926</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57333,7 +57333,7 @@
         <v>44349</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57395,7 +57395,7 @@
         <v>44273</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>45203.44248842593</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57509,7 +57509,7 @@
         <v>45842.6099537037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57566,7 +57566,7 @@
         <v>45841.43987268519</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57623,7 +57623,7 @@
         <v>45165.70483796296</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45887.44883101852</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>45887.59064814815</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>45842</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>44524</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -57908,7 +57908,7 @@
         <v>45448.67574074074</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -57970,7 +57970,7 @@
         <v>45607</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -58027,7 +58027,7 @@
         <v>45887.58372685185</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -58084,7 +58084,7 @@
         <v>45888.72766203704</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -58146,7 +58146,7 @@
         <v>45614.63606481482</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>45614.63701388889</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>44285</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58317,7 +58317,7 @@
         <v>45887.55252314815</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58379,7 +58379,7 @@
         <v>44847</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58436,7 +58436,7 @@
         <v>44847</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58493,7 +58493,7 @@
         <v>45842</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58550,7 +58550,7 @@
         <v>45695.45013888889</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58612,7 +58612,7 @@
         <v>44858</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>45888.72445601852</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -58731,7 +58731,7 @@
         <v>45876</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>45140</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>45090</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -58902,7 +58902,7 @@
         <v>45466.62116898148</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -58959,7 +58959,7 @@
         <v>45848.48070601852</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -59016,7 +59016,7 @@
         <v>45180</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -59078,7 +59078,7 @@
         <v>45763.44112268519</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>45848</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -59192,7 +59192,7 @@
         <v>45847.51106481482</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -59249,7 +59249,7 @@
         <v>45639</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59306,7 +59306,7 @@
         <v>45642.6366087963</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59363,7 +59363,7 @@
         <v>44334</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59420,7 +59420,7 @@
         <v>45847.65717592592</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59482,7 +59482,7 @@
         <v>45696.3440162037</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59539,7 +59539,7 @@
         <v>45750.6447800926</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59601,7 +59601,7 @@
         <v>45638.81375</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59658,7 +59658,7 @@
         <v>45889.38626157407</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -59720,7 +59720,7 @@
         <v>45708</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -59782,7 +59782,7 @@
         <v>45889.37520833333</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>45757.56491898148</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45713.36836805556</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -59963,7 +59963,7 @@
         <v>45847.46462962963</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -60020,7 +60020,7 @@
         <v>45848.60371527778</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>45022</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -60134,7 +60134,7 @@
         <v>45849.4525462963</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -60191,7 +60191,7 @@
         <v>44331</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -60248,7 +60248,7 @@
         <v>45692</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60310,7 +60310,7 @@
         <v>45257</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60367,7 +60367,7 @@
         <v>45348</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60424,7 +60424,7 @@
         <v>45849.3859837963</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60486,7 +60486,7 @@
         <v>45630</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60543,7 +60543,7 @@
         <v>45894.63693287037</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60605,7 +60605,7 @@
         <v>45588</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60662,7 +60662,7 @@
         <v>45894.43864583333</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -60719,7 +60719,7 @@
         <v>45817</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -60776,7 +60776,7 @@
         <v>45565.33152777778</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -60833,7 +60833,7 @@
         <v>45694.34268518518</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -60895,7 +60895,7 @@
         <v>45204.40770833333</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45467</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -61009,7 +61009,7 @@
         <v>45139</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -61071,7 +61071,7 @@
         <v>45572</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -61133,7 +61133,7 @@
         <v>45670</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -61190,7 +61190,7 @@
         <v>45614.65925925926</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -61247,7 +61247,7 @@
         <v>45895.36994212963</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61304,7 +61304,7 @@
         <v>45519.60965277778</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61361,7 +61361,7 @@
         <v>45896.34443287037</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61423,7 +61423,7 @@
         <v>45854.65378472222</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61480,7 +61480,7 @@
         <v>44544.49326388889</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61537,7 +61537,7 @@
         <v>45853.6156712963</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61599,7 +61599,7 @@
         <v>45635</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61656,7 +61656,7 @@
         <v>45483</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -61713,7 +61713,7 @@
         <v>45854.66518518519</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -61770,7 +61770,7 @@
         <v>45840.58494212963</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -61827,7 +61827,7 @@
         <v>44377</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -61884,7 +61884,7 @@
         <v>45723.50841435185</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -61941,7 +61941,7 @@
         <v>44732</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>44865</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -62055,7 +62055,7 @@
         <v>45713.59163194444</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -62117,7 +62117,7 @@
         <v>45855.61193287037</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -62179,7 +62179,7 @@
         <v>45897.46832175926</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -62236,7 +62236,7 @@
         <v>44370</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -62293,7 +62293,7 @@
         <v>44427</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62350,7 +62350,7 @@
         <v>45898.64267361111</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62407,7 +62407,7 @@
         <v>44228</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>45173</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62526,7 +62526,7 @@
         <v>45897.44951388889</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>45897.45311342592</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62640,7 +62640,7 @@
         <v>45897.49424768519</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -62697,7 +62697,7 @@
         <v>45694.65905092593</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -62754,7 +62754,7 @@
         <v>45713.59952546296</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -62816,7 +62816,7 @@
         <v>45634.7925</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -62873,7 +62873,7 @@
         <v>45634.79854166666</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -62930,7 +62930,7 @@
         <v>45608.61923611111</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -62987,7 +62987,7 @@
         <v>45653.57240740741</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -63049,7 +63049,7 @@
         <v>45600.433125</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -63111,7 +63111,7 @@
         <v>45701.57363425926</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -63168,7 +63168,7 @@
         <v>45392.95844907407</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -63225,7 +63225,7 @@
         <v>45392</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -63282,7 +63282,7 @@
         <v>45692.60364583333</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63339,7 +63339,7 @@
         <v>45708</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63401,7 +63401,7 @@
         <v>45701</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63463,7 +63463,7 @@
         <v>45713.59741898148</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63525,7 +63525,7 @@
         <v>44335</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63582,7 +63582,7 @@
         <v>44873</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63659,7 +63659,7 @@
         <v>44757</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -63721,7 +63721,7 @@
         <v>45453</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -63783,7 +63783,7 @@
         <v>45453.95237268518</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -63845,7 +63845,7 @@
         <v>45499.48672453704</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -63902,7 +63902,7 @@
         <v>45687</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -63959,7 +63959,7 @@
         <v>44901.54615740741</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -64021,7 +64021,7 @@
         <v>45748.57269675926</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -64078,7 +64078,7 @@
         <v>45649.38149305555</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -64135,7 +64135,7 @@
         <v>44133</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -64192,7 +64192,7 @@
         <v>45764.40834490741</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -64249,7 +64249,7 @@
         <v>45719.37307870371</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -64311,7 +64311,7 @@
         <v>45749.38379629629</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64368,7 +64368,7 @@
         <v>44379.59675925926</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64425,7 +64425,7 @@
         <v>44849.8044212963</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64482,7 +64482,7 @@
         <v>45560.38056712963</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64544,7 +64544,7 @@
         <v>45758.58943287037</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64606,7 +64606,7 @@
         <v>45670</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>44206</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64720,7 +64720,7 @@
         <v>45245</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -64782,7 +64782,7 @@
         <v>44764</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -64839,7 +64839,7 @@
         <v>44764</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -64896,7 +64896,7 @@
         <v>45698.45653935185</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -64953,7 +64953,7 @@
         <v>44875</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -65010,7 +65010,7 @@
         <v>44972.55690972223</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -65067,7 +65067,7 @@
         <v>44211</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -65124,7 +65124,7 @@
         <v>45695</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -65186,7 +65186,7 @@
         <v>45469</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -65243,7 +65243,7 @@
         <v>45721.54896990741</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -65300,7 +65300,7 @@
         <v>45721</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65357,7 +65357,7 @@
         <v>45586.46927083333</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65414,7 +65414,7 @@
         <v>45555.43584490741</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65471,7 +65471,7 @@
         <v>45203</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65528,7 +65528,7 @@
         <v>45216.3965625</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65585,7 +65585,7 @@
         <v>45246</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65642,7 +65642,7 @@
         <v>45289</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65699,7 +65699,7 @@
         <v>45378</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -65756,7 +65756,7 @@
         <v>45226</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -65813,7 +65813,7 @@
         <v>44148</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -65870,7 +65870,7 @@
         <v>45055</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -65927,7 +65927,7 @@
         <v>45561.61509259259</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -65984,7 +65984,7 @@
         <v>45763.46918981482</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -66041,7 +66041,7 @@
         <v>45036</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -66098,7 +66098,7 @@
         <v>45036</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -66155,7 +66155,7 @@
         <v>45603.28460648148</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -66217,7 +66217,7 @@
         <v>45610.36561342593</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -66274,7 +66274,7 @@
         <v>45705.33446759259</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66336,7 +66336,7 @@
         <v>44887</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66398,7 +66398,7 @@
         <v>45231</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66455,7 +66455,7 @@
         <v>45751.37320601852</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66512,7 +66512,7 @@
         <v>44795</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66574,7 +66574,7 @@
         <v>44140</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66631,7 +66631,7 @@
         <v>44488.47928240741</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -66688,7 +66688,7 @@
         <v>45097</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -66745,7 +66745,7 @@
         <v>45226</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -66802,7 +66802,7 @@
         <v>44961</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -66859,7 +66859,7 @@
         <v>45055</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -66916,7 +66916,7 @@
         <v>44391</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -66973,7 +66973,7 @@
         <v>45649.45143518518</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -67030,7 +67030,7 @@
         <v>45452.55271990741</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -67092,7 +67092,7 @@
         <v>44456</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -67149,7 +67149,7 @@
         <v>45744</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -67206,7 +67206,7 @@
         <v>45740.60405092593</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -67268,7 +67268,7 @@
         <v>45107</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67325,7 +67325,7 @@
         <v>45751.6877662037</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67387,7 +67387,7 @@
         <v>45751.28243055556</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67449,7 +67449,7 @@
         <v>45621</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67506,7 +67506,7 @@
         <v>45740.60347222222</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67568,7 +67568,7 @@
         <v>45642.63666666667</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67625,7 +67625,7 @@
         <v>45377</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -67682,7 +67682,7 @@
         <v>45560.45841435185</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -67744,7 +67744,7 @@
         <v>45180.6391087963</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -67806,7 +67806,7 @@
         <v>45260</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -67863,7 +67863,7 @@
         <v>44540</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -67920,7 +67920,7 @@
         <v>45607.63211805555</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -67977,7 +67977,7 @@
         <v>45686.35247685185</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -68039,7 +68039,7 @@
         <v>44390</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -68096,7 +68096,7 @@
         <v>45602.65599537037</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -68153,7 +68153,7 @@
         <v>45190</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -68210,7 +68210,7 @@
         <v>45042</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -68267,7 +68267,7 @@
         <v>45050</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68329,7 +68329,7 @@
         <v>45453.45515046296</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68386,7 +68386,7 @@
         <v>45056</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68443,7 +68443,7 @@
         <v>45000</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68500,7 +68500,7 @@
         <v>45602.57827546296</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68557,7 +68557,7 @@
         <v>45721.55653935186</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68614,7 +68614,7 @@
         <v>45189</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -68671,7 +68671,7 @@
         <v>45452.56446759259</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -68733,7 +68733,7 @@
         <v>45679.70027777777</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -68790,7 +68790,7 @@
         <v>45600.58076388889</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -68847,7 +68847,7 @@
         <v>45560.69164351852</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -68904,7 +68904,7 @@
         <v>44908</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -68966,7 +68966,7 @@
         <v>45586.53618055556</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -69023,7 +69023,7 @@
         <v>45459.55150462963</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -69085,7 +69085,7 @@
         <v>45607</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -69142,7 +69142,7 @@
         <v>45485</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -69199,7 +69199,7 @@
         <v>45665.57373842593</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -69256,7 +69256,7 @@
         <v>45770.64677083334</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -69313,7 +69313,7 @@
         <v>45615.61121527778</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -69375,7 +69375,7 @@
         <v>45608.61606481481</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -69432,7 +69432,7 @@
         <v>45674</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -69489,7 +69489,7 @@
         <v>45593.38568287037</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -69546,7 +69546,7 @@
         <v>45672.53806712963</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -69608,7 +69608,7 @@
         <v>45189.60987268519</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -69665,7 +69665,7 @@
         <v>45649.4634375</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -69722,7 +69722,7 @@
         <v>45643.65354166667</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -69779,7 +69779,7 @@
         <v>45630.47099537037</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -69836,7 +69836,7 @@
         <v>45310</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -69893,7 +69893,7 @@
         <v>45160.66704861111</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -69955,7 +69955,7 @@
         <v>45547.42732638889</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -70012,7 +70012,7 @@
         <v>45602</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -70069,7 +70069,7 @@
         <v>45532.58101851852</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -70126,7 +70126,7 @@
         <v>45758.66180555556</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -70183,7 +70183,7 @@
         <v>45758.67065972222</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -70240,7 +70240,7 @@
         <v>45369</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -70297,7 +70297,7 @@
         <v>45692.64298611111</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -70354,7 +70354,7 @@
         <v>45726.37850694444</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -70416,7 +70416,7 @@
         <v>45209</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -70473,7 +70473,7 @@
         <v>45746</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -70535,7 +70535,7 @@
         <v>45371</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -70592,7 +70592,7 @@
         <v>45090</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -70649,7 +70649,7 @@
         <v>45554.59538194445</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -70706,7 +70706,7 @@
         <v>45726.56341435185</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -70768,7 +70768,7 @@
         <v>45726.5827199074</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -70825,7 +70825,7 @@
         <v>45726.61520833334</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -70887,7 +70887,7 @@
         <v>45118</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -70944,7 +70944,7 @@
         <v>45597.49638888889</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -71001,7 +71001,7 @@
         <v>45279</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -71058,7 +71058,7 @@
         <v>44866</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -71115,7 +71115,7 @@
         <v>45407</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -71172,7 +71172,7 @@
         <v>45748.36445601852</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -71229,7 +71229,7 @@
         <v>45748.37173611111</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -71286,7 +71286,7 @@
         <v>45371</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -71343,7 +71343,7 @@
         <v>44965</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -71405,7 +71405,7 @@
         <v>45266</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -71462,7 +71462,7 @@
         <v>45245</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -71519,7 +71519,7 @@
         <v>45691.61996527778</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -71581,7 +71581,7 @@
         <v>45721.4546412037</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -71638,7 +71638,7 @@
         <v>45446.47634259259</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -71700,7 +71700,7 @@
         <v>45484</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -71762,7 +71762,7 @@
         <v>45527.39858796296</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -71819,7 +71819,7 @@
         <v>45586</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -71876,7 +71876,7 @@
         <v>45478.60708333334</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -71933,7 +71933,7 @@
         <v>45090</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>

--- a/Översikt KROKOM.xlsx
+++ b/Översikt KROKOM.xlsx
@@ -567,7 +567,7 @@
         <v>45716</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44522</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45637</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45348</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44165</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>45384</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>45254</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>45709</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45603</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>44378</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>45887.44892361111</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>45845</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45478</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>44323</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>45121</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>45646</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>45155</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>44565</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45453</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>44363</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45630</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45219</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45625</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45041</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45790</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45663</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>45849</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>45553</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>45644</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>45428</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>45596.5093287037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>44306.52587962963</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44575</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>45792</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44581</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>45475</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44326</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44780</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>44323</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45691</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>45784.56270833333</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>44231</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>45646</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>45646</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44475</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>45551</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>45639</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>44795</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>45534</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45488.56961805555</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>45512</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>45041</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>45719.52238425926</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45580</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>45527</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>44498</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>45643</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>45454</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44118</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>45219</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>44552</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>45181</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44308</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>45457</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44133</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>45169</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>44585</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44698</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>45316</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>45267</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45149</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45475</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>45839.68914351852</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>45616</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>45862.42901620371</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44500</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>44271</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>44265</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44534</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44494</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>44326</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>44797</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>44834</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>45832.38581018519</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>45180</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>45581</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>45755.47527777778</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>45862.4257175926</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>45862.43403935185</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>45370</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>45252</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>44477</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>45474</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>44183</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>44515</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>44557</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44540</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>45874.67765046296</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>45838.67858796296</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45888.55305555555</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>45532</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45551</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45615</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45079</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>44452</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>44150</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44546</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>45726.46192129629</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>44903</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44162</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>44510.94930555556</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>44728</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>44553</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>45310</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>44966</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>45624</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>45169</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>44895</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44879</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>45595</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>45764</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44174</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>45527</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>45849.42818287037</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>45632</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45621</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>44904</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45617</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>45735</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44757</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44841</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44867</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>45636</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>45511.55719907407</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45216</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>45271</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>45453.63133101852</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>44757</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>44540</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44873</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>45821.44299768518</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>45372</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45887.6989699074</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>45526</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>45630</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>45863.58127314815</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>45656.54600694445</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>45692</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>45233</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45313</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>45216.67748842593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>44355</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44161</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>44524</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>44316</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>44230</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>44378</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>44757</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45643.53393518519</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>45793.4189699074</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>45268</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45804.60005787037</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45348</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>45656.59703703703</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>45877.67787037037</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45869</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>45862</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45595</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>45896.34465277778</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>45647</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45863.59111111111</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44279</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>45223</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>45554</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44879</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45376</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>44209</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>44540</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>44099</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>44154</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44090</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>44512</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>44445</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>44512</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>44445</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>44728</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>44797</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44207</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>44742</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45685.78776620371</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>44377</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44568</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45243</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>44683</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>45622</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>45123</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45079</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45271</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45098</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>45595</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>44568</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45645.67945601852</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45635</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>45819.65796296296</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44568</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45826.45174768518</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>45180</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45609</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>45595</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45839.60460648148</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>45020</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>45838</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>45838.67815972222</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20931,7 +20931,7 @@
         <v>45841.52454861111</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45847.46962962963</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>45847.51078703703</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>45595</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45595</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45609</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45686.27208333334</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44540</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>44630</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45467</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45153</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>44603</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45695.42197916667</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>45700</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45736.42743055556</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>45702.47149305556</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>45750.42127314815</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45407</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>44308</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>44313</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>44113</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>44102</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>44103</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>44214</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44371</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>44407</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>44748.94689814815</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>44473.44813657407</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         <v>44473.508125</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>44256</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>44183</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44175</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44449</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44665</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>44679</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>44445</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>44173</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>44494</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44610</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>44376.87497685185</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>44377.44767361111</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44788</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>44285</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>44133</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44263</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>44183</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>44183</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>44524</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44370</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>44591</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>44123</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44714.438125</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>44162</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>44090</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>44141</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>44255</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44533</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>44577.47756944445</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>44287</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>44749</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>44126.94510416667</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>44831.37650462963</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44200</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44172</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44512.94539351852</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44369.41452546296</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44271.43831018519</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44312</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44306</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>44502.94153935185</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>44788</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44502</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>44207</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>44851.57131944445</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44209</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44209</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44243</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44473</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>44106</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>44466.53040509259</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>44300</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>44539</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>44495</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>44495</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>44277.59521990741</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44512</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44172</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44337</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44214</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44502.94140046297</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>44693.41668981482</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>44714</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44377</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>44473.53681712963</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>44459</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>44728.94420138889</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>44382.92065972222</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>44095</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>44358.63585648148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>44526</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>44214</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>44524</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>44113</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>44123</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>44820</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>44848</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>44473.53013888889</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>44459</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>44875.41104166667</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>44727</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -27882,7 +27882,7 @@
         <v>44123</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44610</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>44697.94231481481</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44337</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44123</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44519.63436342592</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44209</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>44169</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>44214</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>44705</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28457,7 +28457,7 @@
         <v>44279</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>44307.42378472222</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>44470</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>44284</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>44447</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>44468</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>44139</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>44470.39989583333</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>45510.58033564815</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44118.98730324074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>44285</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44875</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>44848</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>44400.37204861111</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>45695</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45457.35388888889</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45726.56341435185</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29456,7 +29456,7 @@
         <v>45460.44076388889</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>44470</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>44153</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45692.64298611111</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44151</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>44186</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>45726.5827199074</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45751.37320601852</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>45484</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45484</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>45216</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45706</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>45056</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>45119</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30264,7 +30264,7 @@
         <v>44858</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>45459.55150462963</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>45279</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44516</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45701.57363425926</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>45534.57745370371</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>45701</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>44866</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>45749.38379629629</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>44316</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>45467</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45452.56446759259</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>45721.5113425926</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>44483.42253472222</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45457.38799768518</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>45246</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>45748</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>44873</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>44873</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>45777</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>45777</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45777</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31578,7 +31578,7 @@
         <v>45712</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>45776</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>45639</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>45715</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45198.42734953704</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45511.95109953704</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45693</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45779.42630787037</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45779.56659722222</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>45721.66456018519</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45779.65980324074</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>44732</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45779.57626157408</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45779.5674074074</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45779.63834490741</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45278.65582175926</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45783.45121527778</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>45719.37307870371</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>45688.38393518519</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>45783</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>45720.60774305555</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45716.55237268518</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>45783.43409722222</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>45696</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>45783.44828703703</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45694.65905092593</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45699</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44875</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>45785</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>44539</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>45740</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45785.51092592593</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>45785.5403125</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>45253</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>45203</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>45519.60965277778</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>45785.54635416667</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>45713.37111111111</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>45090</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>45618.54398148148</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>45022</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>45785.52112268518</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34017,7 +34017,7 @@
         <v>45180.6391087963</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>45190</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45770.64677083334</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>45601.38071759259</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>45687</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>44524</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>45000</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>45748.3822337963</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44795</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>45602.38614583333</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45670</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45226</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>45393</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45107</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>45573.54893518519</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
         <v>45786.65702546296</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -34949,7 +34949,7 @@
         <v>44214</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35006,7 +35006,7 @@
         <v>44874</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>45786.66140046297</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>45715</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>45786.35219907408</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45608.43930555556</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>45527.39858796296</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35353,7 +35353,7 @@
         <v>45600.58076388889</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35410,7 +35410,7 @@
         <v>45369</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>44148</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>45614.63697916667</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>45789.58238425926</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>45789.61349537037</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45714.69212962963</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45554.59447916667</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>45525</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>45583.52885416667</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>45750.42650462963</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45786</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44140</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45763.46918981482</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>45411</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36223,7 +36223,7 @@
         <v>45477.32728009259</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>44726</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>45786.64972222222</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>44938.93989583333</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>45786</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>45231</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45600.433125</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>45343.95162037037</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36694,7 +36694,7 @@
         <v>45532.58101851852</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>45392</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>44911</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>44391</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>45691.61996527778</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>44721.39003472222</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -37051,7 +37051,7 @@
         <v>45761.50909722222</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -37108,7 +37108,7 @@
         <v>45632</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>45833.49052083334</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45833.49057870371</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>45195</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>45748.59744212963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>44922</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>45791.3162037037</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>45631.61869212963</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45791</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37626,7 +37626,7 @@
         <v>45833.63579861111</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45695.60015046296</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45414.486875</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>44391</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -37859,7 +37859,7 @@
         <v>45247</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>45166</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -37973,7 +37973,7 @@
         <v>45467</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>45746</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -38092,7 +38092,7 @@
         <v>45834.34737268519</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -38154,7 +38154,7 @@
         <v>45414.96341435185</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -38211,7 +38211,7 @@
         <v>44285</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38268,7 +38268,7 @@
         <v>45411.4666087963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38330,7 +38330,7 @@
         <v>44510.9491087963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         <v>45453</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38449,7 +38449,7 @@
         <v>44466.56642361111</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>45238</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45740.60347222222</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>45531.62141203704</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>44480</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45793.45204861111</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -38801,7 +38801,7 @@
         <v>45726.61520833334</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>45561.61509259259</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -38920,7 +38920,7 @@
         <v>44228</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -38977,7 +38977,7 @@
         <v>45757.56491898148</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>45665.57373842593</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>45692</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45720.40268518519</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45182</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>44887</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45698.40146990741</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45608</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
         <v>45686.33310185185</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>45695.57171296296</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45762.60907407408</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>45706.55993055556</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>45204.40770833333</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>44550</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>44750</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>45232.46239583333</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45378</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>45491.44971064815</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45796.59857638889</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>44904</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>45796.52836805556</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45693</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45653.57240740741</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>45165.70483796296</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45642.6366087963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45701.60901620371</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45266</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>45407</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>44855</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>44855</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -40717,7 +40717,7 @@
         <v>45204</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>45798.63596064815</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45791</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45594.463125</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45117</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44188</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45551.47325231481</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45371</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45362</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>45638.81375</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>45602.57827546296</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45300</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>45140</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45488.94857638889</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45250</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45698.4930787037</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45243.37567129629</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45203</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45798.63611111111</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45282</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>44582</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45684.62510416667</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45260</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45145.95255787037</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45746</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>45803.69828703703</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>44847</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45800.64319444444</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>44141</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45392.95844907407</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45392</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>45117</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45803.6837962963</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45656</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>45800.37061342593</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>44757</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45800.65177083333</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>44711</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -42938,7 +42938,7 @@
         <v>45117</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -43000,7 +43000,7 @@
         <v>45800</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -43057,7 +43057,7 @@
         <v>45474.69074074074</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         <v>45800.57129629629</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -43171,7 +43171,7 @@
         <v>45800.57461805556</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45245</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>45800</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>45800.56810185185</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>44203</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>45160.66704861111</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43523,7 +43523,7 @@
         <v>45572</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>44880</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43642,7 +43642,7 @@
         <v>45692</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>45721</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45238</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -43818,7 +43818,7 @@
         <v>45602</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>44390</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>45687</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45362</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45643.64706018518</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45695.61160879629</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45805</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -44227,7 +44227,7 @@
         <v>45289</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44284,7 +44284,7 @@
         <v>45805.54185185185</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>45807.58930555556</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>44379.59675925926</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45484</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45572.45601851852</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45751.3734837963</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45751.57877314815</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45807.56728009259</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45261</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45733</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45737.36873842592</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45679.70027777777</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45810.31376157407</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45810.32105324074</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45686.35247685185</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45749</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>44970</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45721</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45649.45143518518</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45621</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45475</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>45811.69912037037</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>44971</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>44901.59349537037</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45698.39486111111</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>45466.62116898148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>45667.57217592592</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45615.61121527778</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>45118.94061342593</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45474.3981712963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45246</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45811.54760416667</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>45406.05033564815</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45694.34268518518</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45758.67065972222</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>44349</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45607</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45721.4546412037</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>44498</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>44498</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45785.67431712963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45709</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45813.44443287037</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>44858</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45635</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45813.46969907408</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45813.68361111111</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>45812.32266203704</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -47065,7 +47065,7 @@
         <v>45814</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>45610.36561342593</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>45814</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45117</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>45817.56761574074</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>45815.50844907408</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>44865</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>45552.67611111111</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45701</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>44741</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45818.3293287037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>45818.33532407408</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -47759,7 +47759,7 @@
         <v>45818.34833333334</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -47821,7 +47821,7 @@
         <v>45670</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -47878,7 +47878,7 @@
         <v>45763.44112268519</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -47935,7 +47935,7 @@
         <v>45615.61302083333</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -47997,7 +47997,7 @@
         <v>44540</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -48054,7 +48054,7 @@
         <v>45496.41289351852</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>44427</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -48173,7 +48173,7 @@
         <v>45623.48571759259</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         <v>45818.34473379629</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         <v>45274</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48349,7 +48349,7 @@
         <v>45257</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48406,7 +48406,7 @@
         <v>45818.36246527778</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>45607.63211805555</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45818.34474537037</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -48587,7 +48587,7 @@
         <v>45818.37056712963</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>44658</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45726.37850694444</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45121</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -48830,7 +48830,7 @@
         <v>45820</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -48887,7 +48887,7 @@
         <v>45820</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -48944,7 +48944,7 @@
         <v>45820.36512731481</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -49001,7 +49001,7 @@
         <v>45820</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -49058,7 +49058,7 @@
         <v>45751.6877662037</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -49120,7 +49120,7 @@
         <v>45408</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -49177,7 +49177,7 @@
         <v>45432.36971064815</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -49234,7 +49234,7 @@
         <v>45231</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45820.36498842593</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45820.36506944444</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>45821.39026620371</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45474.69155092593</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45713</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49586,7 +49586,7 @@
         <v>45173</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -49648,7 +49648,7 @@
         <v>45721.54896990741</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -49705,7 +49705,7 @@
         <v>45820.47200231482</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45764.47059027778</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>45560.38056712963</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -49886,7 +49886,7 @@
         <v>45867.46560185185</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -49943,7 +49943,7 @@
         <v>45867.41707175926</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -50000,7 +50000,7 @@
         <v>45245</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -50057,7 +50057,7 @@
         <v>45826.4705787037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -50119,7 +50119,7 @@
         <v>45869.34439814815</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45827.34488425926</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -50243,7 +50243,7 @@
         <v>45699.66576388889</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50305,7 +50305,7 @@
         <v>45870</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50362,7 +50362,7 @@
         <v>45700.30092592593</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50424,7 +50424,7 @@
         <v>45601</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50481,7 +50481,7 @@
         <v>45875.51046296296</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50538,7 +50538,7 @@
         <v>45671.59114583334</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50595,7 +50595,7 @@
         <v>45180</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -50657,7 +50657,7 @@
         <v>45832.34630787037</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -50719,7 +50719,7 @@
         <v>45832.53225694445</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45832</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45833.34490740741</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45833.36050925926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45833.36083333333</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45832.53935185185</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45833.36111111111</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45834.61517361111</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -51195,7 +51195,7 @@
         <v>45835.42712962963</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -51252,7 +51252,7 @@
         <v>44179</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45877.46555555556</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51366,7 +51366,7 @@
         <v>45876</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51423,7 +51423,7 @@
         <v>45876</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51480,7 +51480,7 @@
         <v>45834.34726851852</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51542,7 +51542,7 @@
         <v>45877.57403935185</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45839.61541666667</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>45614.63606481482</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45614.63701388889</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -51780,7 +51780,7 @@
         <v>45056</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>45601.33743055556</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -51899,7 +51899,7 @@
         <v>45454.57899305555</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -51956,7 +51956,7 @@
         <v>45880</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -52013,7 +52013,7 @@
         <v>45839.61594907408</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>45719</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>45764</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45839.72320601852</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>45881.39909722222</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52303,7 +52303,7 @@
         <v>45836.34413194445</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45881.40521990741</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52422,7 +52422,7 @@
         <v>45881.51081018519</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52484,7 +52484,7 @@
         <v>45839.61582175926</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52546,7 +52546,7 @@
         <v>45839.61563657408</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>45878</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -52670,7 +52670,7 @@
         <v>45882.34510416666</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -52732,7 +52732,7 @@
         <v>45883.61028935185</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>45841.46925925926</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45176</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         <v>44334</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -52970,7 +52970,7 @@
         <v>45190</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -53027,7 +53027,7 @@
         <v>45841.43987268519</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         <v>45882.69851851852</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -53146,7 +53146,7 @@
         <v>45841.67834490741</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -53208,7 +53208,7 @@
         <v>45180</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -53270,7 +53270,7 @@
         <v>45840.40717592592</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53332,7 +53332,7 @@
         <v>45883.37883101852</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53389,7 +53389,7 @@
         <v>44757</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53451,7 +53451,7 @@
         <v>45842</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53508,7 +53508,7 @@
         <v>45499.48672453704</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53565,7 +53565,7 @@
         <v>45887.44883101852</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53622,7 +53622,7 @@
         <v>45887.55252314815</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -53684,7 +53684,7 @@
         <v>45842.6099537037</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -53741,7 +53741,7 @@
         <v>45842</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -53798,7 +53798,7 @@
         <v>45887.58372685185</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -53855,7 +53855,7 @@
         <v>45887.59064814815</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -53912,7 +53912,7 @@
         <v>45471.63390046296</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -53969,7 +53969,7 @@
         <v>45842.39587962963</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -54031,7 +54031,7 @@
         <v>45597.49638888889</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -54088,7 +54088,7 @@
         <v>45695.45013888889</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -54150,7 +54150,7 @@
         <v>45239.9681712963</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -54207,7 +54207,7 @@
         <v>45152</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -54269,7 +54269,7 @@
         <v>45842.40013888889</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54331,7 +54331,7 @@
         <v>45876</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54388,7 +54388,7 @@
         <v>45245.5478125</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54450,7 +54450,7 @@
         <v>45672.53806712963</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54512,7 +54512,7 @@
         <v>45674</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54569,7 +54569,7 @@
         <v>45889.37520833333</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54631,7 +54631,7 @@
         <v>45889.38626157407</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>45847.51106481482</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>45847.65717592592</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45847.46462962963</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45888.72445601852</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -54931,7 +54931,7 @@
         <v>45888.72766203704</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45848</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -55050,7 +55050,7 @@
         <v>45848.60371527778</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45848.48070601852</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>44331</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         <v>45849.4525462963</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>45139</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55340,7 +55340,7 @@
         <v>45817</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45849.3859837963</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45853.6156712963</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45694.64416666667</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45894.43864583333</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55640,7 +55640,7 @@
         <v>45894.63693287037</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -55702,7 +55702,7 @@
         <v>45895.36994212963</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -55759,7 +55759,7 @@
         <v>45630</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -55816,7 +55816,7 @@
         <v>44893</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -55873,7 +55873,7 @@
         <v>45764.40834490741</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -55930,7 +55930,7 @@
         <v>45854.66518518519</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -55987,7 +55987,7 @@
         <v>45854.65378472222</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -56044,7 +56044,7 @@
         <v>45896.34443287037</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -56106,7 +56106,7 @@
         <v>45897.49424768519</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -56163,7 +56163,7 @@
         <v>45897.44951388889</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -56220,7 +56220,7 @@
         <v>45897.45311342592</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -56277,7 +56277,7 @@
         <v>45855.61193287037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>45897.46832175926</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56396,7 +56396,7 @@
         <v>45483</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56453,7 +56453,7 @@
         <v>45586</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56510,7 +56510,7 @@
         <v>44901.54615740741</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56572,7 +56572,7 @@
         <v>45099.37211805556</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56629,7 +56629,7 @@
         <v>45109.44534722222</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56691,7 +56691,7 @@
         <v>45588</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -56748,7 +56748,7 @@
         <v>45723.50841435185</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -56805,7 +56805,7 @@
         <v>45713.36836805556</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -56867,7 +56867,7 @@
         <v>45901.38590277778</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>45898.64267361111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -56981,7 +56981,7 @@
         <v>45453.95237268518</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>44764</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>44764</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>45746.79134259259</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>44154</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45783</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>45861.6841087963</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45860</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57447,7 +57447,7 @@
         <v>45719.32584490741</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57504,7 +57504,7 @@
         <v>45615.59521990741</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57561,7 +57561,7 @@
         <v>44834.95019675926</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57623,7 +57623,7 @@
         <v>45448.67574074074</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57685,7 +57685,7 @@
         <v>45695.4046875</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -57747,7 +57747,7 @@
         <v>45373</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45279</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -57861,7 +57861,7 @@
         <v>45348</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -57918,7 +57918,7 @@
         <v>45370.94969907407</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -57980,7 +57980,7 @@
         <v>45863</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -58037,7 +58037,7 @@
         <v>45904.55565972222</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -58094,7 +58094,7 @@
         <v>45905.4174537037</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -58151,7 +58151,7 @@
         <v>45309.94650462963</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -58208,7 +58208,7 @@
         <v>45862.34668981482</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -58270,7 +58270,7 @@
         <v>45863.45778935185</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58327,7 +58327,7 @@
         <v>45300</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58384,7 +58384,7 @@
         <v>45905.4375</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58441,7 +58441,7 @@
         <v>45700.56194444445</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>45574.43403935185</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45097</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58622,7 +58622,7 @@
         <v>45635.67949074074</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58679,7 +58679,7 @@
         <v>45226</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -58736,7 +58736,7 @@
         <v>45904.56144675926</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -58793,7 +58793,7 @@
         <v>45096</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -58850,7 +58850,7 @@
         <v>45708</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -58912,7 +58912,7 @@
         <v>45565.32449074074</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -58969,7 +58969,7 @@
         <v>45560.45841435185</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -59031,7 +59031,7 @@
         <v>45398</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -59088,7 +59088,7 @@
         <v>45216.3965625</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>44788</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -59202,7 +59202,7 @@
         <v>44830</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>45740</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>44600.37212962963</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45764.55260416667</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45666.65987268519</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>44140</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>45446.68733796296</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59611,7 +59611,7 @@
         <v>45377</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59668,7 +59668,7 @@
         <v>44522.46662037037</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -59725,7 +59725,7 @@
         <v>45551.34414351852</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -59782,7 +59782,7 @@
         <v>45700.6833912037</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -59839,7 +59839,7 @@
         <v>45579.66459490741</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -59896,7 +59896,7 @@
         <v>45720</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -59953,7 +59953,7 @@
         <v>45614.63575231482</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -60010,7 +60010,7 @@
         <v>45050</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -60072,7 +60072,7 @@
         <v>45055</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>45705.33446759259</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -60191,7 +60191,7 @@
         <v>45547.42736111111</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -60248,7 +60248,7 @@
         <v>45602.39862268518</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60305,7 +60305,7 @@
         <v>45602.42878472222</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>45686</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60419,7 +60419,7 @@
         <v>45695.47791666666</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60476,7 +60476,7 @@
         <v>45112</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60533,7 +60533,7 @@
         <v>45547.42732638889</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60590,7 +60590,7 @@
         <v>45713.59163194444</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60652,7 +60652,7 @@
         <v>45747.47025462963</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -60714,7 +60714,7 @@
         <v>45608.86341435185</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -60771,7 +60771,7 @@
         <v>45251.65152777778</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -60828,7 +60828,7 @@
         <v>45056</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -60885,7 +60885,7 @@
         <v>45182</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -60942,7 +60942,7 @@
         <v>45485</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -60999,7 +60999,7 @@
         <v>45036</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -61056,7 +61056,7 @@
         <v>45036</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -61113,7 +61113,7 @@
         <v>45586.53618055556</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -61170,7 +61170,7 @@
         <v>44362</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -61227,7 +61227,7 @@
         <v>45600.49616898148</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61284,7 +61284,7 @@
         <v>45476</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61341,7 +61341,7 @@
         <v>45748.57269675926</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61398,7 +61398,7 @@
         <v>45721.45563657407</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61460,7 +61460,7 @@
         <v>45392</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61522,7 +61522,7 @@
         <v>45216</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         <v>45572</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61641,7 +61641,7 @@
         <v>45209</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -61698,7 +61698,7 @@
         <v>45560</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -61760,7 +61760,7 @@
         <v>45082</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -61822,7 +61822,7 @@
         <v>44970</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -61879,7 +61879,7 @@
         <v>45700.27895833334</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -61941,7 +61941,7 @@
         <v>44211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>44965</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -62060,7 +62060,7 @@
         <v>45112</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -62117,7 +62117,7 @@
         <v>45555.43584490741</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -62174,7 +62174,7 @@
         <v>45696.3440162037</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -62231,7 +62231,7 @@
         <v>45217</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -62288,7 +62288,7 @@
         <v>45698.57129629629</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62345,7 +62345,7 @@
         <v>45342</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62407,7 +62407,7 @@
         <v>45418.94616898148</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>45457.55922453704</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62526,7 +62526,7 @@
         <v>45118</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>45401.59810185185</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62640,7 +62640,7 @@
         <v>45705</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -62697,7 +62697,7 @@
         <v>45554</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -62759,7 +62759,7 @@
         <v>44206</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -62816,7 +62816,7 @@
         <v>45698.45653935185</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -62873,7 +62873,7 @@
         <v>45580.36991898148</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -62935,7 +62935,7 @@
         <v>44592</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -62992,7 +62992,7 @@
         <v>44887</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -63054,7 +63054,7 @@
         <v>45097</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -63111,7 +63111,7 @@
         <v>45760.81083333334</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -63168,7 +63168,7 @@
         <v>45607</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -63225,7 +63225,7 @@
         <v>45608.61606481481</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -63282,7 +63282,7 @@
         <v>44741</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63339,7 +63339,7 @@
         <v>45687.48931712963</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63396,7 +63396,7 @@
         <v>45316</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63453,7 +63453,7 @@
         <v>44818</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63510,7 +63510,7 @@
         <v>45401.59133101852</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63567,7 +63567,7 @@
         <v>45195</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63624,7 +63624,7 @@
         <v>44133</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -63681,7 +63681,7 @@
         <v>45713.59741898148</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -63743,7 +63743,7 @@
         <v>45602.65599537037</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -63800,7 +63800,7 @@
         <v>45603.28460648148</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -63862,7 +63862,7 @@
         <v>45452.55271990741</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -63924,7 +63924,7 @@
         <v>44988.94056712963</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -63986,7 +63986,7 @@
         <v>44544.49326388889</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -64043,7 +64043,7 @@
         <v>45225.60212962963</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -64100,7 +64100,7 @@
         <v>45643.65354166667</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -64157,7 +64157,7 @@
         <v>44792.27644675926</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -64214,7 +64214,7 @@
         <v>45614.65925925926</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -64271,7 +64271,7 @@
         <v>45035</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64328,7 +64328,7 @@
         <v>44273</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64385,7 +64385,7 @@
         <v>44151</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64442,7 +64442,7 @@
         <v>44377</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64499,7 +64499,7 @@
         <v>45554.59550925926</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64556,7 +64556,7 @@
         <v>45257</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64613,7 +64613,7 @@
         <v>45182</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64670,7 +64670,7 @@
         <v>45168</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -64727,7 +64727,7 @@
         <v>45478.42063657408</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -64784,7 +64784,7 @@
         <v>45378</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -64841,7 +64841,7 @@
         <v>45692.60364583333</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -64898,7 +64898,7 @@
         <v>45566.51501157408</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -64955,7 +64955,7 @@
         <v>45642.63666666667</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -65012,7 +65012,7 @@
         <v>45133</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -65069,7 +65069,7 @@
         <v>45090</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -65126,7 +65126,7 @@
         <v>45467</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -65183,7 +65183,7 @@
         <v>44488.47928240741</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -65240,7 +65240,7 @@
         <v>45751.28243055556</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65302,7 +65302,7 @@
         <v>45477.35225694445</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65364,7 +65364,7 @@
         <v>45369</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65421,7 +65421,7 @@
         <v>45203.46523148148</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65478,7 +65478,7 @@
         <v>45370</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65535,7 +65535,7 @@
         <v>45243.33297453704</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65597,7 +65597,7 @@
         <v>45707.33935185185</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65659,7 +65659,7 @@
         <v>45750.6447800926</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -65721,7 +65721,7 @@
         <v>45608.61923611111</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -65778,7 +65778,7 @@
         <v>45704.71069444445</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -65840,7 +65840,7 @@
         <v>45620.67667824074</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -65897,7 +65897,7 @@
         <v>44974</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -65959,7 +65959,7 @@
         <v>45634.7925</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -66016,7 +66016,7 @@
         <v>45634.79854166666</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -66073,7 +66073,7 @@
         <v>45714.34859953704</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -66155,7 +66155,7 @@
         <v>45744.59894675926</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -66217,7 +66217,7 @@
         <v>45552.57210648148</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -66274,7 +66274,7 @@
         <v>44456</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66331,7 +66331,7 @@
         <v>44825</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66388,7 +66388,7 @@
         <v>45478.60708333334</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66445,7 +66445,7 @@
         <v>45203.44248842593</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66502,7 +66502,7 @@
         <v>45686.32671296296</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66564,7 +66564,7 @@
         <v>45561.61515046296</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66621,7 +66621,7 @@
         <v>45700.37127314815</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -66678,7 +66678,7 @@
         <v>45700.37481481482</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -66740,7 +66740,7 @@
         <v>45453.45515046296</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -66797,7 +66797,7 @@
         <v>45692.58106481482</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -66854,7 +66854,7 @@
         <v>45565.33152777778</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -66911,7 +66911,7 @@
         <v>45635.39820601852</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -66968,7 +66968,7 @@
         <v>45593.38568287037</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -67025,7 +67025,7 @@
         <v>45586.46927083333</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -67082,7 +67082,7 @@
         <v>44601.35342592592</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -67139,7 +67139,7 @@
         <v>44335</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -67196,7 +67196,7 @@
         <v>45474</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -67253,7 +67253,7 @@
         <v>44939</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67310,7 +67310,7 @@
         <v>44504</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67367,7 +67367,7 @@
         <v>45415.45006944444</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67424,7 +67424,7 @@
         <v>44961</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67481,7 +67481,7 @@
         <v>45660.49618055556</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67538,7 +67538,7 @@
         <v>45560.69164351852</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67595,7 +67595,7 @@
         <v>45254</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -67652,7 +67652,7 @@
         <v>44972.55690972223</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -67709,7 +67709,7 @@
         <v>45189.60987268519</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -67766,7 +67766,7 @@
         <v>45310</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -67823,7 +67823,7 @@
         <v>45532.48732638889</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -67880,7 +67880,7 @@
         <v>45469</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -67937,7 +67937,7 @@
         <v>44370</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -67994,7 +67994,7 @@
         <v>44803</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -68051,7 +68051,7 @@
         <v>45244</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -68108,7 +68108,7 @@
         <v>45676</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -68165,7 +68165,7 @@
         <v>45446.47634259259</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -68227,7 +68227,7 @@
         <v>45550.66542824074</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68284,7 +68284,7 @@
         <v>45707.55246527777</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68346,7 +68346,7 @@
         <v>45649.38149305555</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68403,7 +68403,7 @@
         <v>45708</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68465,7 +68465,7 @@
         <v>45324</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68522,7 +68522,7 @@
         <v>44207</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68579,7 +68579,7 @@
         <v>45744</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -68636,7 +68636,7 @@
         <v>44849.8044212963</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -68693,7 +68693,7 @@
         <v>45090</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -68750,7 +68750,7 @@
         <v>44596</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -68807,7 +68807,7 @@
         <v>45538.68200231482</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -68864,7 +68864,7 @@
         <v>45554.59538194445</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -68921,7 +68921,7 @@
         <v>45750.60577546297</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -68978,7 +68978,7 @@
         <v>45588</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -69035,7 +69035,7 @@
         <v>45560.6599537037</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -69092,7 +69092,7 @@
         <v>44631</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -69149,7 +69149,7 @@
         <v>45772.58283564815</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -69206,7 +69206,7 @@
         <v>45772.59200231481</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -69263,7 +69263,7 @@
         <v>45772.62052083333</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -69320,7 +69320,7 @@
         <v>44715.48863425926</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -69382,7 +69382,7 @@
         <v>45695.42418981482</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -69444,7 +69444,7 @@
         <v>45055</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -69501,7 +69501,7 @@
         <v>45721.55653935186</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -69558,7 +69558,7 @@
         <v>45758.58943287037</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -69620,7 +69620,7 @@
         <v>45432.54027777778</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -69677,7 +69677,7 @@
         <v>45042</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -69734,7 +69734,7 @@
         <v>45618.53126157408</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -69791,7 +69791,7 @@
         <v>45618.53633101852</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -69848,7 +69848,7 @@
         <v>45226</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -69905,7 +69905,7 @@
         <v>45748.36445601852</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -69962,7 +69962,7 @@
         <v>45748.37173611111</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -70019,7 +70019,7 @@
         <v>44908</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -70081,7 +70081,7 @@
         <v>45713.38028935185</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -70143,7 +70143,7 @@
         <v>45740.60405092593</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -70205,7 +70205,7 @@
         <v>45603.44815972223</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -70267,7 +70267,7 @@
         <v>45123.61459490741</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -70329,7 +70329,7 @@
         <v>45602</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -70386,7 +70386,7 @@
         <v>45662</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -70443,7 +70443,7 @@
         <v>45686.39777777778</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -70505,7 +70505,7 @@
         <v>45412.51260416667</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -70562,7 +70562,7 @@
         <v>45371</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -70619,7 +70619,7 @@
         <v>44389</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -70681,7 +70681,7 @@
         <v>44686</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -70738,7 +70738,7 @@
         <v>45189</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -70795,7 +70795,7 @@
         <v>45713.59952546296</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -70857,7 +70857,7 @@
         <v>45693.48239583334</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -70914,7 +70914,7 @@
         <v>45713.60719907407</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -70976,7 +70976,7 @@
         <v>45386</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -71033,7 +71033,7 @@
         <v>45630.47099537037</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -71090,7 +71090,7 @@
         <v>45265.52887731481</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -71147,7 +71147,7 @@
         <v>45713.59623842593</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -71209,7 +71209,7 @@
         <v>44847</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -71266,7 +71266,7 @@
         <v>45649.4634375</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -71323,7 +71323,7 @@
         <v>45638.81385416666</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -71380,7 +71380,7 @@
         <v>44732</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -71437,7 +71437,7 @@
         <v>45165.69965277778</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -71494,7 +71494,7 @@
         <v>45758.66180555556</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -71551,7 +71551,7 @@
         <v>44557</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -71608,7 +71608,7 @@
         <v>44726</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -71665,7 +71665,7 @@
         <v>45693.67361111111</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -71727,7 +71727,7 @@
         <v>45694.43806712963</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -71784,7 +71784,7 @@
         <v>45706.59251157408</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>

--- a/Översikt KROKOM.xlsx
+++ b/Översikt KROKOM.xlsx
@@ -567,7 +567,7 @@
         <v>45716</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44522</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45637</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45348</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>44165</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>45384</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>45254</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>45709</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45603</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44378</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>45887.44892361111</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45845</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45894.43864583333</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>45478</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>44323</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45121</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>45155</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45646</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>44565</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>45453</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45219</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44363</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45630</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45041</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>45625</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45790</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45553</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45663</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>45849</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45644</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>45596.5093287037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45428</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>44306.52587962963</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>44575</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>44326</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>45792</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>44581</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>44323</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>45475</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>44780</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>45691</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>45784.56270833333</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44231</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>45646</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>45646</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45551</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>44475</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>45512</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>45488.56961805555</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>45534</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45639</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44795</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>45719.52238425926</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>45041</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>45580</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>45527</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>45219</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44118</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>45643</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45454</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>44498</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>44552</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45457</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>45181</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>45169</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>44308</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>44133</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44585</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44698</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>44500</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>45316</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>45839.68914351852</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>45149</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>45267</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>45616</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>45862.42901620371</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>45475</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>44271</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44265</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44534</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>44494</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>45370</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>44326</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>44477</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>45180</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>44834</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45252</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>44797</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>45474</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>45755.47527777778</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45581</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45862.4257175926</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45862.43403935185</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45832.38581018519</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>44183</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>44515</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>44557</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44150</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>45874.67765046296</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>45838.67858796296</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>45888.55305555555</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>44452</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>45079</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>44903</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>44540</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45532</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45551</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>45615</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>44546</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>45726.46192129629</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>44162</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>44510.94930555556</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>44728</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>44895</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>45624</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45169</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>44553</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>45595</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>44904</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45764</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>44174</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>44966</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>44879</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45735</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>45632</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45527</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>45849.42818287037</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45621</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>45310</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45617</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>45656.54600694445</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45511.55719907407</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44540</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>45271</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>45453.63133101852</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>45216</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>45821.44299768518</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>45372</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45636</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>45216.67748842593</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>44757</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>44873</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>44757</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>45887.6989699074</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>45526</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45630</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>44841</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45863.58127314815</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>45233</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>44867</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45313</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45692</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>44355</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44161</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>44378</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>44524</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>44316</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>44230</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>44757</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45268</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45376</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>45793.4189699074</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>44540</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45804.60005787037</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>45554</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>44209</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>44683</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>45348</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45877.67787037037</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>45643.53393518519</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45656.59703703703</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45862</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>45595</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>45896.34465277778</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>45647</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>45863.59111111111</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>44279</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>45869</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>44879</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45223</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>44099</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44154</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>44090</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44512</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44445</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>44512</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>44445</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>44728</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>44797</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>44742</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>44207</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>44377</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45123</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45622</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>44603</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45595</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45079</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45271</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45800</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44630</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44568</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>45153</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>45645.67945601852</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>45819.65796296296</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45700</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45826.45174768518</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45609</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45595</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45838.67815972222</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45838</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45020</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>45839.60460648148</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45685.78776620371</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>45098</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45841.52454861111</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>45695.42197916667</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>45686.27208333334</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45750.42127314815</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44540</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45702.47149305556</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45180</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44568</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>45467</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45847.51078703703</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>45847.46962962963</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45595</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>44568</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>45595</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45609</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45736.42743055556</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45407</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45635</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45243</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>44308</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>44313</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44113</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>44102</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>44103</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>44214</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>44371</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>44748.94689814815</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>44407</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>44473.44813657407</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>44473.508125</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>44256</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>44175</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>44183</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>44679</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>44665</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>44173</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>44445</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>44494</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>44610</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -23897,7 +23897,7 @@
         <v>44376.87497685185</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>44377.44767361111</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44788</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44449</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>44133</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>44285</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>44263</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>44183</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>44183</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>44524</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>44370</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44591</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>44123</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>44714.438125</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>44162</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>44090</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -24824,7 +24824,7 @@
         <v>44141</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>44255</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>44577.47756944445</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>44287</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25052,7 +25052,7 @@
         <v>44533</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44749</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>44126.94510416667</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>44831.37650462963</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>44200</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44172</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44512.94539351852</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44369.41452546296</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44271.43831018519</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44312</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44502.94153935185</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>44306</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>44502</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>44788</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44207</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44851.57131944445</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44209</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44209</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44243</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44106</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44473</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44466.53040509259</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44300</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>44539</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>44495</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>44495</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>44277.59521990741</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>44512</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44172</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44337</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>44214</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44502.94140046297</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44693.41668981482</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44858</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44470</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44153</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>44473.53681712963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44151</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44139</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>44382.92065972222</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>44095</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>44358.63585648148</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44459</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>44526</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>44214</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>44524</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>44714</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>44377</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>44728.94420138889</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>44123</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>44610</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>44113</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>44123</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>44697.94231481481</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>44473.53013888889</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>44459</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>44848</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>44875.41104166667</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>44727</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>44169</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>44470</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>44705</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>44307.42378472222</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>44820</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>44209</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>44468</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>44118.98730324074</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>45362</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>44825</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>45370</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29132,7 +29132,7 @@
         <v>45749</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>44285</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>45251.65152777778</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>45572.45601851852</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>44803</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>45720</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45035</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45713.60719907407</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>45342</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>44848</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45700.37127314815</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29774,7 +29774,7 @@
         <v>45700.37481481482</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>45386</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>45362</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>45414.486875</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>44400.37204861111</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45552.57210648148</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>45195</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45412.51260416667</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>45714.34859953704</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45719.32584490741</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30374,7 +30374,7 @@
         <v>45370.94969907407</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45531.62141203704</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>45411</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45747.47025462963</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>44830</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>44316</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>45203.46523148148</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30793,7 +30793,7 @@
         <v>45253</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>44337</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>45698.39486111111</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>44875</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>44834.95019675926</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45254</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>45082</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>45112</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>45740</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45133</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>44539</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>45560</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>44874</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45245.5478125</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>45415.45006944444</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>44123</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45760.81083333334</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>45373</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>45601.33743055556</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45244</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>45324</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>45764.55260416667</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45182</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45217</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45165.69965277778</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45203</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45300</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>45393</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>45686.32671296296</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>44901.59349537037</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45554</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32600,7 +32600,7 @@
         <v>45701</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45471.63390046296</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45239.9681712963</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32771,7 +32771,7 @@
         <v>45474.69155092593</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32828,7 +32828,7 @@
         <v>44389</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>44550</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>44974</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>45243.37567129629</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>45715</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>45776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>45398</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>45693</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45777</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>45457.55922453704</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>44483.42253472222</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>45712</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>44519.63436342592</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>45265.52887731481</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>45777</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45777</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>45748.3822337963</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>45474</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>45282</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>45454.57899305555</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45779.56659722222</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34065,7 +34065,7 @@
         <v>45478.42063657408</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45250</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>44516</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>45779.63834490741</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34298,7 +34298,7 @@
         <v>45457.35388888889</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45226</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45152</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>45779.57626157408</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>45779.65980324074</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34588,7 +34588,7 @@
         <v>45779.42630787037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34645,7 +34645,7 @@
         <v>45411.4666087963</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45779.5674074074</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>45696</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>44504</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>45392</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>45414.96341435185</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>44939</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>45551.34414351852</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45783.45121527778</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45783.43409722222</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>45713.37111111111</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>45688.38393518519</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>45096</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45580.36991898148</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>45474.69074074074</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45740</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>45608.86341435185</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>45112</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>45786.35219907408</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>45418.94616898148</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>45786</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>45785.52112268518</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>45785.5403125</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45117</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>45579.66459490741</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>45392</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44480</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>45278.65582175926</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>45467</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45785.54635416